--- a/Отчёт/МО2.xlsx
+++ b/Отчёт/МО2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artyo\source\repos\MaxArt-Term61\Отчёт\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maksim\Desktop\Мо_Костя\Лаб_2\Отчёт\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DE51A6-3166-4EB0-923E-EABD1B12D445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{320BCE1C-1022-4156-9D7E-14353D01BB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8400" yWindow="1995" windowWidth="25365" windowHeight="17760" xr2:uid="{9776549A-3957-4A95-AACA-BCFA2710EB61}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9776549A-3957-4A95-AACA-BCFA2710EB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="30">
   <si>
     <t>i</t>
   </si>
@@ -76,12 +79,72 @@
   <si>
     <t>eps=</t>
   </si>
+  <si>
+    <t>x0 y0</t>
+  </si>
+  <si>
+    <t>0
+-1</t>
+  </si>
+  <si>
+    <t>4
+-1.6</t>
+  </si>
+  <si>
+    <t>Функция Розенброка</t>
+  </si>
+  <si>
+    <t>0
+0</t>
+  </si>
+  <si>
+    <t>0.5
+0.5</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>grad1</t>
+  </si>
+  <si>
+    <t>grad2</t>
+  </si>
+  <si>
+    <t>5
+6</t>
+  </si>
+  <si>
+    <t>eta1</t>
+  </si>
+  <si>
+    <t>eta2</t>
+  </si>
+  <si>
+    <t>eta3</t>
+  </si>
+  <si>
+    <t>eta4</t>
+  </si>
+  <si>
+    <t>0.0
+0.0</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,6 +152,13 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -99,7 +169,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -122,15 +192,104 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -465,10 +624,48 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{768FE0D3-F3E2-4B20-ACF6-AB64EBC69073}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:BE69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="8.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.85546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.28515625" style="12" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.5703125" style="12" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="34" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="37" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="3" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="46" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="50" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="52" max="54" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="56" max="57" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:57" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -478,218 +675,3556 @@
       <c r="C1" s="1">
         <v>1E-3</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="M1" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="N2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="P2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
+      <c r="Q2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="T2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="U2" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="V2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="W2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="X2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>9.9999999999999995E-8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4">
         <v>6.9649842884258497</v>
       </c>
-      <c r="C3" s="2">
+      <c r="D3" s="4">
         <v>6.9776709558313996</v>
       </c>
-      <c r="D3" s="2">
+      <c r="E3" s="4">
         <v>35.597132714153098</v>
       </c>
-      <c r="E3" s="2">
+      <c r="F3" s="4">
         <v>-9.3925161182585892</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="4">
         <v>-2.5374518687381999</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="4">
         <v>2.4937715662246502E-3</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="4">
         <v>996.96498428842494</v>
       </c>
-      <c r="I3" s="2">
+      <c r="J3" s="4">
         <v>992.02232904416803</v>
       </c>
-      <c r="J3" s="2">
+      <c r="K3" s="4">
         <v>396594145.40286702</v>
       </c>
-      <c r="K3" s="2">
+      <c r="L3" s="4">
         <v>150.06581260871101</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+      <c r="N3" s="10">
+        <v>1</v>
+      </c>
+      <c r="O3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="9">
+        <v>0.676354755254861</v>
+      </c>
+      <c r="Q3" s="9">
+        <v>0.46616128497943199</v>
+      </c>
+      <c r="R3" s="9">
+        <v>0.11232486974526799</v>
+      </c>
+      <c r="S3" s="9">
+        <v>3.0024711011620302</v>
+      </c>
+      <c r="T3" s="9">
+        <v>-1.7411045027959999</v>
+      </c>
+      <c r="U3" s="9">
+        <v>2.3308064248971599E-5</v>
+      </c>
+      <c r="V3" s="9">
+        <v>9.3236452447451299</v>
+      </c>
+      <c r="W3" s="9">
+        <v>0.46616128497943199</v>
+      </c>
+      <c r="X3" s="9">
+        <v>1000080.88767513</v>
+      </c>
+      <c r="Y3" s="9">
+        <v>64.684660313356403</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="22"/>
+      <c r="C4" s="4">
         <v>6.8721276424421101</v>
       </c>
-      <c r="C4" s="2">
+      <c r="D4" s="4">
         <v>6.9525851037647497</v>
       </c>
-      <c r="D4" s="2">
+      <c r="E4" s="4">
         <v>35.1292233573812</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="4">
         <v>-23.220641682356199</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="4">
         <v>-23.539141472396299</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="4">
         <v>9.8862375975301495E-3</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="4">
         <v>9.2856645983736094E-2</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="4">
         <v>2.5085852066642801E-2</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="4">
         <v>0.46790935677196099</v>
       </c>
-      <c r="K4" s="2">
+      <c r="L4" s="4">
         <v>179.94318917669199</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="N4" s="10">
+        <v>2</v>
+      </c>
+      <c r="O4" s="20"/>
+      <c r="P4" s="9">
+        <v>0.68169223692808001</v>
+      </c>
+      <c r="Q4" s="9">
+        <v>0.46306613000150898</v>
+      </c>
+      <c r="R4" s="9">
+        <v>0.10158819405536</v>
+      </c>
+      <c r="S4" s="9">
+        <v>0.22566781385821999</v>
+      </c>
+      <c r="T4" s="9">
+        <v>0.30690699007459898</v>
+      </c>
+      <c r="U4" s="9">
+        <v>1.7776962686346801E-3</v>
+      </c>
+      <c r="V4" s="9">
+        <v>5.3374816732192302E-3</v>
+      </c>
+      <c r="W4" s="9">
+        <v>3.0951549779235001E-3</v>
+      </c>
+      <c r="X4" s="9">
+        <v>1.07366756899075E-2</v>
+      </c>
+      <c r="Y4" s="9">
+        <v>19.4852221044498</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>3.3321069193283801</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>5.6485528070545596</v>
+      </c>
+      <c r="AF4" s="8">
+        <v>-0.42059430076402898</v>
+      </c>
+      <c r="AG4" s="8">
+        <v>-2.2853058565240399E-2</v>
+      </c>
+      <c r="AH4" s="8">
+        <v>-0.169199805893753</v>
+      </c>
+      <c r="AI4" s="8">
+        <v>-3.2000000726837099</v>
+      </c>
+      <c r="AJ4" s="8">
+        <v>1.0072097949287999</v>
+      </c>
+      <c r="AK4" s="8">
+        <v>3.0274732646727598</v>
+      </c>
+      <c r="AL4" s="8">
+        <v>1.42035691711655</v>
+      </c>
+      <c r="AM4" s="8">
+        <v>157.155586838917</v>
+      </c>
+      <c r="AN4" s="8">
+        <v>1.5830273801549201E-2</v>
+      </c>
+      <c r="AO4" s="8">
+        <v>0.14809070506622399</v>
+      </c>
+      <c r="AQ4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS4" s="8">
+        <v>-0.49379627441149798</v>
+      </c>
+      <c r="AT4" s="8">
+        <v>-0.50121588443282905</v>
+      </c>
+      <c r="AU4" s="8">
+        <v>2.2369323707325299</v>
+      </c>
+      <c r="AV4" s="8">
+        <v>2.4939205778358501E-3</v>
+      </c>
+      <c r="AW4" s="8">
+        <v>0.49379627441149798</v>
+      </c>
+      <c r="AX4" s="8">
+        <v>0.49878411556717001</v>
+      </c>
+      <c r="AY4" s="8">
+        <v>98.763067629267397</v>
+      </c>
+      <c r="AZ4" s="8">
+        <v>0.49875309365160297</v>
+      </c>
+      <c r="BA4" s="8">
+        <v>0.49874689044916698</v>
+      </c>
+      <c r="BB4" s="8">
+        <v>0.49874689044916698</v>
+      </c>
+      <c r="BC4" s="8">
+        <v>0.50374065638657695</v>
+      </c>
+      <c r="BD4" s="8">
+        <v>-1.50367054455671</v>
+      </c>
+      <c r="BE4" s="8">
+        <v>-1.48392200426628</v>
+      </c>
+    </row>
+    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="22"/>
+      <c r="C5" s="4">
         <v>6.8865774897436101</v>
       </c>
-      <c r="C5" s="2">
+      <c r="D5" s="4">
         <v>6.8990983471962997</v>
       </c>
-      <c r="D5" s="2">
+      <c r="E5" s="4">
         <v>34.667471729891197</v>
       </c>
-      <c r="E5" s="2">
+      <c r="F5" s="4">
         <v>-7.8265794605631198</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="4">
         <v>-7.8432945642908303</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="4">
         <v>3.3239152521831899E-3</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="4">
         <v>1.44498473014929E-2</v>
       </c>
-      <c r="I5" s="2">
+      <c r="J5" s="4">
         <v>5.3486756568451803E-2</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="4">
         <v>0.461751627489974</v>
       </c>
-      <c r="K5" s="2">
+      <c r="L5" s="4">
         <v>179.99092138527499</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
+      <c r="N5" s="10">
+        <v>3</v>
+      </c>
+      <c r="O5" s="20"/>
+      <c r="P5" s="9">
+        <v>1.0358578464086901</v>
+      </c>
+      <c r="Q5" s="9">
+        <v>1.0740359805217801</v>
+      </c>
+      <c r="R5" s="9">
+        <v>1.3928047027674899E-3</v>
+      </c>
+      <c r="S5" s="9">
+        <v>0.58231923080518899</v>
+      </c>
+      <c r="T5" s="9">
+        <v>0.181929144639803</v>
+      </c>
+      <c r="U5" s="9">
+        <v>1.8647870950699199</v>
+      </c>
+      <c r="V5" s="9">
+        <v>0.35416560948061498</v>
+      </c>
+      <c r="W5" s="9">
+        <v>0.61096985052027897</v>
+      </c>
+      <c r="X5" s="9">
+        <v>0.10019538935259301</v>
+      </c>
+      <c r="Y5" s="9">
+        <v>28.6867076013909</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC5" s="14"/>
+      <c r="AD5" s="8">
+        <v>3.1858473461718901</v>
+      </c>
+      <c r="AE5" s="8">
+        <v>4.5656740616326097</v>
+      </c>
+      <c r="AF5" s="8">
+        <v>-0.64168429098978796</v>
+      </c>
+      <c r="AG5" s="8">
+        <v>-0.11124032769558601</v>
+      </c>
+      <c r="AH5" s="8">
+        <v>-0.830075058655804</v>
+      </c>
+      <c r="AI5" s="8">
+        <v>6.39999992731628</v>
+      </c>
+      <c r="AJ5" s="8">
+        <v>0.14625957315649299</v>
+      </c>
+      <c r="AK5" s="8">
+        <v>1.08287874542194</v>
+      </c>
+      <c r="AL5" s="8">
+        <v>0.22108999022575801</v>
+      </c>
+      <c r="AM5" s="8">
+        <v>152.72620680553899</v>
+      </c>
+      <c r="AN5" s="8">
+        <v>3.5445801360498901E-2</v>
+      </c>
+      <c r="AO5" s="8">
+        <v>0.26890644715048601</v>
+      </c>
+      <c r="AQ5" s="2">
+        <v>2</v>
+      </c>
+      <c r="AR5" s="13"/>
+      <c r="AS5" s="8">
+        <v>0.99999997541970997</v>
+      </c>
+      <c r="AT5" s="8">
+        <v>0.99999994562678995</v>
+      </c>
+      <c r="AU5" s="8">
+        <v>8.93660002739564E-14</v>
+      </c>
+      <c r="AV5" s="8">
+        <v>1.00250622393692</v>
+      </c>
+      <c r="AW5" s="8">
+        <v>1.4937962498312001</v>
+      </c>
+      <c r="AX5" s="8">
+        <v>1.5012158300596199</v>
+      </c>
+      <c r="AY5" s="8">
+        <v>2.2369323707324398</v>
+      </c>
+      <c r="AZ5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BA5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BB5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BC5" s="8">
+        <v>0.505</v>
+      </c>
+      <c r="BD5" s="8">
+        <v>5.9094234698964201E-6</v>
+      </c>
+      <c r="BE5" s="8">
+        <v>-5.9585840483933297E-6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="22"/>
+      <c r="C6" s="4">
         <v>1.00001087773403</v>
       </c>
-      <c r="C6" s="2">
+      <c r="D6" s="4">
         <v>0.99995988665242896</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E6" s="5">
         <v>2.6012736537825401E-7</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="4">
         <v>-1.02376694938674E-2</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="4">
         <v>1.0180480817746701E-2</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="4">
         <v>0.75212506838664805</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="4">
         <v>5.8865666120095801</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="4">
         <v>5.8991384605438704</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="4">
         <v>34.667471469763797</v>
       </c>
-      <c r="K6" s="2">
+      <c r="L6" s="4">
         <v>90.161938675193795</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
+      <c r="N6" s="10">
+        <v>4</v>
+      </c>
+      <c r="O6" s="20"/>
+      <c r="P6" s="9">
+        <v>1.03632844898805</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>1.0741830069639799</v>
+      </c>
+      <c r="R6" s="9">
+        <v>1.32401435294153E-3</v>
+      </c>
+      <c r="S6" s="9">
+        <v>1.9278061384011402E-2</v>
+      </c>
+      <c r="T6" s="9">
+        <v>-3.9272539874810899E-2</v>
+      </c>
+      <c r="U6" s="9">
+        <v>8.0815222040470699E-4</v>
+      </c>
+      <c r="V6" s="9">
+        <v>4.7060257935949102E-4</v>
+      </c>
+      <c r="W6" s="9">
+        <v>1.47026442196995E-4</v>
+      </c>
+      <c r="X6" s="9">
+        <v>6.8790349825966504E-5</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>109.882110872778</v>
+      </c>
+      <c r="AB6" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="8">
+        <v>2.7321410861811701</v>
+      </c>
+      <c r="AE6" s="8">
+        <v>1.12367151856127</v>
+      </c>
+      <c r="AF6" s="8">
+        <v>-1.7846929695290901</v>
+      </c>
+      <c r="AG6" s="8">
+        <v>-0.37027940765911599</v>
+      </c>
+      <c r="AH6" s="8">
+        <v>-0.65365254101690196</v>
+      </c>
+      <c r="AI6" s="8">
+        <v>12.8000000726837</v>
+      </c>
+      <c r="AJ6" s="8">
+        <v>0.45370625999071901</v>
+      </c>
+      <c r="AK6" s="8">
+        <v>3.4420025430713399</v>
+      </c>
+      <c r="AL6" s="8">
+        <v>1.1430086785393101</v>
+      </c>
+      <c r="AM6" s="8">
+        <v>141.88689752264301</v>
+      </c>
+      <c r="AN6" s="8">
+        <v>0.21479862431673599</v>
+      </c>
+      <c r="AO6" s="8">
+        <v>-0.52588871475978405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="23"/>
+      <c r="C7" s="4">
         <v>0.99998539145897603</v>
       </c>
-      <c r="C7" s="2">
+      <c r="D7" s="4">
         <v>0.99998531867431395</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="5">
         <v>2.1393923152977901E-10</v>
       </c>
-      <c r="E7" s="3">
+      <c r="F7" s="5">
         <v>1.4639223216569901E-5</v>
       </c>
-      <c r="F7" s="3">
+      <c r="G7" s="5">
         <v>1.45778142832009E-5</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="4">
         <v>2.4937715662246502E-3</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="5">
         <v>2.54862750530549E-5</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="5">
         <v>2.5432021885318702E-5</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="5">
         <v>2.5991342614672399E-7</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="4">
         <v>0.120423112826495</v>
       </c>
+      <c r="N7" s="10">
+        <v>47</v>
+      </c>
+      <c r="O7" s="20"/>
+      <c r="P7" s="9">
+        <v>0.99947608361539697</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0.99895035151721101</v>
+      </c>
+      <c r="R7" s="9">
+        <v>2.7492527247898902E-7</v>
+      </c>
+      <c r="S7" s="9">
+        <v>2.09854575833723E-4</v>
+      </c>
+      <c r="T7" s="9">
+        <v>4.1922264610809001E-4</v>
+      </c>
+      <c r="U7" s="9">
+        <v>9.9918510595466896E-4</v>
+      </c>
+      <c r="V7" s="9">
+        <v>7.4849567569867896E-5</v>
+      </c>
+      <c r="W7" s="9">
+        <v>3.7890500026338502E-5</v>
+      </c>
+      <c r="X7" s="9">
+        <v>3.5218175485047698E-6</v>
+      </c>
+      <c r="Y7" s="9">
+        <v>18.423431396487199</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>52</v>
+      </c>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="8">
+        <v>1.1900759709298101</v>
+      </c>
+      <c r="AE7" s="8">
+        <v>1.9744968856785901</v>
+      </c>
+      <c r="AF7" s="8">
+        <v>-2.6613256122728099</v>
+      </c>
+      <c r="AG7" s="8">
+        <v>-4.76018264200003E-4</v>
+      </c>
+      <c r="AH7" s="8">
+        <v>4.7681290611787598E-5</v>
+      </c>
+      <c r="AI7" s="8">
+        <v>0.200024439056396</v>
+      </c>
+      <c r="AJ7" s="8">
+        <v>1.55823257380838E-4</v>
+      </c>
+      <c r="AK7" s="8">
+        <v>1.4589468889303299E-4</v>
+      </c>
+      <c r="AL7" s="8">
+        <v>5.0238899707011302E-8</v>
+      </c>
+      <c r="AM7" s="8">
+        <v>115.35830105728699</v>
+      </c>
+      <c r="AN7" s="8">
+        <v>1.91706772289024E-4</v>
+      </c>
+      <c r="AO7" s="8">
+        <v>2.1851476611471599E-4</v>
+      </c>
+      <c r="AQ7" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS7" s="8">
+        <v>1.19201321643103</v>
+      </c>
+      <c r="AT7" s="8">
+        <v>1.19302415417161</v>
+      </c>
+      <c r="AU7" s="8">
+        <v>3.69712747957247E-2</v>
+      </c>
+      <c r="AV7" s="8">
+        <v>2.4937715662246502E-3</v>
+      </c>
+      <c r="AW7" s="8">
+        <v>2.80798678356896</v>
+      </c>
+      <c r="AX7" s="8">
+        <v>2.7930241541716101</v>
+      </c>
+      <c r="AY7" s="11">
+        <v>3144.9630287251998</v>
+      </c>
+      <c r="AZ7" s="8">
+        <v>0.49875314163485501</v>
+      </c>
+      <c r="BA7" s="8">
+        <v>0.49874689068864297</v>
+      </c>
+      <c r="BB7" s="8">
+        <v>0.49874689068864297</v>
+      </c>
+      <c r="BC7" s="8">
+        <v>0.50374060840420598</v>
+      </c>
+      <c r="BD7" s="8">
+        <v>0.18183888474611001</v>
+      </c>
+      <c r="BE7" s="8">
+        <v>0.20218754811596101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="N8" s="10">
+        <v>48</v>
+      </c>
+      <c r="O8" s="20"/>
+      <c r="P8" s="9">
+        <v>0.99999929818358002</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0.99999556768600195</v>
+      </c>
+      <c r="R8" s="9">
+        <v>9.17783800816715E-10</v>
+      </c>
+      <c r="S8" s="9">
+        <v>5.3839694295182796E-4</v>
+      </c>
+      <c r="T8" s="9">
+        <v>4.0986131069677004E-3</v>
+      </c>
+      <c r="U8" s="9">
+        <v>2.49322449179193</v>
+      </c>
+      <c r="V8" s="9">
+        <v>5.2321456818327195E-4</v>
+      </c>
+      <c r="W8" s="9">
+        <v>1.0452161687904899E-3</v>
+      </c>
+      <c r="X8" s="9">
+        <v>2.74007488678172E-7</v>
+      </c>
+      <c r="Y8" s="9">
+        <v>37.516537901757502</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>53</v>
+      </c>
+      <c r="AC8" s="14"/>
+      <c r="AD8" s="8">
+        <v>1.19009514162097</v>
+      </c>
+      <c r="AE8" s="8">
+        <v>1.97451873717108</v>
+      </c>
+      <c r="AF8" s="8">
+        <v>-2.6613256026660701</v>
+      </c>
+      <c r="AG8" s="8">
+        <v>-5.2681233820115901E-4</v>
+      </c>
+      <c r="AH8" s="8">
+        <v>-6.6648957720028196E-4</v>
+      </c>
+      <c r="AI8" s="8">
+        <v>-0.100000072683692</v>
+      </c>
+      <c r="AJ8" s="8">
+        <v>1.9170691162750901E-5</v>
+      </c>
+      <c r="AK8" s="8">
+        <v>2.18514924938961E-5</v>
+      </c>
+      <c r="AL8" s="8">
+        <v>9.6067318544612507E-9</v>
+      </c>
+      <c r="AM8" s="8">
+        <v>172.75464347319601</v>
+      </c>
+      <c r="AN8" s="8">
+        <v>2.1146786588108199E-4</v>
+      </c>
+      <c r="AO8" s="8">
+        <v>3.0704779644408198E-4</v>
+      </c>
+      <c r="AQ8" s="2">
+        <v>2</v>
+      </c>
+      <c r="AR8" s="13"/>
+      <c r="AS8" s="8">
+        <v>1.0000000655286501</v>
+      </c>
+      <c r="AT8" s="8">
+        <v>0.99999994478920295</v>
+      </c>
+      <c r="AU8" s="8">
+        <v>1.46209541822759E-12</v>
+      </c>
+      <c r="AV8" s="8">
+        <v>1.00250622393692</v>
+      </c>
+      <c r="AW8" s="8">
+        <v>0.19201315090238499</v>
+      </c>
+      <c r="AX8" s="8">
+        <v>0.19302420938241199</v>
+      </c>
+      <c r="AY8" s="8">
+        <v>3.6971274794262599E-2</v>
+      </c>
+      <c r="AZ8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BA8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BB8" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="BC8" s="8">
+        <v>0.505</v>
+      </c>
+      <c r="BD8" s="8">
+        <v>2.4278946767708401E-5</v>
+      </c>
+      <c r="BE8" s="8">
+        <v>-2.4147889465808699E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>1</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.28281879270070898</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.18208641359160499</v>
+      </c>
+      <c r="E9" s="4">
+        <v>1.5290501042012901</v>
+      </c>
+      <c r="F9" s="4">
+        <v>-18.711945020888901</v>
+      </c>
+      <c r="G9" s="4">
+        <v>20.146308275428702</v>
+      </c>
+      <c r="H9" s="4">
+        <v>2.4937715662246502E-3</v>
+      </c>
+      <c r="I9" s="4">
+        <v>5626.2828187926998</v>
+      </c>
+      <c r="J9" s="4">
+        <v>5598.2179135863998</v>
+      </c>
+      <c r="K9" s="4">
+        <v>12630378663.4709</v>
+      </c>
+      <c r="L9" s="4">
+        <v>100.111483698109</v>
+      </c>
+      <c r="N9" s="10">
+        <v>49</v>
+      </c>
+      <c r="O9" s="21"/>
+      <c r="P9" s="9">
+        <v>0.99999809000305095</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0.99999617247741202</v>
+      </c>
+      <c r="R9" s="9">
+        <v>3.6537619555389398E-12</v>
+      </c>
+      <c r="S9" s="9">
+        <v>8.0513427237143501E-7</v>
+      </c>
+      <c r="T9" s="9">
+        <v>1.50743380986373E-6</v>
+      </c>
+      <c r="U9" s="9">
+        <v>9.9844004789870189E-4</v>
+      </c>
+      <c r="V9" s="9">
+        <v>1.20818052906646E-6</v>
+      </c>
+      <c r="W9" s="9">
+        <v>6.0479141061886502E-7</v>
+      </c>
+      <c r="X9" s="9">
+        <v>9.1413003886117599E-10</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>16.892969539981301</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>54</v>
+      </c>
+      <c r="AC9" s="14"/>
+      <c r="AD9" s="8">
+        <v>1.1900169429141101</v>
+      </c>
+      <c r="AE9" s="8">
+        <v>1.9744198051239401</v>
+      </c>
+      <c r="AF9" s="8">
+        <v>-2.6613256266033098</v>
+      </c>
+      <c r="AG9" s="8">
+        <v>-2.27207239487404E-4</v>
+      </c>
+      <c r="AH9" s="8">
+        <v>-2.96601104184398E-5</v>
+      </c>
+      <c r="AI9" s="8">
+        <v>0.14843750078125001</v>
+      </c>
+      <c r="AJ9" s="8">
+        <v>7.81987068632084E-5</v>
+      </c>
+      <c r="AK9" s="8">
+        <v>9.8932047136290796E-5</v>
+      </c>
+      <c r="AL9" s="8">
+        <v>2.3937232196402601E-8</v>
+      </c>
+      <c r="AM9" s="8">
+        <v>128.51555037534999</v>
+      </c>
+      <c r="AN9" s="8">
+        <v>1.3013537842176899E-4</v>
+      </c>
+      <c r="AO9" s="8">
+        <v>-9.3149055100716306E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>2</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="4">
+        <v>0.236082980534878</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.232404757213514</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.58492214530865705</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0.76326257696009203</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.766788844270198</v>
+      </c>
+      <c r="H10" s="4">
+        <v>2.4976458681156802E-3</v>
+      </c>
+      <c r="I10" s="4">
+        <v>4.6735812165831198E-2</v>
+      </c>
+      <c r="J10" s="4">
+        <v>5.0318343621909303E-2</v>
+      </c>
+      <c r="K10" s="4">
+        <v>0.94412795889263401</v>
+      </c>
+      <c r="L10" s="4">
+        <v>0.58188311211999599</v>
+      </c>
+      <c r="AQ10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AT10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AU10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AZ10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="BA10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="BB10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BD10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="BE10" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>3</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="4">
+        <v>0.72477003623153002</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.68621042101424401</v>
+      </c>
+      <c r="E11" s="4">
+        <v>0.22443592552650601</v>
+      </c>
+      <c r="F11" s="4">
+        <v>67.913712641208406</v>
+      </c>
+      <c r="G11" s="4">
+        <v>77.428400229152402</v>
+      </c>
+      <c r="H11" s="4">
+        <v>0.61688160852686202</v>
+      </c>
+      <c r="I11" s="4">
+        <v>0.488687055696652</v>
+      </c>
+      <c r="J11" s="4">
+        <v>0.45380566380073001</v>
+      </c>
+      <c r="K11" s="4">
+        <v>0.36048621978215001</v>
+      </c>
+      <c r="L11" s="4">
+        <v>5.3108743866407604</v>
+      </c>
+      <c r="N11" s="2">
+        <v>1</v>
+      </c>
+      <c r="O11" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="P11" s="8">
+        <v>-161.41646514750599</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>-248.68411656856901</v>
+      </c>
+      <c r="R11" s="3">
+        <v>69189854060.861099</v>
+      </c>
+      <c r="S11" s="3">
+        <v>1267660893.1593101</v>
+      </c>
+      <c r="T11" s="3">
+        <v>6103641.6779909804</v>
+      </c>
+      <c r="U11" s="8">
+        <v>6.2252902798354596E-8</v>
+      </c>
+      <c r="V11" s="8">
+        <v>416.91646514750602</v>
+      </c>
+      <c r="W11" s="8">
+        <v>0.815883431430108</v>
+      </c>
+      <c r="X11" s="3">
+        <v>360225024215.638</v>
+      </c>
+      <c r="Y11" s="8">
+        <v>123.262760294557</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AL11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="AO11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="AQ11" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR11" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="AS11" s="8">
+        <v>0.16126198025543501</v>
+      </c>
+      <c r="AT11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU11" s="8">
+        <v>0.771109685344183</v>
+      </c>
+      <c r="AV11" s="8">
+        <v>8.0630990127717503E-2</v>
+      </c>
+      <c r="AW11" s="8">
+        <v>0.16126198025543501</v>
+      </c>
+      <c r="AX11" s="8">
+        <v>0</v>
+      </c>
+      <c r="AY11" s="8">
+        <v>0.228890314655816</v>
+      </c>
+      <c r="AZ11" s="8">
+        <v>0.88997432880677496</v>
+      </c>
+      <c r="BA11" s="8">
+        <v>0.31122070310084898</v>
+      </c>
+      <c r="BB11" s="8">
+        <v>0.31122070310084898</v>
+      </c>
+      <c r="BC11" s="8">
+        <v>0.11967520862938499</v>
+      </c>
+      <c r="BD11" s="8">
+        <v>-1.42403350866793E-6</v>
+      </c>
+      <c r="BE11" s="8">
+        <v>-5.2010852551808604</v>
+      </c>
+    </row>
+    <row r="12" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>4</v>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="4">
+        <v>1.0000009877001601</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1.0000011333310399</v>
+      </c>
+      <c r="E12" s="5">
+        <v>3.0963871550969701E-12</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2.7151749400963398E-5</v>
+      </c>
+      <c r="G12" s="5">
+        <v>-2.9125069195548E-5</v>
+      </c>
+      <c r="H12" s="4">
+        <v>4.0526565367245996E-3</v>
+      </c>
+      <c r="I12" s="4">
+        <v>0.27523095146863003</v>
+      </c>
+      <c r="J12" s="4">
+        <v>0.313790712316803</v>
+      </c>
+      <c r="K12" s="4">
+        <v>0.22443592552340999</v>
+      </c>
+      <c r="L12" s="4">
+        <v>92.008230562653296</v>
+      </c>
+      <c r="N12" s="2">
+        <v>2</v>
+      </c>
+      <c r="O12" s="17"/>
+      <c r="P12" s="8">
+        <v>11.947201283894101</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>-247.849390416181</v>
+      </c>
+      <c r="R12" s="3">
+        <v>15255784.761618201</v>
+      </c>
+      <c r="S12" s="3">
+        <v>-1865047.09142735</v>
+      </c>
+      <c r="T12" s="3">
+        <v>78124.387296172106</v>
+      </c>
+      <c r="U12" s="8">
+        <v>1.3675870839506301E-7</v>
+      </c>
+      <c r="V12" s="8">
+        <v>173.36366643139999</v>
+      </c>
+      <c r="W12" s="8">
+        <v>0.83472615238832704</v>
+      </c>
+      <c r="X12" s="3">
+        <v>69174598276.099503</v>
+      </c>
+      <c r="Y12" s="8">
+        <v>95.1583624922703</v>
+      </c>
+      <c r="AB12" s="2">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD12" s="8">
+        <v>1.92573714625681</v>
+      </c>
+      <c r="AE12" s="8">
+        <v>-4.7915034410233597</v>
+      </c>
+      <c r="AF12" s="8">
+        <v>-0.248219289520268</v>
+      </c>
+      <c r="AG12" s="8">
+        <v>1.22628285959304E-2</v>
+      </c>
+      <c r="AH12" s="8">
+        <v>8.4436339650737602E-2</v>
+      </c>
+      <c r="AI12" s="8">
+        <v>-12.8000000726837</v>
+      </c>
+      <c r="AJ12" s="8">
+        <v>0.46298277384419101</v>
+      </c>
+      <c r="AK12" s="8">
+        <v>3.2184052820921898</v>
+      </c>
+      <c r="AL12" s="8">
+        <v>0.45483331514571101</v>
+      </c>
+      <c r="AM12" s="8">
+        <v>149.84109112464901</v>
+      </c>
+      <c r="AN12" s="8">
+        <v>-9.7145490663121808E-3</v>
+      </c>
+      <c r="AO12" s="8">
+        <v>-6.6722081665988295E-2</v>
+      </c>
+      <c r="AQ12" s="2">
+        <v>2</v>
+      </c>
+      <c r="AR12" s="15"/>
+      <c r="AS12" s="8">
+        <v>0.29283632719854802</v>
+      </c>
+      <c r="AT12" s="8">
+        <v>5.0594919126046002E-2</v>
+      </c>
+      <c r="AU12" s="8">
+        <v>0.62369033051615597</v>
+      </c>
+      <c r="AV12" s="8">
+        <v>8.1284629560217397E-2</v>
+      </c>
+      <c r="AW12" s="8">
+        <v>0.13157434694311301</v>
+      </c>
+      <c r="AX12" s="8">
+        <v>5.0594919126046002E-2</v>
+      </c>
+      <c r="AY12" s="8">
+        <v>0.14741935482802601</v>
+      </c>
+      <c r="AZ12" s="8">
+        <v>7.4122938708285693E-2</v>
+      </c>
+      <c r="BA12" s="8">
+        <v>3.7610265869870603E-2</v>
+      </c>
+      <c r="BB12" s="8">
+        <v>3.7610265869870603E-2</v>
+      </c>
+      <c r="BC12" s="8">
+        <v>2.7915027461231701E-2</v>
+      </c>
+      <c r="BD12" s="8">
+        <v>2.7039113792706702</v>
+      </c>
+      <c r="BE12" s="8">
+        <v>-7.0316390802178903</v>
+      </c>
+    </row>
+    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="N13" s="2">
+        <v>3</v>
+      </c>
+      <c r="O13" s="17"/>
+      <c r="P13" s="8">
+        <v>9.9560154431959005E-3</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>-247.34981294340301</v>
+      </c>
+      <c r="R13" s="3">
+        <v>6118198.8800754296</v>
+      </c>
+      <c r="S13" s="3">
+        <v>-2292.3948498974</v>
+      </c>
+      <c r="T13" s="3">
+        <v>49524.778165331198</v>
+      </c>
+      <c r="U13" s="8">
+        <v>6.3952463785186396E-6</v>
+      </c>
+      <c r="V13" s="8">
+        <v>11.9372452684509</v>
+      </c>
+      <c r="W13" s="8">
+        <v>0.49957747277784298</v>
+      </c>
+      <c r="X13" s="3">
+        <v>9137585.8815428093</v>
+      </c>
+      <c r="Y13" s="8">
+        <v>177.352100170911</v>
+      </c>
+      <c r="AB13" s="2">
+        <v>2</v>
+      </c>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="8">
+        <v>2.8818894698056501</v>
+      </c>
+      <c r="AE13" s="8">
+        <v>1.79213276635249</v>
+      </c>
+      <c r="AF13" s="8">
+        <v>-1.9705013471487001</v>
+      </c>
+      <c r="AG13" s="8">
+        <v>0.159688896609986</v>
+      </c>
+      <c r="AH13" s="8">
+        <v>4.4960425823261696</v>
+      </c>
+      <c r="AI13" s="8">
+        <v>77.971596525955405</v>
+      </c>
+      <c r="AJ13" s="8">
+        <v>0.95615232354883795</v>
+      </c>
+      <c r="AK13" s="8">
+        <v>6.5836362073758501</v>
+      </c>
+      <c r="AL13" s="8">
+        <v>1.7222820576284299</v>
+      </c>
+      <c r="AM13" s="8">
+        <v>56.090001182434598</v>
+      </c>
+      <c r="AN13" s="8">
+        <v>0.48308934719546998</v>
+      </c>
+      <c r="AO13" s="8">
+        <v>-7.0159786241621405E-2</v>
+      </c>
+      <c r="AQ13" s="2">
+        <v>3</v>
+      </c>
+      <c r="AR13" s="15"/>
+      <c r="AS13" s="8">
+        <v>0.344615765395275</v>
+      </c>
+      <c r="AT13" s="8">
+        <v>0.12707844888374101</v>
+      </c>
+      <c r="AU13" s="8">
+        <v>0.43644811129668998</v>
+      </c>
+      <c r="AV13" s="8">
+        <v>0.80854891101148096</v>
+      </c>
+      <c r="AW13" s="8">
+        <v>5.1779438196726903E-2</v>
+      </c>
+      <c r="AX13" s="8">
+        <v>7.6483529757695096E-2</v>
+      </c>
+      <c r="AY13" s="8">
+        <v>0.18724221921946599</v>
+      </c>
+      <c r="AZ13" s="8">
+        <v>3.7154534991116699E-2</v>
+      </c>
+      <c r="BA13" s="8">
+        <v>2.8008935996947398E-2</v>
+      </c>
+      <c r="BB13" s="8">
+        <v>2.8008935996947398E-2</v>
+      </c>
+      <c r="BC13" s="8">
+        <v>2.54213970617705E-2</v>
+      </c>
+      <c r="BD13" s="8">
+        <v>-2.4574323700191201</v>
+      </c>
+      <c r="BE13" s="8">
+        <v>1.6636846249538899</v>
+      </c>
+    </row>
+    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="N14" s="2">
+        <v>1596</v>
+      </c>
+      <c r="O14" s="17"/>
+      <c r="P14" s="8">
+        <v>0.99998698008290499</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0.99996318463170997</v>
+      </c>
+      <c r="R14" s="8">
+        <v>1.17810970885547E-8</v>
+      </c>
+      <c r="S14" s="8">
+        <v>1.1970003524803499E-2</v>
+      </c>
+      <c r="T14" s="8">
+        <v>3.4466617718447799E-2</v>
+      </c>
+      <c r="U14" s="8">
+        <v>2.4408269429015501</v>
+      </c>
+      <c r="V14" s="8">
+        <v>6.9746978865225997E-4</v>
+      </c>
+      <c r="W14" s="8">
+        <v>1.3864905228369001E-3</v>
+      </c>
+      <c r="X14" s="3">
+        <v>4.9381613684022399E-7</v>
+      </c>
+      <c r="Y14" s="8">
+        <v>25.848942495508101</v>
+      </c>
+      <c r="AB14" s="2">
+        <v>3</v>
+      </c>
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="8">
+        <v>2.8818895049183602</v>
+      </c>
+      <c r="AE14" s="8">
+        <v>1.79213276125301</v>
+      </c>
+      <c r="AF14" s="8">
+        <v>-1.97050132982834</v>
+      </c>
+      <c r="AG14" s="8">
+        <v>-0.96617868700134801</v>
+      </c>
+      <c r="AH14" s="8">
+        <v>0.140319569541904</v>
+      </c>
+      <c r="AI14" s="8">
+        <v>-7.2683691978454604E-8</v>
+      </c>
+      <c r="AJ14" s="8">
+        <v>3.5112717178265003E-8</v>
+      </c>
+      <c r="AK14" s="8">
+        <v>5.0994723999053804E-9</v>
+      </c>
+      <c r="AL14" s="8">
+        <v>1.7320357814654101E-8</v>
+      </c>
+      <c r="AM14" s="8">
+        <v>139.86078127751</v>
+      </c>
+      <c r="AN14" s="8">
+        <v>0.48308934490941102</v>
+      </c>
+      <c r="AO14" s="8">
+        <v>-7.0159784041477102E-2</v>
+      </c>
+      <c r="AQ14" s="2">
+        <v>4</v>
+      </c>
+      <c r="AR14" s="15"/>
+      <c r="AS14" s="8">
+        <v>0.46111377455341201</v>
+      </c>
+      <c r="AT14" s="8">
+        <v>0.19622898068071301</v>
+      </c>
+      <c r="AU14" s="8">
+        <v>0.31728430319624201</v>
+      </c>
+      <c r="AV14" s="8">
+        <v>2.60582764898763</v>
+      </c>
+      <c r="AW14" s="8">
+        <v>0.116498009158137</v>
+      </c>
+      <c r="AX14" s="8">
+        <v>6.9150531796972503E-2</v>
+      </c>
+      <c r="AY14" s="8">
+        <v>0.11916380810044799</v>
+      </c>
+      <c r="AZ14" s="8">
+        <v>0.20753532885734099</v>
+      </c>
+      <c r="BA14" s="8">
+        <v>0.16133445399034901</v>
+      </c>
+      <c r="BB14" s="8">
+        <v>0.16133445399034901</v>
+      </c>
+      <c r="BC14" s="8">
+        <v>0.12975060779526101</v>
+      </c>
+      <c r="BD14" s="8">
+        <v>1.9465681055337201</v>
+      </c>
+      <c r="BE14" s="8">
+        <v>-3.2793864804363801</v>
+      </c>
+    </row>
+    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="N15" s="2">
+        <v>1597</v>
+      </c>
+      <c r="O15" s="18"/>
+      <c r="P15" s="8">
+        <v>0.99998270258053601</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>0.99996533641051799</v>
+      </c>
+      <c r="R15" s="8">
+        <v>2.9967750697401302E-10</v>
+      </c>
+      <c r="S15" s="8">
+        <v>6.9308252610428597E-6</v>
+      </c>
+      <c r="T15" s="8">
+        <v>1.38323815126714E-5</v>
+      </c>
+      <c r="U15" s="8">
+        <v>9.9844004789870189E-4</v>
+      </c>
+      <c r="V15" s="8">
+        <v>4.2775023695318297E-6</v>
+      </c>
+      <c r="W15" s="8">
+        <v>2.15177880735772E-6</v>
+      </c>
+      <c r="X15" s="3">
+        <v>1.14814195815807E-8</v>
+      </c>
+      <c r="Y15" s="8">
+        <v>18.3869722311921</v>
+      </c>
+      <c r="AB15" s="2">
+        <v>12</v>
+      </c>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="8">
+        <v>1.1899145223262799</v>
+      </c>
+      <c r="AE15" s="8">
+        <v>1.97451551144384</v>
+      </c>
+      <c r="AF15" s="8">
+        <v>-2.6613256263443801</v>
+      </c>
+      <c r="AG15" s="8">
+        <v>-2.4545312918516102E-4</v>
+      </c>
+      <c r="AH15" s="8">
+        <v>-2.5111820135399E-4</v>
+      </c>
+      <c r="AI15" s="8">
+        <v>0.50625001171874895</v>
+      </c>
+      <c r="AJ15" s="8">
+        <v>7.7799967332548004E-4</v>
+      </c>
+      <c r="AK15" s="8">
+        <v>1.12795575732516E-4</v>
+      </c>
+      <c r="AL15" s="8">
+        <v>3.0501500791757502E-7</v>
+      </c>
+      <c r="AM15" s="8">
+        <v>166.72831186232</v>
+      </c>
+      <c r="AN15" s="8">
+        <v>4.0220025906395597E-5</v>
+      </c>
+      <c r="AO15" s="8">
+        <v>2.8087320876259099E-4</v>
+      </c>
+      <c r="AQ15" s="2">
+        <v>5</v>
+      </c>
+      <c r="AR15" s="15"/>
+      <c r="AS15" s="8">
+        <v>0.53849589576151302</v>
+      </c>
+      <c r="AT15" s="8">
+        <v>0.26517213061389</v>
+      </c>
+      <c r="AU15" s="8">
+        <v>0.274518309201981</v>
+      </c>
+      <c r="AV15" s="8">
+        <v>0.61858004287124502</v>
+      </c>
+      <c r="AW15" s="8">
+        <v>7.7382121208100701E-2</v>
+      </c>
+      <c r="AX15" s="8">
+        <v>6.89431499331771E-2</v>
+      </c>
+      <c r="AY15" s="8">
+        <v>4.2765993994261099E-2</v>
+      </c>
+      <c r="AZ15" s="8">
+        <v>8.3779441707349106E-2</v>
+      </c>
+      <c r="BA15" s="8">
+        <v>7.7210423344994603E-2</v>
+      </c>
+      <c r="BB15" s="8">
+        <v>7.7210423344994603E-2</v>
+      </c>
+      <c r="BC15" s="8">
+        <v>7.2566641076624805E-2</v>
+      </c>
+      <c r="BD15" s="8">
+        <v>4.4200986624685896</v>
+      </c>
+      <c r="BE15" s="8">
+        <v>-4.9611398276207899</v>
+      </c>
+    </row>
+    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="AB16" s="2">
+        <v>13</v>
+      </c>
+      <c r="AC16" s="17"/>
+      <c r="AD16" s="8">
+        <v>1.1899145223292</v>
+      </c>
+      <c r="AE16" s="8">
+        <v>1.9745155114642601</v>
+      </c>
+      <c r="AF16" s="8">
+        <v>-2.6613256263443699</v>
+      </c>
+      <c r="AG16" s="8">
+        <v>-8.0440079160217805E-5</v>
+      </c>
+      <c r="AH16" s="8">
+        <v>-5.61746660276466E-4</v>
+      </c>
+      <c r="AI16" s="8">
+        <v>-7.2683691978454604E-8</v>
+      </c>
+      <c r="AJ16" s="8">
+        <v>2.9234392684429602E-12</v>
+      </c>
+      <c r="AK16" s="8">
+        <v>2.04150030214123E-11</v>
+      </c>
+      <c r="AL16" s="8">
+        <v>5.3290705182007498E-15</v>
+      </c>
+      <c r="AM16" s="8">
+        <v>157.07446020764601</v>
+      </c>
+      <c r="AN16" s="8">
+        <v>4.0220030179061098E-5</v>
+      </c>
+      <c r="AO16" s="8">
+        <v>2.8087329037319799E-4</v>
+      </c>
+      <c r="AQ16" s="2">
+        <v>6</v>
+      </c>
+      <c r="AR16" s="15"/>
+      <c r="AS16" s="8">
+        <v>0.66587897628147696</v>
+      </c>
+      <c r="AT16" s="8">
+        <v>0.45252777190817001</v>
+      </c>
+      <c r="AU16" s="8">
+        <v>0.11997795588769999</v>
+      </c>
+      <c r="AV16" s="8">
+        <v>9.9999999377470896</v>
+      </c>
+      <c r="AW16" s="8">
+        <v>0.127383080519963</v>
+      </c>
+      <c r="AX16" s="8">
+        <v>0.18735564129428001</v>
+      </c>
+      <c r="AY16" s="8">
+        <v>0.15454035331428001</v>
+      </c>
+      <c r="AZ16" s="8">
+        <v>0.55929292117285501</v>
+      </c>
+      <c r="BA16" s="8">
+        <v>0.63847247357372705</v>
+      </c>
+      <c r="BB16" s="8">
+        <v>0.63847247357372705</v>
+      </c>
+      <c r="BC16" s="8">
+        <v>0.73504016208185097</v>
+      </c>
+      <c r="BD16" s="8">
+        <v>-3.1008206971229701</v>
+      </c>
+      <c r="BE16" s="8">
+        <v>1.82659217090046</v>
+      </c>
+    </row>
+    <row r="17" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AB17" s="2">
+        <v>14</v>
+      </c>
+      <c r="AC17" s="18"/>
+      <c r="AD17" s="8">
+        <v>1.18990459300586</v>
+      </c>
+      <c r="AE17" s="8">
+        <v>1.97444617085342</v>
+      </c>
+      <c r="AF17" s="8">
+        <v>-2.6613256365372302</v>
+      </c>
+      <c r="AG17" s="8">
+        <v>-2.63801092976428E-5</v>
+      </c>
+      <c r="AH17" s="8">
+        <v>-8.3863187477465003E-6</v>
+      </c>
+      <c r="AI17" s="8">
+        <v>0.12343751328124999</v>
+      </c>
+      <c r="AJ17" s="8">
+        <v>9.9293233397634799E-6</v>
+      </c>
+      <c r="AK17" s="8">
+        <v>6.9340610838519696E-5</v>
+      </c>
+      <c r="AL17" s="8">
+        <v>1.0192859445368099E-8</v>
+      </c>
+      <c r="AM17" s="8">
+        <v>138.710988849122</v>
+      </c>
+      <c r="AN17" s="8">
+        <v>2.57063102705457E-5</v>
+      </c>
+      <c r="AO17" s="8">
+        <v>3.6808987988745601E-6</v>
+      </c>
+      <c r="AQ17" s="2">
+        <v>7</v>
+      </c>
+      <c r="AR17" s="15"/>
+      <c r="AS17" s="8">
+        <v>0.72887472331885494</v>
+      </c>
+      <c r="AT17" s="8">
+        <v>0.52319027400642304</v>
+      </c>
+      <c r="AU17" s="8">
+        <v>8.00183205156485E-2</v>
+      </c>
+      <c r="AV17" s="8">
+        <v>0.110900538273298</v>
+      </c>
+      <c r="AW17" s="8">
+        <v>6.2995747037377495E-2</v>
+      </c>
+      <c r="AX17" s="8">
+        <v>7.0662502098252603E-2</v>
+      </c>
+      <c r="AY17" s="8">
+        <v>3.9959635372052001E-2</v>
+      </c>
+      <c r="AZ17" s="8">
+        <v>0.12624893006114399</v>
+      </c>
+      <c r="BA17" s="8">
+        <v>0.161905843200462</v>
+      </c>
+      <c r="BB17" s="8">
+        <v>0.161905843200462</v>
+      </c>
+      <c r="BC17" s="8">
+        <v>0.21057669451986899</v>
+      </c>
+      <c r="BD17" s="8">
+        <v>1.8099996937140099</v>
+      </c>
+      <c r="BE17" s="8">
+        <v>-1.6136176573428</v>
+      </c>
+    </row>
+    <row r="18" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ18" s="2">
+        <v>8</v>
+      </c>
+      <c r="AR18" s="15"/>
+      <c r="AS18" s="8">
+        <v>0.79028554486773805</v>
+      </c>
+      <c r="AT18" s="8">
+        <v>0.61085282092075399</v>
+      </c>
+      <c r="AU18" s="8">
+        <v>6.2744827867420305E-2</v>
+      </c>
+      <c r="AV18" s="8">
+        <v>1.8755059472979001</v>
+      </c>
+      <c r="AW18" s="8">
+        <v>6.1410821548883603E-2</v>
+      </c>
+      <c r="AX18" s="8">
+        <v>8.7662546914330994E-2</v>
+      </c>
+      <c r="AY18" s="8">
+        <v>1.7273492648228202E-2</v>
+      </c>
+      <c r="AZ18" s="8">
+        <v>0.109669145456254</v>
+      </c>
+      <c r="BA18" s="8">
+        <v>0.15006767100881299</v>
+      </c>
+      <c r="BB18" s="8">
+        <v>0.15006767100881299</v>
+      </c>
+      <c r="BC18" s="8">
+        <v>0.20212409250006899</v>
+      </c>
+      <c r="BD18" s="8">
+        <v>3.9108368912598901</v>
+      </c>
+      <c r="BE18" s="8">
+        <v>-2.7396843012288099</v>
+      </c>
+    </row>
+    <row r="19" spans="28:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AQ19" s="2">
+        <v>9</v>
+      </c>
+      <c r="AR19" s="15"/>
+      <c r="AS19" s="8">
+        <v>0.79028554376212101</v>
+      </c>
+      <c r="AT19" s="8">
+        <v>0.61085281885806797</v>
+      </c>
+      <c r="AU19" s="8">
+        <v>6.2744829194640098E-2</v>
+      </c>
+      <c r="AV19" s="8">
+        <v>6.2252902798354596E-8</v>
+      </c>
+      <c r="AW19" s="8">
+        <v>1.1056175974744001E-9</v>
+      </c>
+      <c r="AX19" s="8">
+        <v>2.0626864660755398E-9</v>
+      </c>
+      <c r="AY19" s="8">
+        <v>1.32721986179085E-9</v>
+      </c>
+      <c r="AZ19" s="8">
+        <v>0.18088775521266801</v>
+      </c>
+      <c r="BA19" s="8">
+        <v>0.27971580570018501</v>
+      </c>
+      <c r="BB19" s="8">
+        <v>0.27971580570018501</v>
+      </c>
+      <c r="BC19" s="8">
+        <v>0.43813879268085398</v>
+      </c>
+      <c r="BD19" s="8">
+        <v>3.9108369826232301</v>
+      </c>
+      <c r="BE19" s="8">
+        <v>-2.7396843642646802</v>
+      </c>
+    </row>
+    <row r="20" spans="28:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AQ20" s="2">
+        <v>10</v>
+      </c>
+      <c r="AR20" s="15"/>
+      <c r="AS20" s="8">
+        <v>0.95785290430231196</v>
+      </c>
+      <c r="AT20" s="8">
+        <v>0.91361237959406305</v>
+      </c>
+      <c r="AU20" s="8">
+        <v>3.27391805469127E-3</v>
+      </c>
+      <c r="AV20" s="8">
+        <v>2.8444397929800398</v>
+      </c>
+      <c r="AW20" s="8">
+        <v>0.16756736054019</v>
+      </c>
+      <c r="AX20" s="8">
+        <v>0.30275956073599503</v>
+      </c>
+      <c r="AY20" s="8">
+        <v>5.9470911139948797E-2</v>
+      </c>
+      <c r="AZ20" s="8">
+        <v>0.23188045599516699</v>
+      </c>
+      <c r="BA20" s="8">
+        <v>0.38161793760955998</v>
+      </c>
+      <c r="BB20" s="8">
+        <v>0.38161793760955998</v>
+      </c>
+      <c r="BC20" s="8">
+        <v>0.64177665316537502</v>
+      </c>
+      <c r="BD20" s="8">
+        <v>1.3983880380329601</v>
+      </c>
+      <c r="BE20" s="8">
+        <v>-0.77396133726206295</v>
+      </c>
+    </row>
+    <row r="21" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ21" s="2">
+        <v>11</v>
+      </c>
+      <c r="AR21" s="15"/>
+      <c r="AS21" s="8">
+        <v>0.95292153181586203</v>
+      </c>
+      <c r="AT21" s="8">
+        <v>0.907309446222622</v>
+      </c>
+      <c r="AU21" s="8">
+        <v>2.2726321029149401E-3</v>
+      </c>
+      <c r="AV21" s="8">
+        <v>0.170627893812483</v>
+      </c>
+      <c r="AW21" s="8">
+        <v>4.9313724864492496E-3</v>
+      </c>
+      <c r="AX21" s="8">
+        <v>6.3029333714408296E-3</v>
+      </c>
+      <c r="AY21" s="8">
+        <v>1.00128595177633E-3</v>
+      </c>
+      <c r="AZ21" s="8">
+        <v>0.10703339767192099</v>
+      </c>
+      <c r="BA21" s="8">
+        <v>0.19908678874796901</v>
+      </c>
+      <c r="BB21" s="8">
+        <v>0.19908678874796901</v>
+      </c>
+      <c r="BC21" s="8">
+        <v>0.37490916944406599</v>
+      </c>
+      <c r="BD21" s="8">
+        <v>0.19171936143419599</v>
+      </c>
+      <c r="BE21" s="8">
+        <v>-0.149999915133469</v>
+      </c>
+    </row>
+    <row r="22" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ22" s="2">
+        <v>12</v>
+      </c>
+      <c r="AR22" s="15"/>
+      <c r="AS22" s="8">
+        <v>0.99337845476188302</v>
+      </c>
+      <c r="AT22" s="8">
+        <v>0.98554842130953202</v>
+      </c>
+      <c r="AU22" s="8">
+        <v>2.00678674558399E-4</v>
+      </c>
+      <c r="AV22" s="8">
+        <v>4.3303584713443204</v>
+      </c>
+      <c r="AW22" s="8">
+        <v>4.0456922946021101E-2</v>
+      </c>
+      <c r="AX22" s="8">
+        <v>7.8238975086909898E-2</v>
+      </c>
+      <c r="AY22" s="8">
+        <v>2.07195342835655E-3</v>
+      </c>
+      <c r="AZ22" s="8">
+        <v>0.41735185896767102</v>
+      </c>
+      <c r="BA22" s="8">
+        <v>0.81303253215830495</v>
+      </c>
+      <c r="BB22" s="8">
+        <v>0.81303253215830495</v>
+      </c>
+      <c r="BC22" s="8">
+        <v>1.5895625751028299</v>
+      </c>
+      <c r="BD22" s="8">
+        <v>0.48437318770862797</v>
+      </c>
+      <c r="BE22" s="8">
+        <v>-0.25046661511505203</v>
+      </c>
+    </row>
+    <row r="23" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ23" s="2">
+        <v>13</v>
+      </c>
+      <c r="AR23" s="15"/>
+      <c r="AS23" s="8">
+        <v>0.99479366199113395</v>
+      </c>
+      <c r="AT23" s="8">
+        <v>0.989670816084538</v>
+      </c>
+      <c r="AU23" s="8">
+        <v>2.7423895217741501E-5</v>
+      </c>
+      <c r="AV23" s="8">
+        <v>0.95399340775034602</v>
+      </c>
+      <c r="AW23" s="8">
+        <v>1.41520722925025E-3</v>
+      </c>
+      <c r="AX23" s="8">
+        <v>4.1223947750053096E-3</v>
+      </c>
+      <c r="AY23" s="8">
+        <v>1.73254779340657E-4</v>
+      </c>
+      <c r="AZ23" s="8">
+        <v>0.118181393953846</v>
+      </c>
+      <c r="BA23" s="8">
+        <v>0.23894097767806299</v>
+      </c>
+      <c r="BB23" s="8">
+        <v>0.23894097767806299</v>
+      </c>
+      <c r="BC23" s="8">
+        <v>0.48791267490191798</v>
+      </c>
+      <c r="BD23" s="8">
+        <v>-3.2849708605002699E-2</v>
+      </c>
+      <c r="BE23" s="8">
+        <v>1.1277229361494801E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ24" s="2">
+        <v>14</v>
+      </c>
+      <c r="AR24" s="15"/>
+      <c r="AS24" s="8">
+        <v>0.99990757024690202</v>
+      </c>
+      <c r="AT24" s="8">
+        <v>0.99977623134446403</v>
+      </c>
+      <c r="AU24" s="8">
+        <v>1.60001938983331E-7</v>
+      </c>
+      <c r="AV24" s="8">
+        <v>4.3059698899519097</v>
+      </c>
+      <c r="AW24" s="8">
+        <v>5.1139082557683999E-3</v>
+      </c>
+      <c r="AX24" s="8">
+        <v>1.0105415259926699E-2</v>
+      </c>
+      <c r="AY24" s="8">
+        <v>2.72638932787582E-5</v>
+      </c>
+      <c r="AZ24" s="8">
+        <v>0.50064469720632898</v>
+      </c>
+      <c r="BA24" s="8">
+        <v>0.99851325832349602</v>
+      </c>
+      <c r="BB24" s="8">
+        <v>0.99851325832349602</v>
+      </c>
+      <c r="BC24" s="8">
+        <v>1.99642354279041</v>
+      </c>
+      <c r="BD24" s="8">
+        <v>1.5380778672453001E-2</v>
+      </c>
+      <c r="BE24" s="8">
+        <v>-7.7835385198676797E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ25" s="2">
+        <v>15</v>
+      </c>
+      <c r="AR25" s="15"/>
+      <c r="AS25" s="8">
+        <v>0.99998158963223704</v>
+      </c>
+      <c r="AT25" s="8">
+        <v>0.99996352669438304</v>
+      </c>
+      <c r="AU25" s="8">
+        <v>3.50988855027479E-10</v>
+      </c>
+      <c r="AV25" s="8">
+        <v>1.0329084669222599</v>
+      </c>
+      <c r="AW25" s="8">
+        <v>7.4019385335355405E-5</v>
+      </c>
+      <c r="AX25" s="8">
+        <v>1.87295349918792E-4</v>
+      </c>
+      <c r="AY25" s="8">
+        <v>1.59650950128303E-7</v>
+      </c>
+      <c r="AZ25" s="8">
+        <v>0.54720119733947903</v>
+      </c>
+      <c r="BA25" s="8">
+        <v>1.0934121495159901</v>
+      </c>
+      <c r="BB25" s="8">
+        <v>1.0934121495159901</v>
+      </c>
+      <c r="BC25" s="8">
+        <v>2.1898616131739099</v>
+      </c>
+      <c r="BD25" s="8">
+        <v>-1.7565456601610101E-4</v>
+      </c>
+      <c r="BE25" s="8">
+        <v>6.9418193260339906E-5</v>
+      </c>
+    </row>
+    <row r="26" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR26" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS26" s="8">
+        <v>0.61984874343257301</v>
+      </c>
+      <c r="AT26" s="8">
+        <v>0.38250123192884899</v>
+      </c>
+      <c r="AU26" s="8">
+        <v>0.14480780964145701</v>
+      </c>
+      <c r="AV26" s="8">
+        <v>2.3499753614229998E-3</v>
+      </c>
+      <c r="AW26" s="8">
+        <v>0.119848743432573</v>
+      </c>
+      <c r="AX26" s="8">
+        <v>0.11749876807115001</v>
+      </c>
+      <c r="AY26" s="8">
+        <v>6.3551921903585402</v>
+      </c>
+      <c r="AZ26" s="8">
+        <v>0.49801295768084902</v>
+      </c>
+      <c r="BA26" s="8">
+        <v>0.49881503795585702</v>
+      </c>
+      <c r="BB26" s="8">
+        <v>0.49881503795585702</v>
+      </c>
+      <c r="BC26" s="8">
+        <v>0.50433692283891196</v>
+      </c>
+      <c r="BD26" s="8">
+        <v>-0.33602031130452698</v>
+      </c>
+      <c r="BE26" s="8">
+        <v>-0.34224656121810598</v>
+      </c>
+    </row>
+    <row r="27" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ27" s="2">
+        <v>2</v>
+      </c>
+      <c r="AR27" s="15"/>
+      <c r="AS27" s="8">
+        <v>0.655522854730612</v>
+      </c>
+      <c r="AT27" s="8">
+        <v>0.41840321180757301</v>
+      </c>
+      <c r="AU27" s="8">
+        <v>0.131449331377233</v>
+      </c>
+      <c r="AV27" s="8">
+        <v>0.10552591297496799</v>
+      </c>
+      <c r="AW27" s="8">
+        <v>3.5674111298039497E-2</v>
+      </c>
+      <c r="AX27" s="8">
+        <v>3.5901979878723497E-2</v>
+      </c>
+      <c r="AY27" s="8">
+        <v>1.33584782642237E-2</v>
+      </c>
+      <c r="AZ27" s="8">
+        <v>8.6093984700783999E-2</v>
+      </c>
+      <c r="BA27" s="8">
+        <v>9.8580830281777596E-2</v>
+      </c>
+      <c r="BB27" s="8">
+        <v>9.8580830281777596E-2</v>
+      </c>
+      <c r="BC27" s="8">
+        <v>0.115456022710404</v>
+      </c>
+      <c r="BD27" s="8">
+        <v>2.2758448089506902</v>
+      </c>
+      <c r="BE27" s="8">
+        <v>-2.2614002533198101</v>
+      </c>
+    </row>
+    <row r="28" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ28" s="2">
+        <v>3</v>
+      </c>
+      <c r="AR28" s="15"/>
+      <c r="AS28" s="8">
+        <v>0.75545537277409003</v>
+      </c>
+      <c r="AT28" s="8">
+        <v>0.55440599230987098</v>
+      </c>
+      <c r="AU28" s="8">
+        <v>8.6393338462521396E-2</v>
+      </c>
+      <c r="AV28" s="8">
+        <v>3.7020042231013601</v>
+      </c>
+      <c r="AW28" s="8">
+        <v>9.9932518043477303E-2</v>
+      </c>
+      <c r="AX28" s="8">
+        <v>0.136002780502298</v>
+      </c>
+      <c r="AY28" s="8">
+        <v>4.5055992914712302E-2</v>
+      </c>
+      <c r="AZ28" s="8">
+        <v>7.3043305387553201E-2</v>
+      </c>
+      <c r="BA28" s="8">
+        <v>5.8040122609748203E-2</v>
+      </c>
+      <c r="BB28" s="8">
+        <v>5.8040122609748203E-2</v>
+      </c>
+      <c r="BC28" s="8">
+        <v>-1.04798722037171E-2</v>
+      </c>
+      <c r="BD28" s="8">
+        <v>4.4385430586363297</v>
+      </c>
+      <c r="BE28" s="8">
+        <v>-3.2613655886736899</v>
+      </c>
+    </row>
+    <row r="29" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ29" s="2">
+        <v>4</v>
+      </c>
+      <c r="AR29" s="15"/>
+      <c r="AS29" s="8">
+        <v>0.75545536437519001</v>
+      </c>
+      <c r="AT29" s="8">
+        <v>0.55440597414495396</v>
+      </c>
+      <c r="AU29" s="8">
+        <v>8.6393360426078494E-2</v>
+      </c>
+      <c r="AV29" s="8">
+        <v>6.2252902798354596E-8</v>
+      </c>
+      <c r="AW29" s="8">
+        <v>8.3989000199124997E-9</v>
+      </c>
+      <c r="AX29" s="8">
+        <v>1.8164916348872801E-8</v>
+      </c>
+      <c r="AY29" s="8">
+        <v>2.1963557181314799E-8</v>
+      </c>
+      <c r="AZ29" s="8">
+        <v>0.170922891328777</v>
+      </c>
+      <c r="BA29" s="8">
+        <v>0.25474596210410899</v>
+      </c>
+      <c r="BB29" s="8">
+        <v>0.25474596210410899</v>
+      </c>
+      <c r="BC29" s="8">
+        <v>0.38483429794833202</v>
+      </c>
+      <c r="BD29" s="8">
+        <v>4.4385446414803003</v>
+      </c>
+      <c r="BE29" s="8">
+        <v>-3.26136668365932</v>
+      </c>
+    </row>
+    <row r="30" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ30" s="2">
+        <v>5</v>
+      </c>
+      <c r="AR30" s="15"/>
+      <c r="AS30" s="8">
+        <v>0.915370720424591</v>
+      </c>
+      <c r="AT30" s="8">
+        <v>0.83001460537619498</v>
+      </c>
+      <c r="AU30" s="8">
+        <v>1.3385668857156601E-2</v>
+      </c>
+      <c r="AV30" s="8">
+        <v>2.2157807414863799</v>
+      </c>
+      <c r="AW30" s="8">
+        <v>0.15991535604940099</v>
+      </c>
+      <c r="AX30" s="8">
+        <v>0.27560863123124102</v>
+      </c>
+      <c r="AY30" s="8">
+        <v>7.3007691568921895E-2</v>
+      </c>
+      <c r="AZ30" s="8">
+        <v>0.180064878043704</v>
+      </c>
+      <c r="BA30" s="8">
+        <v>0.278868719700406</v>
+      </c>
+      <c r="BB30" s="8">
+        <v>0.278868719700406</v>
+      </c>
+      <c r="BC30" s="8">
+        <v>0.448486483430031</v>
+      </c>
+      <c r="BD30" s="8">
+        <v>2.7192671378758</v>
+      </c>
+      <c r="BE30" s="8">
+        <v>-1.5777900868878501</v>
+      </c>
+    </row>
+    <row r="31" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ31" s="2">
+        <v>6</v>
+      </c>
+      <c r="AR31" s="15"/>
+      <c r="AS31" s="8">
+        <v>0.90698818162734796</v>
+      </c>
+      <c r="AT31" s="8">
+        <v>0.82145431089747301</v>
+      </c>
+      <c r="AU31" s="8">
+        <v>8.7888500808267593E-3</v>
+      </c>
+      <c r="AV31" s="8">
+        <v>0.168838711396884</v>
+      </c>
+      <c r="AW31" s="8">
+        <v>8.3825387972424805E-3</v>
+      </c>
+      <c r="AX31" s="8">
+        <v>8.5602944787225299E-3</v>
+      </c>
+      <c r="AY31" s="8">
+        <v>4.5968187763298796E-3</v>
+      </c>
+      <c r="AZ31" s="8">
+        <v>9.8294777903322E-2</v>
+      </c>
+      <c r="BA31" s="8">
+        <v>0.17522613326571501</v>
+      </c>
+      <c r="BB31" s="8">
+        <v>0.17522613326571501</v>
+      </c>
+      <c r="BC31" s="8">
+        <v>0.31712079224913398</v>
+      </c>
+      <c r="BD31" s="8">
+        <v>0.23962617600484001</v>
+      </c>
+      <c r="BE31" s="8">
+        <v>-0.23465014284222899</v>
+      </c>
+    </row>
+    <row r="32" spans="28:57" x14ac:dyDescent="0.25">
+      <c r="AQ32" s="2">
+        <v>7</v>
+      </c>
+      <c r="AR32" s="15"/>
+      <c r="AS32" s="8">
+        <v>0.97030032391341603</v>
+      </c>
+      <c r="AT32" s="8">
+        <v>0.93833817480242299</v>
+      </c>
+      <c r="AU32" s="8">
+        <v>1.87088632063289E-3</v>
+      </c>
+      <c r="AV32" s="8">
+        <v>3.6048929835575798</v>
+      </c>
+      <c r="AW32" s="8">
+        <v>6.3312142286067505E-2</v>
+      </c>
+      <c r="AX32" s="8">
+        <v>0.11688386390494999</v>
+      </c>
+      <c r="AY32" s="8">
+        <v>6.9179637601938697E-3</v>
+      </c>
+      <c r="AZ32" s="8">
+        <v>0.35480493399150198</v>
+      </c>
+      <c r="BA32" s="8">
+        <v>0.66864136431788601</v>
+      </c>
+      <c r="BB32" s="8">
+        <v>0.66864136431788601</v>
+      </c>
+      <c r="BC32" s="8">
+        <v>1.2662395092116401</v>
+      </c>
+      <c r="BD32" s="8">
+        <v>1.1610613887188399</v>
+      </c>
+      <c r="BE32" s="8">
+        <v>-0.62890875681131897</v>
+      </c>
+    </row>
+    <row r="33" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ33" s="2">
+        <v>8</v>
+      </c>
+      <c r="AR33" s="15"/>
+      <c r="AS33" s="8">
+        <v>0.97980724354348103</v>
+      </c>
+      <c r="AT33" s="8">
+        <v>0.96055711516374298</v>
+      </c>
+      <c r="AU33" s="8">
+        <v>4.36357145727451E-4</v>
+      </c>
+      <c r="AV33" s="8">
+        <v>1.11008977599795</v>
+      </c>
+      <c r="AW33" s="8">
+        <v>9.5069196300652196E-3</v>
+      </c>
+      <c r="AX33" s="8">
+        <v>2.22189403613192E-2</v>
+      </c>
+      <c r="AY33" s="8">
+        <v>1.4345291749054401E-3</v>
+      </c>
+      <c r="AZ33" s="8">
+        <v>-0.18252187421237101</v>
+      </c>
+      <c r="BA33" s="8">
+        <v>-0.33707152563500598</v>
+      </c>
+      <c r="BB33" s="8">
+        <v>-0.33707152563500598</v>
+      </c>
+      <c r="BC33" s="8">
+        <v>-0.61615013071421099</v>
+      </c>
+      <c r="BD33" s="8">
+        <v>-0.25001749231189402</v>
+      </c>
+      <c r="BE33" s="8">
+        <v>0.10697613269356999</v>
+      </c>
+    </row>
+    <row r="34" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ34" s="2">
+        <v>9</v>
+      </c>
+      <c r="AR34" s="15"/>
+      <c r="AS34" s="8">
+        <v>0.97980724294740595</v>
+      </c>
+      <c r="AT34" s="8">
+        <v>0.96055711402075294</v>
+      </c>
+      <c r="AU34" s="8">
+        <v>4.3635717248401401E-4</v>
+      </c>
+      <c r="AV34" s="8">
+        <v>6.2252902798354596E-8</v>
+      </c>
+      <c r="AW34" s="8">
+        <v>5.9607485614066005E-10</v>
+      </c>
+      <c r="AX34" s="8">
+        <v>1.14298936981782E-9</v>
+      </c>
+      <c r="AY34" s="8">
+        <v>2.6756563490434099E-11</v>
+      </c>
+      <c r="AZ34" s="8">
+        <v>0.55270085170804895</v>
+      </c>
+      <c r="BA34" s="8">
+        <v>1.0815540452374599</v>
+      </c>
+      <c r="BB34" s="8">
+        <v>1.0815540452374599</v>
+      </c>
+      <c r="BC34" s="8">
+        <v>2.1211136117983802</v>
+      </c>
+      <c r="BD34" s="8">
+        <v>-0.25001750320891702</v>
+      </c>
+      <c r="BE34" s="8">
+        <v>0.10697613771109001</v>
+      </c>
+    </row>
+    <row r="35" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ35" s="2">
+        <v>10</v>
+      </c>
+      <c r="AR35" s="15"/>
+      <c r="AS35" s="8">
+        <v>0.998321853102348</v>
+      </c>
+      <c r="AT35" s="8">
+        <v>0.99637593645853395</v>
+      </c>
+      <c r="AU35" s="8">
+        <v>1.01378511920041E-5</v>
+      </c>
+      <c r="AV35" s="8">
+        <v>0.82344202550381895</v>
+      </c>
+      <c r="AW35" s="8">
+        <v>1.85146101549419E-2</v>
+      </c>
+      <c r="AX35" s="8">
+        <v>3.5818822437781103E-2</v>
+      </c>
+      <c r="AY35" s="8">
+        <v>4.2621932129201001E-4</v>
+      </c>
+      <c r="AZ35" s="8">
+        <v>0.49379189366085502</v>
+      </c>
+      <c r="BA35" s="8">
+        <v>0.97235725495256997</v>
+      </c>
+      <c r="BB35" s="8">
+        <v>0.97235725495256997</v>
+      </c>
+      <c r="BC35" s="8">
+        <v>1.91870061038405</v>
+      </c>
+      <c r="BD35" s="8">
+        <v>0.104696442302656</v>
+      </c>
+      <c r="BE35" s="8">
+        <v>-5.4117184634483402E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ36" s="2">
+        <v>11</v>
+      </c>
+      <c r="AR36" s="15"/>
+      <c r="AS36" s="8">
+        <v>0.99971749419261002</v>
+      </c>
+      <c r="AT36" s="8">
+        <v>0.99944902061966701</v>
+      </c>
+      <c r="AU36" s="8">
+        <v>9.9276547310544904E-8</v>
+      </c>
+      <c r="AV36" s="8">
+        <v>1.51209903762259</v>
+      </c>
+      <c r="AW36" s="8">
+        <v>1.3956410902619099E-3</v>
+      </c>
+      <c r="AX36" s="8">
+        <v>3.0730841611326101E-3</v>
+      </c>
+      <c r="AY36" s="8">
+        <v>1.00385746446935E-5</v>
+      </c>
+      <c r="AZ36" s="8">
+        <v>0.58919195879963904</v>
+      </c>
+      <c r="BA36" s="8">
+        <v>1.1721122553657</v>
+      </c>
+      <c r="BB36" s="8">
+        <v>1.1721122553657</v>
+      </c>
+      <c r="BC36" s="8">
+        <v>2.33696091379166</v>
+      </c>
+      <c r="BD36" s="8">
+        <v>-6.1444049244763297E-3</v>
+      </c>
+      <c r="BE36" s="8">
+        <v>2.7904849830617802E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ37" s="2">
+        <v>12</v>
+      </c>
+      <c r="AR37" s="15"/>
+      <c r="AS37" s="8">
+        <v>0.99999698593479003</v>
+      </c>
+      <c r="AT37" s="8">
+        <v>0.99999339526608599</v>
+      </c>
+      <c r="AU37" s="8">
+        <v>4.2332795753808402E-11</v>
+      </c>
+      <c r="AV37" s="8">
+        <v>0.79975357516659495</v>
+      </c>
+      <c r="AW37" s="8">
+        <v>2.7949174218000402E-4</v>
+      </c>
+      <c r="AX37" s="8">
+        <v>5.4437464641876598E-4</v>
+      </c>
+      <c r="AY37" s="8">
+        <v>9.9234214514791099E-8</v>
+      </c>
+      <c r="AZ37" s="8">
+        <v>0.498495443008449</v>
+      </c>
+      <c r="BA37" s="8">
+        <v>0.99643086093006805</v>
+      </c>
+      <c r="BB37" s="8">
+        <v>0.99643086093006805</v>
+      </c>
+      <c r="BC37" s="8">
+        <v>1.99666170734906</v>
+      </c>
+      <c r="BD37" s="8">
+        <v>2.24616206141973E-4</v>
+      </c>
+      <c r="BE37" s="8">
+        <v>-1.15322515870097E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ40" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR40" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS40" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AT40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AU40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="AW40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="AX40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AY40" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AZ40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="BA40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="BB40" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="BD40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="BE40" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ41" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR41" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS41" s="8">
+        <v>1.8361881453861399</v>
+      </c>
+      <c r="AT41" s="8">
+        <v>1.85990431982613</v>
+      </c>
+      <c r="AU41" s="8">
+        <v>2.48569673407416</v>
+      </c>
+      <c r="AV41" s="8">
+        <v>15.1640311398804</v>
+      </c>
+      <c r="AW41" s="8">
+        <v>1.8361881453861399</v>
+      </c>
+      <c r="AX41" s="8">
+        <v>2.8599043198261298</v>
+      </c>
+      <c r="AY41" s="8">
+        <v>1.8814838737637301</v>
+      </c>
+      <c r="AZ41" s="8">
+        <v>4.6128170876110399</v>
+      </c>
+      <c r="BA41" s="8">
+        <v>8.1709572737942207</v>
+      </c>
+      <c r="BB41" s="8">
+        <v>8.1709572737942207</v>
+      </c>
+      <c r="BC41" s="8">
+        <v>19.479912254378299</v>
+      </c>
+      <c r="BD41" s="8">
+        <v>0.41590434579954699</v>
+      </c>
+      <c r="BE41" s="8">
+        <v>-0.26702947795808502</v>
+      </c>
+    </row>
+    <row r="42" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ42" s="2">
+        <v>2</v>
+      </c>
+      <c r="AR42" s="15"/>
+      <c r="AS42" s="8">
+        <v>1.83618812624156</v>
+      </c>
+      <c r="AT42" s="8">
+        <v>1.8599041887502401</v>
+      </c>
+      <c r="AU42" s="8">
+        <v>2.48569670703532</v>
+      </c>
+      <c r="AV42" s="8">
+        <v>-7.2683691978454604E-8</v>
+      </c>
+      <c r="AW42" s="8">
+        <v>1.9144577922958199E-8</v>
+      </c>
+      <c r="AX42" s="8">
+        <v>1.3107589191818599E-7</v>
+      </c>
+      <c r="AY42" s="8">
+        <v>2.7038838279480602E-8</v>
+      </c>
+      <c r="AZ42" s="8">
+        <v>1.0408937575080299</v>
+      </c>
+      <c r="BA42" s="8">
+        <v>-9.0341593850292001E-2</v>
+      </c>
+      <c r="BB42" s="8">
+        <v>-9.0341593850292001E-2</v>
+      </c>
+      <c r="BC42" s="8">
+        <v>0.37282269135115298</v>
+      </c>
+      <c r="BD42" s="8">
+        <v>0.41590429584224797</v>
+      </c>
+      <c r="BE42" s="8">
+        <v>-0.26702984164065302</v>
+      </c>
+    </row>
+    <row r="43" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ43" s="2">
+        <v>3</v>
+      </c>
+      <c r="AR43" s="15"/>
+      <c r="AS43" s="8">
+        <v>1.1049303542026701</v>
+      </c>
+      <c r="AT43" s="8">
+        <v>2.0793093846486101</v>
+      </c>
+      <c r="AU43" s="8">
+        <v>2.6363274800985201</v>
+      </c>
+      <c r="AV43" s="8">
+        <v>1.60000007268371</v>
+      </c>
+      <c r="AW43" s="8">
+        <v>0.73125777203888398</v>
+      </c>
+      <c r="AX43" s="8">
+        <v>0.21940519589836999</v>
+      </c>
+      <c r="AY43" s="8">
+        <v>0.150630773063199</v>
+      </c>
+      <c r="AZ43" s="8">
+        <v>2.0945149353603201</v>
+      </c>
+      <c r="BA43" s="8">
+        <v>0.44264536654943398</v>
+      </c>
+      <c r="BB43" s="8">
+        <v>0.44264536654943398</v>
+      </c>
+      <c r="BC43" s="8">
+        <v>0.64244056343607103</v>
+      </c>
+      <c r="BD43" s="8">
+        <v>-7.7202514403495598E-2</v>
+      </c>
+      <c r="BE43" s="8">
+        <v>0.41424196088489301</v>
+      </c>
+    </row>
+    <row r="44" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ44" s="2">
+        <v>4</v>
+      </c>
+      <c r="AR44" s="15"/>
+      <c r="AS44" s="8">
+        <v>1.0954834129533899</v>
+      </c>
+      <c r="AT44" s="8">
+        <v>1.97814619828079</v>
+      </c>
+      <c r="AU44" s="8">
+        <v>2.6570478821036998</v>
+      </c>
+      <c r="AV44" s="8">
+        <v>0.43613750598696399</v>
+      </c>
+      <c r="AW44" s="8">
+        <v>9.44694124928213E-3</v>
+      </c>
+      <c r="AX44" s="8">
+        <v>0.10116318636782</v>
+      </c>
+      <c r="AY44" s="8">
+        <v>2.0720402005187599E-2</v>
+      </c>
+      <c r="AZ44" s="8">
+        <v>1.5295548008473301</v>
+      </c>
+      <c r="BA44" s="8">
+        <v>-2.80633255109809E-2</v>
+      </c>
+      <c r="BB44" s="8">
+        <v>-2.80633255109809E-2</v>
+      </c>
+      <c r="BC44" s="8">
+        <v>0.25025948862054398</v>
+      </c>
+      <c r="BD44" s="8">
+        <v>-9.0823427094219394E-2</v>
+      </c>
+      <c r="BE44" s="8">
+        <v>8.4813839966966197E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ45" s="2">
+        <v>5</v>
+      </c>
+      <c r="AR45" s="15"/>
+      <c r="AS45" s="8">
+        <v>1.20680936289287</v>
+      </c>
+      <c r="AT45" s="8">
+        <v>1.97440911456496</v>
+      </c>
+      <c r="AU45" s="8">
+        <v>2.66119033435643</v>
+      </c>
+      <c r="AV45" s="8">
+        <v>0.80000007268371198</v>
+      </c>
+      <c r="AW45" s="8">
+        <v>0.111325949939481</v>
+      </c>
+      <c r="AX45" s="8">
+        <v>3.7370837158319202E-3</v>
+      </c>
+      <c r="AY45" s="8">
+        <v>4.14245225272047E-3</v>
+      </c>
+      <c r="AZ45" s="8">
+        <v>1.0413010621878001</v>
+      </c>
+      <c r="BA45" s="8">
+        <v>-1.7756028491328901E-2</v>
+      </c>
+      <c r="BB45" s="8">
+        <v>-1.7756028491328901E-2</v>
+      </c>
+      <c r="BC45" s="8">
+        <v>0.25004189607912702</v>
+      </c>
+      <c r="BD45" s="8">
+        <v>1.59614595328532E-2</v>
+      </c>
+      <c r="BE45" s="8">
+        <v>1.11858498058418E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ46" s="2">
+        <v>6</v>
+      </c>
+      <c r="AR46" s="15"/>
+      <c r="AS46" s="8">
+        <v>1.1898798465112601</v>
+      </c>
+      <c r="AT46" s="8">
+        <v>1.9744129072216401</v>
+      </c>
+      <c r="AU46" s="8">
+        <v>2.6613256347394598</v>
+      </c>
+      <c r="AV46" s="8">
+        <v>1.0197998159500099</v>
+      </c>
+      <c r="AW46" s="8">
+        <v>1.6929516381610301E-2</v>
+      </c>
+      <c r="AX46" s="8">
+        <v>3.7926566840429299E-6</v>
+      </c>
+      <c r="AY46" s="8">
+        <v>1.3530038303866099E-4</v>
+      </c>
+      <c r="AZ46" s="8">
+        <v>1.0621895390146301</v>
+      </c>
+      <c r="BA46" s="8">
+        <v>-1.9824935101327299E-2</v>
+      </c>
+      <c r="BB46" s="8">
+        <v>-1.9824935101327299E-2</v>
+      </c>
+      <c r="BC46" s="8">
+        <v>0.25024681166949703</v>
+      </c>
+      <c r="BD46" s="8">
+        <v>-1.7823080100676199E-7</v>
+      </c>
+      <c r="BE46" s="8">
+        <v>-1.3076470745183801E-4</v>
+      </c>
+    </row>
+    <row r="47" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ47" s="2">
+        <v>1</v>
+      </c>
+      <c r="AR47" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS47" s="8">
+        <v>3.2591466109293399</v>
+      </c>
+      <c r="AT47" s="8">
+        <v>0.95126788687869102</v>
+      </c>
+      <c r="AU47" s="8">
+        <v>1.5847900408139399</v>
+      </c>
+      <c r="AV47" s="8">
+        <v>51.2000000726837</v>
+      </c>
+      <c r="AW47" s="8">
+        <v>1.7408533890706499</v>
+      </c>
+      <c r="AX47" s="8">
+        <v>5.0487321131213001</v>
+      </c>
+      <c r="AY47" s="8">
+        <v>1.2527098403126899</v>
+      </c>
+      <c r="AZ47" s="8">
+        <v>3.2007271618408399</v>
+      </c>
+      <c r="BA47" s="8">
+        <v>5.1280841687029497</v>
+      </c>
+      <c r="BB47" s="8">
+        <v>5.1280841687029497</v>
+      </c>
+      <c r="BC47" s="8">
+        <v>12.9493446063095</v>
+      </c>
+      <c r="BD47" s="8">
+        <v>0.25495133445540302</v>
+      </c>
+      <c r="BE47" s="8">
+        <v>-0.37877393402439202</v>
+      </c>
+    </row>
+    <row r="48" spans="43:57" x14ac:dyDescent="0.25">
+      <c r="AQ48" s="2">
+        <v>2</v>
+      </c>
+      <c r="AR48" s="15"/>
+      <c r="AS48" s="8">
+        <v>3.4844176834867602</v>
+      </c>
+      <c r="AT48" s="8">
+        <v>1.67076060786737</v>
+      </c>
+      <c r="AU48" s="8">
+        <v>1.6836076638547099</v>
+      </c>
+      <c r="AV48" s="8">
+        <v>0.20000007268370301</v>
+      </c>
+      <c r="AW48" s="8">
+        <v>0.22527107255741799</v>
+      </c>
+      <c r="AX48" s="8">
+        <v>0.719492720988678</v>
+      </c>
+      <c r="AY48" s="8">
+        <v>9.8817623040769798E-2</v>
+      </c>
+      <c r="AZ48" s="8">
+        <v>0.91275492320182805</v>
+      </c>
+      <c r="BA48" s="8">
+        <v>0.15794058132678901</v>
+      </c>
+      <c r="BB48" s="8">
+        <v>0.15794058132678901</v>
+      </c>
+      <c r="BC48" s="8">
+        <v>2.1527418932318798</v>
+      </c>
+      <c r="BD48" s="8">
+        <v>0.44635190269220498</v>
+      </c>
+      <c r="BE48" s="8">
+        <v>-5.8594907387670397E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+      <c r="AQ49" s="2">
+        <v>3</v>
+      </c>
+      <c r="AR49" s="15"/>
+      <c r="AS49" s="8">
+        <v>0.93622320381316804</v>
+      </c>
+      <c r="AT49" s="8">
+        <v>2.02687346231779</v>
+      </c>
+      <c r="AU49" s="8">
+        <v>2.62529864527523</v>
+      </c>
+      <c r="AV49" s="8">
+        <v>6.4000000726837101</v>
+      </c>
+      <c r="AW49" s="8">
+        <v>2.5481944796735898</v>
+      </c>
+      <c r="AX49" s="8">
+        <v>0.35611285445042601</v>
+      </c>
+      <c r="AY49" s="8">
+        <v>0.94169098142051599</v>
+      </c>
+      <c r="AZ49" s="8">
+        <v>3.79162838970448</v>
+      </c>
+      <c r="BA49" s="8">
+        <v>0.283925570845322</v>
+      </c>
+      <c r="BB49" s="8">
+        <v>0.283925570845322</v>
+      </c>
+      <c r="BC49" s="8">
+        <v>2.15825523647836</v>
+      </c>
+      <c r="BD49" s="8">
+        <v>-0.24487100478024601</v>
+      </c>
+      <c r="BE49" s="8">
+        <v>0.197338081306109</v>
+      </c>
+    </row>
+    <row r="50" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="AQ50" s="2">
+        <v>4</v>
+      </c>
+      <c r="AR50" s="15"/>
+      <c r="AS50" s="8">
+        <v>1.1389615854687201</v>
+      </c>
+      <c r="AT50" s="8">
+        <v>1.9440564745995601</v>
+      </c>
+      <c r="AU50" s="8">
+        <v>2.6581308287134902</v>
+      </c>
+      <c r="AV50" s="8">
+        <v>0.232383411145484</v>
+      </c>
+      <c r="AW50" s="8">
+        <v>0.20273838165555499</v>
+      </c>
+      <c r="AX50" s="8">
+        <v>8.28169877182343E-2</v>
+      </c>
+      <c r="AY50" s="8">
+        <v>3.28321834382636E-2</v>
+      </c>
+      <c r="AZ50" s="8">
+        <v>3.0594477976614098</v>
+      </c>
+      <c r="BA50" s="8">
+        <v>1.21075772743038</v>
+      </c>
+      <c r="BB50" s="8">
+        <v>1.21075772743038</v>
+      </c>
+      <c r="BC50" s="8">
+        <v>0.98502303691525195</v>
+      </c>
+      <c r="BD50" s="8">
+        <v>-5.1051285656992101E-2</v>
+      </c>
+      <c r="BE50" s="8">
+        <v>-0.124974898671857</v>
+      </c>
+    </row>
+    <row r="51" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J51" s="1"/>
+      <c r="AQ51" s="2">
+        <v>5</v>
+      </c>
+      <c r="AR51" s="15"/>
+      <c r="AS51" s="8">
+        <v>1.2004622213737499</v>
+      </c>
+      <c r="AT51" s="8">
+        <v>1.98103926660626</v>
+      </c>
+      <c r="AU51" s="8">
+        <v>2.6611809519541101</v>
+      </c>
+      <c r="AV51" s="8">
+        <v>0.20000007268370301</v>
+      </c>
+      <c r="AW51" s="8">
+        <v>6.1500635905031603E-2</v>
+      </c>
+      <c r="AX51" s="8">
+        <v>3.69827920067042E-2</v>
+      </c>
+      <c r="AY51" s="8">
+        <v>3.0501232406141502E-3</v>
+      </c>
+      <c r="AZ51" s="8">
+        <v>1.0296912661604101</v>
+      </c>
+      <c r="BA51" s="8">
+        <v>-1.21763342067473E-2</v>
+      </c>
+      <c r="BB51" s="8">
+        <v>-1.21763342067473E-2</v>
+      </c>
+      <c r="BC51" s="8">
+        <v>0.248201799539392</v>
+      </c>
+      <c r="BD51" s="8">
+        <v>1.04736579487551E-2</v>
+      </c>
+      <c r="BE51" s="8">
+        <v>2.70463209652336E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="AQ52" s="2">
+        <v>6</v>
+      </c>
+      <c r="AR52" s="15"/>
+      <c r="AS52" s="8">
+        <v>1.1899497347037</v>
+      </c>
+      <c r="AT52" s="8">
+        <v>1.9744178377642101</v>
+      </c>
+      <c r="AU52" s="8">
+        <v>2.6613256330104398</v>
+      </c>
+      <c r="AV52" s="8">
+        <v>1.0054687621581999</v>
+      </c>
+      <c r="AW52" s="8">
+        <v>1.0512486670051399E-2</v>
+      </c>
+      <c r="AX52" s="8">
+        <v>6.6214288420569601E-3</v>
+      </c>
+      <c r="AY52" s="8">
+        <v>1.4468105633147401E-4</v>
+      </c>
+      <c r="AZ52" s="8">
+        <v>1.0399872534141399</v>
+      </c>
+      <c r="BA52" s="8">
+        <v>-1.1452926484131E-2</v>
+      </c>
+      <c r="BB52" s="8">
+        <v>-1.1452926484131E-2</v>
+      </c>
+      <c r="BC52" s="8">
+        <v>0.24825262698509901</v>
+      </c>
+      <c r="BD52" s="8">
+        <v>6.6357656171300795E-5</v>
+      </c>
+      <c r="BE52" s="8">
+        <v>-1.05951174109261E-4</v>
+      </c>
+    </row>
+    <row r="53" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J61" s="1"/>
+    </row>
+    <row r="62" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="J62" s="1"/>
+    </row>
+    <row r="63" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+    </row>
+    <row r="64" spans="6:57" x14ac:dyDescent="0.25">
+      <c r="F64" s="1"/>
+      <c r="J64" s="1"/>
+    </row>
+    <row r="65" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+    </row>
+    <row r="66" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="J66" s="1"/>
+    </row>
+    <row r="67" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+    </row>
+    <row r="68" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="F68" s="1"/>
+      <c r="J68" s="1"/>
+    </row>
+    <row r="69" spans="6:10" x14ac:dyDescent="0.25">
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="AR47:AR52"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="O3:O9"/>
+    <mergeCell ref="O11:O15"/>
+    <mergeCell ref="AC4:AC9"/>
+    <mergeCell ref="AC12:AC17"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="AR4:AR5"/>
+    <mergeCell ref="AR7:AR8"/>
+    <mergeCell ref="AR11:AR25"/>
+    <mergeCell ref="AR26:AR37"/>
+    <mergeCell ref="AR41:AR46"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Отчёт/МО2.xlsx
+++ b/Отчёт/МО2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maksim\Desktop\Мо_Костя\Лаб_2\Отчёт\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maksim\source\repos\MaxArt-Term66\Отчёт\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{320BCE1C-1022-4156-9D7E-14353D01BB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0C3C17-4A86-4AF0-83B3-2156FF490180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9776549A-3957-4A95-AACA-BCFA2710EB61}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{9776549A-3957-4A95-AACA-BCFA2710EB61}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="47">
   <si>
     <t>i</t>
   </si>
@@ -136,13 +136,65 @@
     <t>0.0
 0.0</t>
   </si>
+  <si>
+    <t>|xi - xi-1|</t>
+  </si>
+  <si>
+    <t>|yi - yi-1|</t>
+  </si>
+  <si>
+    <t>|fi - fi-1|</t>
+  </si>
+  <si>
+    <t>angle</t>
+  </si>
+  <si>
+    <t>1 функция</t>
+  </si>
+  <si>
+    <t>я не нашёл точность</t>
+  </si>
+  <si>
+    <t>2 функция</t>
+  </si>
+  <si>
+    <t>только пшеничный другой, остальное то же</t>
+  </si>
+  <si>
+    <t>0 0</t>
+  </si>
+  <si>
+    <t>пшеница</t>
+  </si>
+  <si>
+    <t>золотое</t>
+  </si>
+  <si>
+    <t>парабола</t>
+  </si>
+  <si>
+    <t>-1 6</t>
+  </si>
+  <si>
+    <t>курочка</t>
+  </si>
+  <si>
+    <t>3 функция</t>
+  </si>
+  <si>
+    <t>0 -1</t>
+  </si>
+  <si>
+    <t>5 6</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -233,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -257,9 +309,6 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -290,6 +339,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -624,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{768FE0D3-F3E2-4B20-ACF6-AB64EBC69073}">
-  <dimension ref="A1:BE69"/>
+  <dimension ref="A1:CJ84"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
@@ -663,9 +717,10 @@
     <col min="55" max="55" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="56" max="57" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="6" bestFit="1" customWidth="1"/>
+    <col min="76" max="88" width="9.140625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:88" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -678,8 +733,25 @@
       <c r="M1" s="6" t="s">
         <v>16</v>
       </c>
+      <c r="BI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="BJ1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="BK1" s="12"/>
+      <c r="BL1" s="12"/>
+      <c r="BM1" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="BN1" s="12"/>
+      <c r="BO1" s="12"/>
+      <c r="BP1" s="12"/>
+      <c r="BW1" t="s">
+        <v>43</v>
+      </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -759,11 +831,11 @@
         <v>9.9999999999999995E-8</v>
       </c>
     </row>
-    <row r="3" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:88" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="4">
@@ -799,7 +871,7 @@
       <c r="N3" s="10">
         <v>1</v>
       </c>
-      <c r="O3" s="19" t="s">
+      <c r="O3" s="18" t="s">
         <v>17</v>
       </c>
       <c r="P3" s="9">
@@ -919,12 +991,93 @@
       <c r="BE3" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="BI3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BX3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BY3" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BZ3" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="CA3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="CC3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="CD3" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="CE3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG3" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="CH3" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="CI3" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="CJ3" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:57" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:88" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2</v>
       </c>
-      <c r="B4" s="22"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="4">
         <v>6.8721276424421101</v>
       </c>
@@ -958,7 +1111,7 @@
       <c r="N4" s="10">
         <v>2</v>
       </c>
-      <c r="O4" s="20"/>
+      <c r="O4" s="19"/>
       <c r="P4" s="9">
         <v>0.68169223692808001</v>
       </c>
@@ -992,7 +1145,7 @@
       <c r="AB4" s="2">
         <v>1</v>
       </c>
-      <c r="AC4" s="14" t="s">
+      <c r="AC4" s="13" t="s">
         <v>14</v>
       </c>
       <c r="AD4" s="8">
@@ -1034,7 +1187,7 @@
       <c r="AQ4" s="2">
         <v>1</v>
       </c>
-      <c r="AR4" s="13" t="s">
+      <c r="AR4" s="23" t="s">
         <v>14</v>
       </c>
       <c r="AS4" s="8">
@@ -1076,12 +1229,93 @@
       <c r="BE4" s="8">
         <v>-1.48392200426628</v>
       </c>
+      <c r="BI4">
+        <v>1</v>
+      </c>
+      <c r="BJ4">
+        <v>-0.49379039942668501</v>
+      </c>
+      <c r="BK4">
+        <v>-0.50122181876092398</v>
+      </c>
+      <c r="BL4">
+        <v>2.2369323567514598</v>
+      </c>
+      <c r="BM4">
+        <v>1.4901401649513999</v>
+      </c>
+      <c r="BN4">
+        <v>1.49755332851867</v>
+      </c>
+      <c r="BO4">
+        <v>2.49389090619537E-3</v>
+      </c>
+      <c r="BP4">
+        <v>0.49379039942668501</v>
+      </c>
+      <c r="BQ4">
+        <v>0.49877818123907502</v>
+      </c>
+      <c r="BR4">
+        <v>98.763067643248505</v>
+      </c>
+      <c r="BS4">
+        <v>179.714248489228</v>
+      </c>
+      <c r="BT4">
+        <v>-1.50129693200557</v>
+      </c>
+      <c r="BU4">
+        <v>-1.48628386684779</v>
+      </c>
+      <c r="BW4">
+        <v>1</v>
+      </c>
+      <c r="BX4" s="12">
+        <v>-0.49378417191427199</v>
+      </c>
+      <c r="BY4" s="12">
+        <v>-0.50122810917750205</v>
+      </c>
+      <c r="BZ4" s="12">
+        <v>2.2369323724595001</v>
+      </c>
+      <c r="CA4" s="12">
+        <v>2.49385945411248E-3</v>
+      </c>
+      <c r="CB4" s="12">
+        <v>0.49378417191427199</v>
+      </c>
+      <c r="CC4" s="12">
+        <v>0.49877189082249701</v>
+      </c>
+      <c r="CD4" s="12">
+        <v>98.763067627540394</v>
+      </c>
+      <c r="CE4" s="12">
+        <v>0.49875309365160397</v>
+      </c>
+      <c r="CF4" s="12">
+        <v>0.49874689044916698</v>
+      </c>
+      <c r="CG4" s="12">
+        <v>0.49874689044916698</v>
+      </c>
+      <c r="CH4" s="12">
+        <v>0.50374065638657695</v>
+      </c>
+      <c r="CI4" s="12">
+        <v>-1.4987808911824301</v>
+      </c>
+      <c r="CJ4" s="12">
+        <v>-1.48878745264611</v>
+      </c>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>3</v>
       </c>
-      <c r="B5" s="22"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="4">
         <v>6.8865774897436101</v>
       </c>
@@ -1115,7 +1349,7 @@
       <c r="N5" s="10">
         <v>3</v>
       </c>
-      <c r="O5" s="20"/>
+      <c r="O5" s="19"/>
       <c r="P5" s="9">
         <v>1.0358578464086901</v>
       </c>
@@ -1149,7 +1383,7 @@
       <c r="AB5" s="2">
         <v>2</v>
       </c>
-      <c r="AC5" s="14"/>
+      <c r="AC5" s="13"/>
       <c r="AD5" s="8">
         <v>3.1858473461718901</v>
       </c>
@@ -1189,7 +1423,7 @@
       <c r="AQ5" s="2">
         <v>2</v>
       </c>
-      <c r="AR5" s="13"/>
+      <c r="AR5" s="23"/>
       <c r="AS5" s="8">
         <v>0.99999997541970997</v>
       </c>
@@ -1229,12 +1463,93 @@
       <c r="BE5" s="8">
         <v>-5.9585840483933297E-6</v>
       </c>
+      <c r="BI5">
+        <v>2</v>
+      </c>
+      <c r="BJ5">
+        <v>0.97785191729377596</v>
+      </c>
+      <c r="BK5">
+        <v>0.95570398084765396</v>
+      </c>
+      <c r="BL5">
+        <v>4.9543646449706602E-2</v>
+      </c>
+      <c r="BM5">
+        <v>8.6842376891580795</v>
+      </c>
+      <c r="BN5">
+        <v>17.368419979750001</v>
+      </c>
+      <c r="BO5">
+        <v>0.98024733505216599</v>
+      </c>
+      <c r="BP5">
+        <v>1.47164231672046</v>
+      </c>
+      <c r="BQ5">
+        <v>1.45692579960857</v>
+      </c>
+      <c r="BR5">
+        <v>2.18738871030176</v>
+      </c>
+      <c r="BS5">
+        <v>19.091142132654301</v>
+      </c>
+      <c r="BT5">
+        <v>4.3852911238119097</v>
+      </c>
+      <c r="BU5">
+        <v>-4.42958728922435</v>
+      </c>
+      <c r="BW5">
+        <v>2</v>
+      </c>
+      <c r="BX5" s="12">
+        <v>1.0000000161313001</v>
+      </c>
+      <c r="BY5" s="12">
+        <v>1.00000004766192</v>
+      </c>
+      <c r="BZ5" s="12">
+        <v>9.9678247351070206E-14</v>
+      </c>
+      <c r="CA5" s="12">
+        <v>1.0025062716152999</v>
+      </c>
+      <c r="CB5" s="12">
+        <v>1.49378418804557</v>
+      </c>
+      <c r="CC5" s="12">
+        <v>1.5012281568394199</v>
+      </c>
+      <c r="CD5" s="12">
+        <v>2.2369323724594001</v>
+      </c>
+      <c r="CE5" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="CF5" s="12">
+        <v>0.499999999999999</v>
+      </c>
+      <c r="CG5" s="12">
+        <v>0.499999999999999</v>
+      </c>
+      <c r="CH5" s="12">
+        <v>0.50499999999999901</v>
+      </c>
+      <c r="CI5" s="12">
+        <v>-6.2738623096691896E-6</v>
+      </c>
+      <c r="CJ5" s="12">
+        <v>6.3061249111484501E-6</v>
+      </c>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B6" s="22"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="4">
         <v>1.00001087773403</v>
       </c>
@@ -1268,7 +1583,7 @@
       <c r="N6" s="10">
         <v>4</v>
       </c>
-      <c r="O6" s="20"/>
+      <c r="O6" s="19"/>
       <c r="P6" s="9">
         <v>1.03632844898805</v>
       </c>
@@ -1302,7 +1617,7 @@
       <c r="AB6" s="2">
         <v>3</v>
       </c>
-      <c r="AC6" s="14"/>
+      <c r="AC6" s="13"/>
       <c r="AD6" s="8">
         <v>2.7321410861811701</v>
       </c>
@@ -1339,12 +1654,51 @@
       <c r="AO6" s="8">
         <v>-0.52588871475978405</v>
       </c>
+      <c r="BI6">
+        <v>3</v>
+      </c>
+      <c r="BJ6">
+        <v>0.99999999507633797</v>
+      </c>
+      <c r="BK6">
+        <v>0.99999999512556303</v>
+      </c>
+      <c r="BL6" s="1">
+        <v>2.4484761836621999E-17</v>
+      </c>
+      <c r="BM6" s="1">
+        <v>1.9692448447004299E-8</v>
+      </c>
+      <c r="BN6" s="1">
+        <v>-9.8451244987795593E-9</v>
+      </c>
+      <c r="BO6">
+        <v>2.5503767371789798E-3</v>
+      </c>
+      <c r="BP6">
+        <v>2.2148077782561702E-2</v>
+      </c>
+      <c r="BQ6">
+        <v>4.42960142779091E-2</v>
+      </c>
+      <c r="BR6">
+        <v>4.9543646449706602E-2</v>
+      </c>
+      <c r="BS6">
+        <v>71.562491375200494</v>
+      </c>
+      <c r="BT6" s="1">
+        <v>-1.9692448338659501E-8</v>
+      </c>
+      <c r="BU6" s="1">
+        <v>9.8451247154685007E-9</v>
+      </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B7" s="23"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="4">
         <v>0.99998539145897603</v>
       </c>
@@ -1378,7 +1732,7 @@
       <c r="N7" s="10">
         <v>47</v>
       </c>
-      <c r="O7" s="20"/>
+      <c r="O7" s="19"/>
       <c r="P7" s="9">
         <v>0.99947608361539697</v>
       </c>
@@ -1412,7 +1766,7 @@
       <c r="AB7" s="2">
         <v>52</v>
       </c>
-      <c r="AC7" s="14"/>
+      <c r="AC7" s="13"/>
       <c r="AD7" s="8">
         <v>1.1900759709298101</v>
       </c>
@@ -1452,7 +1806,7 @@
       <c r="AQ7" s="2">
         <v>1</v>
       </c>
-      <c r="AR7" s="13" t="s">
+      <c r="AR7" s="23" t="s">
         <v>15</v>
       </c>
       <c r="AS7" s="8">
@@ -1494,12 +1848,54 @@
       <c r="BE7" s="8">
         <v>0.20218754811596101</v>
       </c>
+      <c r="BW7" t="s">
+        <v>0</v>
+      </c>
+      <c r="BX7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BY7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BZ7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="CA7" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB7" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="CC7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="CD7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="CE7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="CH7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="CI7" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="CJ7" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:88" x14ac:dyDescent="0.25">
       <c r="N8" s="10">
         <v>48</v>
       </c>
-      <c r="O8" s="20"/>
+      <c r="O8" s="19"/>
       <c r="P8" s="9">
         <v>0.99999929818358002</v>
       </c>
@@ -1533,7 +1929,7 @@
       <c r="AB8" s="2">
         <v>53</v>
       </c>
-      <c r="AC8" s="14"/>
+      <c r="AC8" s="13"/>
       <c r="AD8" s="8">
         <v>1.19009514162097</v>
       </c>
@@ -1573,7 +1969,7 @@
       <c r="AQ8" s="2">
         <v>2</v>
       </c>
-      <c r="AR8" s="13"/>
+      <c r="AR8" s="23"/>
       <c r="AS8" s="8">
         <v>1.0000000655286501</v>
       </c>
@@ -1613,12 +2009,93 @@
       <c r="BE8" s="8">
         <v>-2.4147889465808699E-5</v>
       </c>
+      <c r="BI8" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BW8">
+        <v>1</v>
+      </c>
+      <c r="BX8" s="12">
+        <v>1.1920352975299</v>
+      </c>
+      <c r="BY8" s="12">
+        <v>1.19300219073401</v>
+      </c>
+      <c r="BZ8" s="12">
+        <v>3.69710437442154E-2</v>
+      </c>
+      <c r="CA8" s="12">
+        <v>2.4937519560125098E-3</v>
+      </c>
+      <c r="CB8" s="12">
+        <v>2.8079647024700898</v>
+      </c>
+      <c r="CC8" s="12">
+        <v>2.7930021907340099</v>
+      </c>
+      <c r="CD8" s="12">
+        <v>3144.9630289562501</v>
+      </c>
+      <c r="CE8" s="12">
+        <v>0.49875314163485501</v>
+      </c>
+      <c r="CF8" s="12">
+        <v>0.49874689068864297</v>
+      </c>
+      <c r="CG8" s="12">
+        <v>0.49874689068864297</v>
+      </c>
+      <c r="CH8" s="12">
+        <v>0.50374060840420598</v>
+      </c>
+      <c r="CI8" s="12">
+        <v>0.19069195423803101</v>
+      </c>
+      <c r="CJ8" s="12">
+        <v>0.19337864082178399</v>
+      </c>
     </row>
-    <row r="9" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:88" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>1</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="4">
@@ -1654,7 +2131,7 @@
       <c r="N9" s="10">
         <v>49</v>
       </c>
-      <c r="O9" s="21"/>
+      <c r="O9" s="20"/>
       <c r="P9" s="9">
         <v>0.99999809000305095</v>
       </c>
@@ -1688,7 +2165,7 @@
       <c r="AB9" s="2">
         <v>54</v>
       </c>
-      <c r="AC9" s="14"/>
+      <c r="AC9" s="13"/>
       <c r="AD9" s="8">
         <v>1.1900169429141101</v>
       </c>
@@ -1725,12 +2202,93 @@
       <c r="AO9" s="8">
         <v>-9.3149055100716306E-5</v>
       </c>
+      <c r="BI9">
+        <v>1</v>
+      </c>
+      <c r="BJ9">
+        <v>1.19203737363762</v>
+      </c>
+      <c r="BK9">
+        <v>1.1930001256890399</v>
+      </c>
+      <c r="BL9">
+        <v>3.6971042024887303E-2</v>
+      </c>
+      <c r="BM9">
+        <v>-0.19155726385694399</v>
+      </c>
+      <c r="BN9">
+        <v>-0.192517658872292</v>
+      </c>
+      <c r="BO9">
+        <v>2.4937501122223602E-3</v>
+      </c>
+      <c r="BP9">
+        <v>2.8079626263623698</v>
+      </c>
+      <c r="BQ9">
+        <v>2.7930001256890402</v>
+      </c>
+      <c r="BR9">
+        <v>3144.96302895797</v>
+      </c>
+      <c r="BS9">
+        <v>179.87985806496201</v>
+      </c>
+      <c r="BT9">
+        <v>0.191524336991125</v>
+      </c>
+      <c r="BU9">
+        <v>0.19255041028412001</v>
+      </c>
+      <c r="BW9">
+        <v>2</v>
+      </c>
+      <c r="BX9" s="12">
+        <v>1.00000000105543</v>
+      </c>
+      <c r="BY9" s="12">
+        <v>0.99999999065546896</v>
+      </c>
+      <c r="BZ9" s="12">
+        <v>1.08170325898423E-14</v>
+      </c>
+      <c r="CA9" s="12">
+        <v>1.0025062716152999</v>
+      </c>
+      <c r="CB9" s="12">
+        <v>0.19203529647447701</v>
+      </c>
+      <c r="CC9" s="12">
+        <v>0.19300220007854699</v>
+      </c>
+      <c r="CD9" s="12">
+        <v>3.6971043744204603E-2</v>
+      </c>
+      <c r="CE9" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="CF9" s="12">
+        <v>0.499999999999999</v>
+      </c>
+      <c r="CG9" s="12">
+        <v>0.499999999999999</v>
+      </c>
+      <c r="CH9" s="12">
+        <v>0.505</v>
+      </c>
+      <c r="CI9" s="12">
+        <v>2.0821030393136602E-6</v>
+      </c>
+      <c r="CJ9" s="12">
+        <v>-2.0799921784941901E-6</v>
+      </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:88" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>2</v>
       </c>
-      <c r="B10" s="17"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="4">
         <v>0.236082980534878</v>
       </c>
@@ -1806,12 +2364,51 @@
       <c r="BE10" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="BI10">
+        <v>2</v>
+      </c>
+      <c r="BJ10">
+        <v>1.00003529480438</v>
+      </c>
+      <c r="BK10">
+        <v>0.99996941410664897</v>
+      </c>
+      <c r="BL10" s="1">
+        <v>4.3527235668551502E-7</v>
+      </c>
+      <c r="BM10">
+        <v>-1.41531969832462E-2</v>
+      </c>
+      <c r="BN10">
+        <v>1.2264815406895601E-2</v>
+      </c>
+      <c r="BO10">
+        <v>1.00249441846197</v>
+      </c>
+      <c r="BP10">
+        <v>0.192002078833233</v>
+      </c>
+      <c r="BQ10">
+        <v>0.19303071158239399</v>
+      </c>
+      <c r="BR10">
+        <v>3.6970606752530603E-2</v>
+      </c>
+      <c r="BS10">
+        <v>94.090483371080893</v>
+      </c>
+      <c r="BT10">
+        <v>1.3246729156743501E-2</v>
+      </c>
+      <c r="BU10">
+        <v>-1.31761395479657E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:88" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>3</v>
       </c>
-      <c r="B11" s="17"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="4">
         <v>0.72477003623153002</v>
       </c>
@@ -1845,7 +2442,7 @@
       <c r="N11" s="2">
         <v>1</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="O11" s="15" t="s">
         <v>18</v>
       </c>
       <c r="P11" s="8">
@@ -1923,7 +2520,7 @@
       <c r="AQ11" s="2">
         <v>1</v>
       </c>
-      <c r="AR11" s="14" t="s">
+      <c r="AR11" s="13" t="s">
         <v>29</v>
       </c>
       <c r="AS11" s="8">
@@ -1965,12 +2562,51 @@
       <c r="BE11" s="8">
         <v>-5.2010852551808604</v>
       </c>
+      <c r="BI11">
+        <v>3</v>
+      </c>
+      <c r="BJ11">
+        <v>0.99999999985231303</v>
+      </c>
+      <c r="BK11">
+        <v>0.999999999851517</v>
+      </c>
+      <c r="BL11" s="1">
+        <v>2.1874674855317501E-20</v>
+      </c>
+      <c r="BM11" s="1">
+        <v>1.3621170679973099E-10</v>
+      </c>
+      <c r="BN11" s="1">
+        <v>1.5916157435215499E-10</v>
+      </c>
+      <c r="BO11">
+        <v>2.4937794702761498E-3</v>
+      </c>
+      <c r="BP11" s="1">
+        <v>3.5294952075548497E-5</v>
+      </c>
+      <c r="BQ11" s="1">
+        <v>3.0585744868472098E-5</v>
+      </c>
+      <c r="BR11" s="1">
+        <v>4.35272356685494E-7</v>
+      </c>
+      <c r="BS11">
+        <v>4.4428325759062997</v>
+      </c>
+      <c r="BT11" s="1">
+        <v>-1.3621170857902601E-10</v>
+      </c>
+      <c r="BU11" s="1">
+        <v>-1.59161572810262E-10</v>
+      </c>
     </row>
-    <row r="12" spans="1:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:88" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>4</v>
       </c>
-      <c r="B12" s="18"/>
+      <c r="B12" s="17"/>
       <c r="C12" s="4">
         <v>1.0000009877001601</v>
       </c>
@@ -2004,7 +2640,7 @@
       <c r="N12" s="2">
         <v>2</v>
       </c>
-      <c r="O12" s="17"/>
+      <c r="O12" s="16"/>
       <c r="P12" s="8">
         <v>11.947201283894101</v>
       </c>
@@ -2038,7 +2674,7 @@
       <c r="AB12" s="2">
         <v>1</v>
       </c>
-      <c r="AC12" s="16" t="s">
+      <c r="AC12" s="15" t="s">
         <v>24</v>
       </c>
       <c r="AD12" s="8">
@@ -2080,7 +2716,7 @@
       <c r="AQ12" s="2">
         <v>2</v>
       </c>
-      <c r="AR12" s="15"/>
+      <c r="AR12" s="14"/>
       <c r="AS12" s="8">
         <v>0.29283632719854802</v>
       </c>
@@ -2121,11 +2757,11 @@
         <v>-7.0316390802178903</v>
       </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:88" x14ac:dyDescent="0.25">
       <c r="N13" s="2">
         <v>3</v>
       </c>
-      <c r="O13" s="17"/>
+      <c r="O13" s="16"/>
       <c r="P13" s="8">
         <v>9.9560154431959005E-3</v>
       </c>
@@ -2159,7 +2795,7 @@
       <c r="AB13" s="2">
         <v>2</v>
       </c>
-      <c r="AC13" s="17"/>
+      <c r="AC13" s="16"/>
       <c r="AD13" s="8">
         <v>2.8818894698056501</v>
       </c>
@@ -2199,7 +2835,7 @@
       <c r="AQ13" s="2">
         <v>3</v>
       </c>
-      <c r="AR13" s="15"/>
+      <c r="AR13" s="14"/>
       <c r="AS13" s="8">
         <v>0.344615765395275</v>
       </c>
@@ -2239,12 +2875,40 @@
       <c r="BE13" s="8">
         <v>1.6636846249538899</v>
       </c>
+      <c r="BI13" t="s">
+        <v>36</v>
+      </c>
+      <c r="BJ13" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="BK13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="BL13" s="12"/>
+      <c r="BM13" s="12"/>
+      <c r="BN13" s="12"/>
+      <c r="BO13" s="12"/>
+      <c r="BP13" s="12"/>
+      <c r="BQ13" s="12"/>
+      <c r="BR13" s="12"/>
+      <c r="BS13" s="12"/>
+      <c r="BT13" s="12"/>
+      <c r="BU13" s="12"/>
+      <c r="BW13" t="s">
+        <v>36</v>
+      </c>
+      <c r="BX13" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="BY13" s="12" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:88" x14ac:dyDescent="0.25">
       <c r="N14" s="2">
         <v>1596</v>
       </c>
-      <c r="O14" s="17"/>
+      <c r="O14" s="16"/>
       <c r="P14" s="8">
         <v>0.99998698008290499</v>
       </c>
@@ -2278,7 +2942,7 @@
       <c r="AB14" s="2">
         <v>3</v>
       </c>
-      <c r="AC14" s="17"/>
+      <c r="AC14" s="16"/>
       <c r="AD14" s="8">
         <v>2.8818895049183602</v>
       </c>
@@ -2318,7 +2982,7 @@
       <c r="AQ14" s="2">
         <v>4</v>
       </c>
-      <c r="AR14" s="15"/>
+      <c r="AR14" s="14"/>
       <c r="AS14" s="8">
         <v>0.46111377455341201</v>
       </c>
@@ -2358,12 +3022,30 @@
       <c r="BE14" s="8">
         <v>-3.2793864804363801</v>
       </c>
+      <c r="BI14" t="s">
+        <v>38</v>
+      </c>
+      <c r="BJ14" s="12"/>
+      <c r="BK14" s="12"/>
+      <c r="BL14" s="12"/>
+      <c r="BM14" s="12"/>
+      <c r="BN14" s="12"/>
+      <c r="BO14" s="12"/>
+      <c r="BP14" s="12"/>
+      <c r="BQ14" s="12"/>
+      <c r="BR14" s="12"/>
+      <c r="BS14" s="12"/>
+      <c r="BT14" s="12"/>
+      <c r="BU14" s="12"/>
+      <c r="BW14" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:88" x14ac:dyDescent="0.25">
       <c r="N15" s="2">
         <v>1597</v>
       </c>
-      <c r="O15" s="18"/>
+      <c r="O15" s="17"/>
       <c r="P15" s="8">
         <v>0.99998270258053601</v>
       </c>
@@ -2397,7 +3079,7 @@
       <c r="AB15" s="2">
         <v>12</v>
       </c>
-      <c r="AC15" s="17"/>
+      <c r="AC15" s="16"/>
       <c r="AD15" s="8">
         <v>1.1899145223262799</v>
       </c>
@@ -2437,7 +3119,7 @@
       <c r="AQ15" s="2">
         <v>5</v>
       </c>
-      <c r="AR15" s="15"/>
+      <c r="AR15" s="14"/>
       <c r="AS15" s="8">
         <v>0.53849589576151302</v>
       </c>
@@ -2477,12 +3159,93 @@
       <c r="BE15" s="8">
         <v>-4.9611398276207899</v>
       </c>
+      <c r="BI15" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM15" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN15" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS15" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BW15" t="s">
+        <v>0</v>
+      </c>
+      <c r="BX15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BY15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BZ15" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="CA15" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB15" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="CC15" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="CD15" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="CE15" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG15" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="CH15" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="CI15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="CJ15" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:88" x14ac:dyDescent="0.25">
       <c r="AB16" s="2">
         <v>13</v>
       </c>
-      <c r="AC16" s="17"/>
+      <c r="AC16" s="16"/>
       <c r="AD16" s="8">
         <v>1.1899145223292</v>
       </c>
@@ -2522,7 +3285,7 @@
       <c r="AQ16" s="2">
         <v>6</v>
       </c>
-      <c r="AR16" s="15"/>
+      <c r="AR16" s="14"/>
       <c r="AS16" s="8">
         <v>0.66587897628147696</v>
       </c>
@@ -2562,12 +3325,93 @@
       <c r="BE16" s="8">
         <v>1.82659217090046</v>
       </c>
+      <c r="BI16">
+        <v>1</v>
+      </c>
+      <c r="BJ16" s="12">
+        <v>0.16126202325479599</v>
+      </c>
+      <c r="BK16" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL16" s="12">
+        <v>0.77110968534415303</v>
+      </c>
+      <c r="BM16" s="12">
+        <v>13.5256583380775</v>
+      </c>
+      <c r="BN16" s="12">
+        <v>5.2010880288461196</v>
+      </c>
+      <c r="BO16" s="12">
+        <v>8.0631011627398302E-2</v>
+      </c>
+      <c r="BP16" s="12">
+        <v>0.16126202325479599</v>
+      </c>
+      <c r="BQ16" s="12">
+        <v>0</v>
+      </c>
+      <c r="BR16" s="12">
+        <v>0.228890314655846</v>
+      </c>
+      <c r="BS16" s="12">
+        <v>21.0334950450215</v>
+      </c>
+      <c r="BT16" s="12">
+        <v>3.8256506851297404E-9</v>
+      </c>
+      <c r="BU16" s="12">
+        <v>-5.2010880288461196</v>
+      </c>
+      <c r="BW16">
+        <v>1</v>
+      </c>
+      <c r="BX16" s="12">
+        <v>0.161261997003911</v>
+      </c>
+      <c r="BY16" s="12">
+        <v>0</v>
+      </c>
+      <c r="BZ16" s="12">
+        <v>0.77110968534416402</v>
+      </c>
+      <c r="CA16" s="12">
+        <v>8.0630998501955806E-2</v>
+      </c>
+      <c r="CB16" s="12">
+        <v>0.161261997003911</v>
+      </c>
+      <c r="CC16" s="12">
+        <v>0</v>
+      </c>
+      <c r="CD16" s="12">
+        <v>0.22889031465583501</v>
+      </c>
+      <c r="CE16" s="12">
+        <v>0.889974312015411</v>
+      </c>
+      <c r="CF16" s="12">
+        <v>0.31122072394383099</v>
+      </c>
+      <c r="CG16" s="12">
+        <v>0.31122072394383099</v>
+      </c>
+      <c r="CH16" s="12">
+        <v>0.119675225064805</v>
+      </c>
+      <c r="CI16" s="12">
+        <v>-8.6787497255436097E-7</v>
+      </c>
+      <c r="CJ16" s="12">
+        <v>-5.2010863355379202</v>
+      </c>
     </row>
-    <row r="17" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="17" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AB17" s="2">
         <v>14</v>
       </c>
-      <c r="AC17" s="18"/>
+      <c r="AC17" s="17"/>
       <c r="AD17" s="8">
         <v>1.18990459300586</v>
       </c>
@@ -2607,7 +3451,7 @@
       <c r="AQ17" s="2">
         <v>7</v>
       </c>
-      <c r="AR17" s="15"/>
+      <c r="AR17" s="14"/>
       <c r="AS17" s="8">
         <v>0.72887472331885494</v>
       </c>
@@ -2647,12 +3491,93 @@
       <c r="BE17" s="8">
         <v>-1.6136176573428</v>
       </c>
+      <c r="BI17">
+        <v>2</v>
+      </c>
+      <c r="BJ17" s="12">
+        <v>0.16126202323566799</v>
+      </c>
+      <c r="BK17" s="12">
+        <v>2.60054403817724E-2</v>
+      </c>
+      <c r="BL17" s="12">
+        <v>0.70348139366672402</v>
+      </c>
+      <c r="BM17" s="12">
+        <v>1.6774759688512499</v>
+      </c>
+      <c r="BN17" s="12">
+        <v>0.54102629263134505</v>
+      </c>
+      <c r="BO17" s="12">
+        <v>5.0000000456715699E-3</v>
+      </c>
+      <c r="BP17" s="12">
+        <v>1.9128254535871699E-11</v>
+      </c>
+      <c r="BQ17" s="12">
+        <v>2.60054403817724E-2</v>
+      </c>
+      <c r="BR17" s="12">
+        <v>6.7628291677428898E-2</v>
+      </c>
+      <c r="BS17" s="12">
+        <v>8.7149911392387391</v>
+      </c>
+      <c r="BT17" s="12">
+        <v>-1.6774759692492001</v>
+      </c>
+      <c r="BU17" s="12">
+        <v>4.8742240105203998E-8</v>
+      </c>
+      <c r="BW17">
+        <v>2</v>
+      </c>
+      <c r="BX17" s="12">
+        <v>0.29283623893224098</v>
+      </c>
+      <c r="BY17" s="12">
+        <v>5.0594883705819001E-2</v>
+      </c>
+      <c r="BZ17" s="12">
+        <v>0.62369034091422404</v>
+      </c>
+      <c r="CA17" s="12">
+        <v>8.1284567211131906E-2</v>
+      </c>
+      <c r="CB17" s="12">
+        <v>0.13157424192832901</v>
+      </c>
+      <c r="CC17" s="12">
+        <v>5.0594883705819001E-2</v>
+      </c>
+      <c r="CD17" s="12">
+        <v>0.14741934442993901</v>
+      </c>
+      <c r="CE17" s="12">
+        <v>7.4122941351074695E-2</v>
+      </c>
+      <c r="CF17" s="12">
+        <v>3.76102590906651E-2</v>
+      </c>
+      <c r="CG17" s="12">
+        <v>3.76102590906651E-2</v>
+      </c>
+      <c r="CH17" s="12">
+        <v>2.7915023183664001E-2</v>
+      </c>
+      <c r="CI17" s="12">
+        <v>2.70390805506895</v>
+      </c>
+      <c r="CJ17" s="12">
+        <v>-7.0316358252323097</v>
+      </c>
     </row>
-    <row r="18" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="18" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ18" s="2">
         <v>8</v>
       </c>
-      <c r="AR18" s="15"/>
+      <c r="AR18" s="14"/>
       <c r="AS18" s="8">
         <v>0.79028554486773805</v>
       </c>
@@ -2692,12 +3617,93 @@
       <c r="BE18" s="8">
         <v>-2.7396843012288099</v>
       </c>
+      <c r="BI18">
+        <v>3</v>
+      </c>
+      <c r="BJ18" s="12">
+        <v>0.31220393983004902</v>
+      </c>
+      <c r="BK18" s="12">
+        <v>7.4687834081666099E-2</v>
+      </c>
+      <c r="BL18" s="12">
+        <v>0.52497205251739099</v>
+      </c>
+      <c r="BM18" s="12">
+        <v>12.195711278238001</v>
+      </c>
+      <c r="BN18" s="12">
+        <v>8.9640981915243696</v>
+      </c>
+      <c r="BO18" s="12">
+        <v>8.99815671861732E-2</v>
+      </c>
+      <c r="BP18" s="12">
+        <v>0.15094191659438</v>
+      </c>
+      <c r="BQ18" s="12">
+        <v>4.8682393699893599E-2</v>
+      </c>
+      <c r="BR18" s="12">
+        <v>0.17850934114933301</v>
+      </c>
+      <c r="BS18" s="12">
+        <v>22.862763185667198</v>
+      </c>
+      <c r="BT18" s="12">
+        <v>1.4696430144053101</v>
+      </c>
+      <c r="BU18" s="12">
+        <v>-4.5566931927477397</v>
+      </c>
+      <c r="BW18">
+        <v>3</v>
+      </c>
+      <c r="BX18" s="12">
+        <v>0.34461574321913802</v>
+      </c>
+      <c r="BY18" s="12">
+        <v>0.12707844660439399</v>
+      </c>
+      <c r="BZ18" s="12">
+        <v>0.43644816200094999</v>
+      </c>
+      <c r="CA18" s="12">
+        <v>0.80854906978283503</v>
+      </c>
+      <c r="CB18" s="12">
+        <v>5.1779504286897302E-2</v>
+      </c>
+      <c r="CC18" s="12">
+        <v>7.6483562898575205E-2</v>
+      </c>
+      <c r="CD18" s="12">
+        <v>0.18724217891327399</v>
+      </c>
+      <c r="CE18" s="12">
+        <v>3.7154521547913703E-2</v>
+      </c>
+      <c r="CF18" s="12">
+        <v>2.8008931054787901E-2</v>
+      </c>
+      <c r="CG18" s="12">
+        <v>2.8008931054787901E-2</v>
+      </c>
+      <c r="CH18" s="12">
+        <v>2.5421394823475399E-2</v>
+      </c>
+      <c r="CI18" s="12">
+        <v>-2.4574341332943801</v>
+      </c>
+      <c r="CJ18" s="12">
+        <v>1.66368722598302</v>
+      </c>
     </row>
-    <row r="19" spans="28:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="28:88" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AQ19" s="2">
         <v>9</v>
       </c>
-      <c r="AR19" s="15"/>
+      <c r="AR19" s="14"/>
       <c r="AS19" s="8">
         <v>0.79028554376212101</v>
       </c>
@@ -2737,12 +3743,93 @@
       <c r="BE19" s="8">
         <v>-2.7396843642646802</v>
       </c>
+      <c r="BI19">
+        <v>19</v>
+      </c>
+      <c r="BJ19" s="12">
+        <v>0.99937713855888</v>
+      </c>
+      <c r="BK19" s="12">
+        <v>0.998519812800576</v>
+      </c>
+      <c r="BL19" s="12">
+        <v>5.9035154144538001E-6</v>
+      </c>
+      <c r="BM19" s="12">
+        <v>0.23032852664721701</v>
+      </c>
+      <c r="BN19" s="12">
+        <v>0.68393304572477498</v>
+      </c>
+      <c r="BO19" s="12">
+        <v>2.3474507894686498</v>
+      </c>
+      <c r="BP19" s="12">
+        <v>1.6041171532553002E-2</v>
+      </c>
+      <c r="BQ19" s="12">
+        <v>3.1636926052801898E-2</v>
+      </c>
+      <c r="BR19" s="12">
+        <v>2.7223186625203002E-4</v>
+      </c>
+      <c r="BS19" s="12">
+        <v>26.412575133412901</v>
+      </c>
+      <c r="BT19" s="12">
+        <v>9.2636674371454605E-2</v>
+      </c>
+      <c r="BU19" s="12">
+        <v>-4.6970454711958702E-2</v>
+      </c>
+      <c r="BW19">
+        <v>11</v>
+      </c>
+      <c r="BX19" s="12">
+        <v>1.0007949049656</v>
+      </c>
+      <c r="BY19" s="12">
+        <v>1.00138922492001</v>
+      </c>
+      <c r="BZ19" s="12">
+        <v>4.6806973891805803E-6</v>
+      </c>
+      <c r="CA19" s="12">
+        <v>2.1737022153313301</v>
+      </c>
+      <c r="CB19" s="12">
+        <v>1.0330525888837001E-2</v>
+      </c>
+      <c r="CC19" s="12">
+        <v>2.1085581076135899E-2</v>
+      </c>
+      <c r="CD19" s="12">
+        <v>1.37519037431822E-4</v>
+      </c>
+      <c r="CE19" s="12">
+        <v>0.50384366306091799</v>
+      </c>
+      <c r="CF19" s="12">
+        <v>0.99323845822811596</v>
+      </c>
+      <c r="CG19" s="12">
+        <v>0.99323845822811596</v>
+      </c>
+      <c r="CH19" s="12">
+        <v>1.96499377812383</v>
+      </c>
+      <c r="CI19" s="12">
+        <v>8.2140543290684001E-2</v>
+      </c>
+      <c r="CJ19" s="12">
+        <v>-4.0243377019510897E-2</v>
+      </c>
     </row>
-    <row r="20" spans="28:57" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="28:88" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AQ20" s="2">
         <v>10</v>
       </c>
-      <c r="AR20" s="15"/>
+      <c r="AR20" s="14"/>
       <c r="AS20" s="8">
         <v>0.95785290430231196</v>
       </c>
@@ -2782,12 +3869,93 @@
       <c r="BE20" s="8">
         <v>-0.77396133726206295</v>
       </c>
+      <c r="BI20">
+        <v>20</v>
+      </c>
+      <c r="BJ20" s="12">
+        <v>0.99928455094657198</v>
+      </c>
+      <c r="BK20" s="12">
+        <v>0.99856675837888298</v>
+      </c>
+      <c r="BL20" s="12">
+        <v>5.1268266846412101E-7</v>
+      </c>
+      <c r="BM20" s="12">
+        <v>2.8604208522304203E-4</v>
+      </c>
+      <c r="BN20" s="12">
+        <v>5.7286136966234601E-4</v>
+      </c>
+      <c r="BO20" s="12">
+        <v>9.9947038185881597E-4</v>
+      </c>
+      <c r="BP20" s="12">
+        <v>9.2587612308125901E-5</v>
+      </c>
+      <c r="BQ20" s="12">
+        <v>4.6945578307089301E-5</v>
+      </c>
+      <c r="BR20" s="12">
+        <v>5.3908327459896799E-6</v>
+      </c>
+      <c r="BS20" s="12">
+        <v>18.486635817666102</v>
+      </c>
+      <c r="BT20" s="12">
+        <v>-2.8956261499824497E-4</v>
+      </c>
+      <c r="BU20" s="12">
+        <v>-5.7107632194241999E-4</v>
+      </c>
+      <c r="BW20">
+        <v>12</v>
+      </c>
+      <c r="BX20" s="12">
+        <v>0.99992821901524498</v>
+      </c>
+      <c r="BY20" s="12">
+        <v>0.99985329023192504</v>
+      </c>
+      <c r="BZ20" s="12">
+        <v>6.14661982001474E-9</v>
+      </c>
+      <c r="CA20" s="12">
+        <v>0.61261905930059801</v>
+      </c>
+      <c r="CB20" s="12">
+        <v>8.6668595036032403E-4</v>
+      </c>
+      <c r="CC20" s="12">
+        <v>1.53593468809187E-3</v>
+      </c>
+      <c r="CD20" s="12">
+        <v>4.6745507693605596E-6</v>
+      </c>
+      <c r="CE20" s="12">
+        <v>0.44094644071306199</v>
+      </c>
+      <c r="CF20" s="12">
+        <v>0.88002201057075002</v>
+      </c>
+      <c r="CG20" s="12">
+        <v>0.88002201057075002</v>
+      </c>
+      <c r="CH20" s="12">
+        <v>1.7612015669310599</v>
+      </c>
+      <c r="CI20" s="12">
+        <v>1.1175279314074599E-3</v>
+      </c>
+      <c r="CJ20" s="12">
+        <v>-6.3059021484512801E-4</v>
+      </c>
     </row>
-    <row r="21" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="21" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ21" s="2">
         <v>11</v>
       </c>
-      <c r="AR21" s="15"/>
+      <c r="AR21" s="14"/>
       <c r="AS21" s="8">
         <v>0.95292153181586203</v>
       </c>
@@ -2827,12 +3995,93 @@
       <c r="BE21" s="8">
         <v>-0.149999915133469</v>
       </c>
+      <c r="BI21">
+        <v>21</v>
+      </c>
+      <c r="BJ21" s="12">
+        <v>1.00000010852147</v>
+      </c>
+      <c r="BK21" s="12">
+        <v>0.99999981775583702</v>
+      </c>
+      <c r="BL21" s="12">
+        <v>1.59547980694456E-11</v>
+      </c>
+      <c r="BM21" s="12">
+        <v>-1.3763639723012199E-4</v>
+      </c>
+      <c r="BN21" s="12">
+        <v>1.2450903405950901E-4</v>
+      </c>
+      <c r="BO21" s="12">
+        <v>2.5015814520687099</v>
+      </c>
+      <c r="BP21" s="12">
+        <v>7.1555757490493401E-4</v>
+      </c>
+      <c r="BQ21" s="12">
+        <v>1.43305937695403E-3</v>
+      </c>
+      <c r="BR21" s="12">
+        <v>5.1266671366605095E-7</v>
+      </c>
+      <c r="BS21" s="12">
+        <v>92.866793907337595</v>
+      </c>
+      <c r="BT21" s="12">
+        <v>1.5993191198684399E-4</v>
+      </c>
+      <c r="BU21" s="12">
+        <v>-7.9857425849816298E-5</v>
+      </c>
+      <c r="BW21">
+        <v>13</v>
+      </c>
+      <c r="BX21" s="12">
+        <v>0.99999958874844697</v>
+      </c>
+      <c r="BY21" s="12">
+        <v>0.99999926813157203</v>
+      </c>
+      <c r="BZ21" s="12">
+        <v>9.9058925982611292E-13</v>
+      </c>
+      <c r="CA21" s="12">
+        <v>1.14810068809885</v>
+      </c>
+      <c r="CB21" s="12">
+        <v>7.1369733202208895E-5</v>
+      </c>
+      <c r="CC21" s="12">
+        <v>1.45977899646876E-4</v>
+      </c>
+      <c r="CD21" s="12">
+        <v>6.1456292307549203E-9</v>
+      </c>
+      <c r="CE21" s="12">
+        <v>0.49916526765783997</v>
+      </c>
+      <c r="CF21" s="12">
+        <v>0.998444534138343</v>
+      </c>
+      <c r="CG21" s="12">
+        <v>0.998444534138343</v>
+      </c>
+      <c r="CH21" s="12">
+        <v>2.0020840241028401</v>
+      </c>
+      <c r="CI21" s="12">
+        <v>-3.7076291754952299E-5</v>
+      </c>
+      <c r="CJ21" s="12">
+        <v>1.8126901779602599E-5</v>
+      </c>
     </row>
-    <row r="22" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="22" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ22" s="2">
         <v>12</v>
       </c>
-      <c r="AR22" s="15"/>
+      <c r="AR22" s="14"/>
       <c r="AS22" s="8">
         <v>0.99337845476188302</v>
       </c>
@@ -2872,12 +4121,30 @@
       <c r="BE22" s="8">
         <v>-0.25046661511505203</v>
       </c>
+      <c r="BI22" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="BJ22" s="12"/>
+      <c r="BK22" s="12"/>
+      <c r="BL22" s="12"/>
+      <c r="BM22" s="12"/>
+      <c r="BN22" s="12"/>
+      <c r="BO22" s="12"/>
+      <c r="BP22" s="12"/>
+      <c r="BQ22" s="12"/>
+      <c r="BR22" s="12"/>
+      <c r="BS22" s="12"/>
+      <c r="BT22" s="12"/>
+      <c r="BU22" s="12"/>
+      <c r="BW22" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="23" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="23" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ23" s="2">
         <v>13</v>
       </c>
-      <c r="AR23" s="15"/>
+      <c r="AR23" s="14"/>
       <c r="AS23" s="8">
         <v>0.99479366199113395</v>
       </c>
@@ -2917,12 +4184,93 @@
       <c r="BE23" s="8">
         <v>1.1277229361494801E-2</v>
       </c>
+      <c r="BI23" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK23" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL23" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM23" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN23" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP23" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ23" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR23" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS23" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT23" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BW23" t="s">
+        <v>0</v>
+      </c>
+      <c r="BX23" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BY23" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BZ23" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="CA23" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB23" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="CC23" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="CD23" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="CE23" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF23" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG23" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="CH23" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="CI23" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="CJ23" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="24" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="24" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ24" s="2">
         <v>14</v>
       </c>
-      <c r="AR24" s="15"/>
+      <c r="AR24" s="14"/>
       <c r="AS24" s="8">
         <v>0.99990757024690202</v>
       </c>
@@ -2962,12 +4310,93 @@
       <c r="BE24" s="8">
         <v>-7.7835385198676797E-3</v>
       </c>
+      <c r="BI24">
+        <v>1</v>
+      </c>
+      <c r="BJ24" s="12">
+        <v>2.8117928404913801</v>
+      </c>
+      <c r="BK24" s="12">
+        <v>7.9097158519495903</v>
+      </c>
+      <c r="BL24" s="12">
+        <v>3.2838442447035301</v>
+      </c>
+      <c r="BM24" s="12">
+        <v>0.35414654897318398</v>
+      </c>
+      <c r="BN24" s="12">
+        <v>-0.70750041901471905</v>
+      </c>
+      <c r="BO24" s="12">
+        <v>-1.9097158519495901E-3</v>
+      </c>
+      <c r="BP24" s="12">
+        <v>3.8117928404913801</v>
+      </c>
+      <c r="BQ24" s="12">
+        <v>1.90971585194959</v>
+      </c>
+      <c r="BR24" s="24">
+        <v>2500.7161557552899</v>
+      </c>
+      <c r="BS24" s="12">
+        <v>133.83969189462701</v>
+      </c>
+      <c r="BT24" s="12">
+        <v>-0.35439724021890601</v>
+      </c>
+      <c r="BU24" s="12">
+        <v>0.70737482219822501</v>
+      </c>
+      <c r="BW24">
+        <v>1</v>
+      </c>
+      <c r="BX24" s="12">
+        <v>2.8118287642430699</v>
+      </c>
+      <c r="BY24" s="12">
+        <v>7.9097338498211798</v>
+      </c>
+      <c r="BZ24" s="12">
+        <v>3.28384763151668</v>
+      </c>
+      <c r="CA24" s="12">
+        <v>-1.9097338498211801E-3</v>
+      </c>
+      <c r="CB24" s="12">
+        <v>3.8118287642430699</v>
+      </c>
+      <c r="CC24" s="12">
+        <v>1.90973384982118</v>
+      </c>
+      <c r="CD24" s="24">
+        <v>2500.7161523684799</v>
+      </c>
+      <c r="CE24" s="12">
+        <v>0.198875982383489</v>
+      </c>
+      <c r="CF24" s="12">
+        <v>-0.40106654693810401</v>
+      </c>
+      <c r="CG24" s="12">
+        <v>-0.40106654693810401</v>
+      </c>
+      <c r="CH24" s="12">
+        <v>0.79921413971406596</v>
+      </c>
+      <c r="CI24" s="12">
+        <v>-0.14739894625633601</v>
+      </c>
+      <c r="CJ24" s="12">
+        <v>0.670570079283905</v>
+      </c>
     </row>
-    <row r="25" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="25" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ25" s="2">
         <v>15</v>
       </c>
-      <c r="AR25" s="15"/>
+      <c r="AR25" s="14"/>
       <c r="AS25" s="8">
         <v>0.99998158963223704</v>
       </c>
@@ -3007,12 +4436,93 @@
       <c r="BE25" s="8">
         <v>6.9418193260339906E-5</v>
       </c>
+      <c r="BI25">
+        <v>2</v>
+      </c>
+      <c r="BJ25" s="12">
+        <v>2.8119449397826699</v>
+      </c>
+      <c r="BK25" s="12">
+        <v>7.9094122626522596</v>
+      </c>
+      <c r="BL25" s="12">
+        <v>3.2837099143400401</v>
+      </c>
+      <c r="BM25" s="12">
+        <v>-0.31105252015509299</v>
+      </c>
+      <c r="BN25" s="12">
+        <v>-1.7494415937635599</v>
+      </c>
+      <c r="BO25" s="12">
+        <v>4.2917741457163103E-4</v>
+      </c>
+      <c r="BP25" s="12">
+        <v>1.5209929128845399E-4</v>
+      </c>
+      <c r="BQ25" s="12">
+        <v>3.0358929732443498E-4</v>
+      </c>
+      <c r="BR25" s="12">
+        <v>1.34330363492196E-4</v>
+      </c>
+      <c r="BS25" s="12">
+        <v>170.51063210856901</v>
+      </c>
+      <c r="BT25" s="12">
+        <v>0.949259766443877</v>
+      </c>
+      <c r="BU25" s="12">
+        <v>0.47558365657902602</v>
+      </c>
+      <c r="BW25">
+        <v>2</v>
+      </c>
+      <c r="BX25" s="12">
+        <v>2.8119566981232502</v>
+      </c>
+      <c r="BY25" s="12">
+        <v>7.9094786120837197</v>
+      </c>
+      <c r="BZ25" s="12">
+        <v>3.2837526308423199</v>
+      </c>
+      <c r="CA25" s="12">
+        <v>4.2893791553871098E-4</v>
+      </c>
+      <c r="CB25" s="12">
+        <v>1.2793388017717699E-4</v>
+      </c>
+      <c r="CC25" s="12">
+        <v>2.5523773745650402E-4</v>
+      </c>
+      <c r="CD25" s="12">
+        <v>9.5000674357414899E-5</v>
+      </c>
+      <c r="CE25" s="12">
+        <v>-7.8488962461431501E-5</v>
+      </c>
+      <c r="CF25" s="12">
+        <v>-1.09771515115875E-3</v>
+      </c>
+      <c r="CG25" s="12">
+        <v>-1.09771515115875E-3</v>
+      </c>
+      <c r="CH25" s="12">
+        <v>-4.8646292563619903E-3</v>
+      </c>
+      <c r="CI25" s="12">
+        <v>0.94902275649548995</v>
+      </c>
+      <c r="CJ25" s="12">
+        <v>0.47562799269567002</v>
+      </c>
     </row>
-    <row r="26" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="26" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ26" s="2">
         <v>1</v>
       </c>
-      <c r="AR26" s="14" t="s">
+      <c r="AR26" s="13" t="s">
         <v>18</v>
       </c>
       <c r="AS26" s="8">
@@ -3054,12 +4564,93 @@
       <c r="BE26" s="8">
         <v>-0.34224656121810598</v>
       </c>
+      <c r="BI26">
+        <v>3</v>
+      </c>
+      <c r="BJ26" s="12">
+        <v>2.60784935453038</v>
+      </c>
+      <c r="BK26" s="12">
+        <v>6.7615247426738403</v>
+      </c>
+      <c r="BL26" s="12">
+        <v>2.7400494473810402</v>
+      </c>
+      <c r="BM26" s="12">
+        <v>-602.068338399656</v>
+      </c>
+      <c r="BN26" s="24">
+        <v>-3129.3519608616498</v>
+      </c>
+      <c r="BO26" s="12">
+        <v>0.65614509456642001</v>
+      </c>
+      <c r="BP26" s="12">
+        <v>0.20409558525228699</v>
+      </c>
+      <c r="BQ26" s="12">
+        <v>1.14788751997842</v>
+      </c>
+      <c r="BR26" s="12">
+        <v>0.54366046695899495</v>
+      </c>
+      <c r="BS26" s="12">
+        <v>169.799186914437</v>
+      </c>
+      <c r="BT26" s="12">
+        <v>44.266912360793299</v>
+      </c>
+      <c r="BU26" s="12">
+        <v>-7.8707026501392701</v>
+      </c>
+      <c r="BW26">
+        <v>3</v>
+      </c>
+      <c r="BX26" s="12">
+        <v>2.6079456978471698</v>
+      </c>
+      <c r="BY26" s="12">
+        <v>6.7620257306980998</v>
+      </c>
+      <c r="BZ26" s="12">
+        <v>2.7403712233405999</v>
+      </c>
+      <c r="CA26" s="12">
+        <v>-341.96074754881897</v>
+      </c>
+      <c r="CB26" s="12">
+        <v>0.20401100027608099</v>
+      </c>
+      <c r="CC26" s="12">
+        <v>1.14745288138561</v>
+      </c>
+      <c r="CD26" s="12">
+        <v>0.54338140750171704</v>
+      </c>
+      <c r="CE26" s="12">
+        <v>0.101846153986525</v>
+      </c>
+      <c r="CF26" s="12">
+        <v>0.55305008903339004</v>
+      </c>
+      <c r="CG26" s="12">
+        <v>0.55305008903339004</v>
+      </c>
+      <c r="CH26" s="12">
+        <v>3.0079473855598202</v>
+      </c>
+      <c r="CI26" s="12">
+        <v>44.2702061839518</v>
+      </c>
+      <c r="CJ26" s="12">
+        <v>-7.8710064442958503</v>
+      </c>
     </row>
-    <row r="27" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="27" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ27" s="2">
         <v>2</v>
       </c>
-      <c r="AR27" s="15"/>
+      <c r="AR27" s="14"/>
       <c r="AS27" s="8">
         <v>0.655522854730612</v>
       </c>
@@ -3099,12 +4690,93 @@
       <c r="BE27" s="8">
         <v>-2.2614002533198101</v>
       </c>
+      <c r="BI27">
+        <v>30</v>
+      </c>
+      <c r="BJ27" s="12">
+        <v>1.0007614358523</v>
+      </c>
+      <c r="BK27" s="12">
+        <v>1.0015265064807399</v>
+      </c>
+      <c r="BL27" s="12">
+        <v>5.8071785453073599E-7</v>
+      </c>
+      <c r="BM27" s="12">
+        <v>-3.0371771278903201E-4</v>
+      </c>
+      <c r="BN27" s="12">
+        <v>-6.0914615162501297E-4</v>
+      </c>
+      <c r="BO27" s="12">
+        <v>9.9710920486817097E-4</v>
+      </c>
+      <c r="BP27" s="12">
+        <v>9.8657794308731799E-5</v>
+      </c>
+      <c r="BQ27" s="12">
+        <v>4.8429635840063699E-5</v>
+      </c>
+      <c r="BR27" s="12">
+        <v>6.0566656471654496E-6</v>
+      </c>
+      <c r="BS27" s="12">
+        <v>161.522543858777</v>
+      </c>
+      <c r="BT27" s="12">
+        <v>2.9994460165907202E-4</v>
+      </c>
+      <c r="BU27" s="12">
+        <v>6.1099831545341401E-4</v>
+      </c>
+      <c r="BW27">
+        <v>22</v>
+      </c>
+      <c r="BX27" s="12">
+        <v>1.00082577196609</v>
+      </c>
+      <c r="BY27" s="12">
+        <v>1.0014477637194401</v>
+      </c>
+      <c r="BZ27" s="12">
+        <v>4.8623748677426402E-6</v>
+      </c>
+      <c r="CA27" s="12">
+        <v>1.33961360985607</v>
+      </c>
+      <c r="CB27" s="12">
+        <v>1.1673191235030699E-2</v>
+      </c>
+      <c r="CC27" s="12">
+        <v>2.3837114315713202E-2</v>
+      </c>
+      <c r="CD27" s="12">
+        <v>1.5307067551538199E-4</v>
+      </c>
+      <c r="CE27" s="12">
+        <v>0.49845839873528403</v>
+      </c>
+      <c r="CF27" s="12">
+        <v>1.0028155283242499</v>
+      </c>
+      <c r="CG27" s="12">
+        <v>1.0028155283242499</v>
+      </c>
+      <c r="CH27" s="12">
+        <v>2.02275791161403</v>
+      </c>
+      <c r="CI27" s="12">
+        <v>8.3503924397642607E-2</v>
+      </c>
+      <c r="CJ27" s="12">
+        <v>-4.0892422416671702E-2</v>
+      </c>
     </row>
-    <row r="28" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="28" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ28" s="2">
         <v>3</v>
       </c>
-      <c r="AR28" s="15"/>
+      <c r="AR28" s="14"/>
       <c r="AS28" s="8">
         <v>0.75545537277409003</v>
       </c>
@@ -3144,12 +4816,93 @@
       <c r="BE28" s="8">
         <v>-3.2613655886736899</v>
       </c>
+      <c r="BI28">
+        <v>31</v>
+      </c>
+      <c r="BJ28" s="12">
+        <v>1.0000003672316899</v>
+      </c>
+      <c r="BK28" s="12">
+        <v>1.00000008243022</v>
+      </c>
+      <c r="BL28" s="12">
+        <v>4.2649600275067001E-11</v>
+      </c>
+      <c r="BM28" s="12">
+        <v>-3.1754247566665399E-4</v>
+      </c>
+      <c r="BN28" s="12">
+        <v>1.8102061013164299E-5</v>
+      </c>
+      <c r="BO28" s="12">
+        <v>2.50584206507054</v>
+      </c>
+      <c r="BP28" s="12">
+        <v>7.6106862061386905E-4</v>
+      </c>
+      <c r="BQ28" s="12">
+        <v>1.52642405051772E-3</v>
+      </c>
+      <c r="BR28" s="12">
+        <v>5.8067520493046098E-7</v>
+      </c>
+      <c r="BS28" s="12">
+        <v>131.73729391120699</v>
+      </c>
+      <c r="BT28" s="12">
+        <v>2.6154787526297602E-4</v>
+      </c>
+      <c r="BU28" s="12">
+        <v>-1.3040665804986399E-4</v>
+      </c>
+      <c r="BW28">
+        <v>23</v>
+      </c>
+      <c r="BX28" s="12">
+        <v>1.00020397219419</v>
+      </c>
+      <c r="BY28" s="12">
+        <v>1.0004140222826401</v>
+      </c>
+      <c r="BZ28" s="12">
+        <v>4.52483352083879E-8</v>
+      </c>
+      <c r="CA28" s="12">
+        <v>1.0099460044713</v>
+      </c>
+      <c r="CB28" s="12">
+        <v>6.2179977189424896E-4</v>
+      </c>
+      <c r="CC28" s="12">
+        <v>1.0337414367982401E-3</v>
+      </c>
+      <c r="CD28" s="12">
+        <v>4.8171265325342501E-6</v>
+      </c>
+      <c r="CE28" s="12">
+        <v>-35.964081834509301</v>
+      </c>
+      <c r="CF28" s="12">
+        <v>-73.063404702962899</v>
+      </c>
+      <c r="CG28" s="12">
+        <v>-73.063404702962899</v>
+      </c>
+      <c r="CH28" s="12">
+        <v>-148.42767544431101</v>
+      </c>
+      <c r="CI28" s="12">
+        <v>-2.0070639420324199E-3</v>
+      </c>
+      <c r="CJ28" s="12">
+        <v>1.2072579181676699E-3</v>
+      </c>
     </row>
-    <row r="29" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="29" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ29" s="2">
         <v>4</v>
       </c>
-      <c r="AR29" s="15"/>
+      <c r="AR29" s="14"/>
       <c r="AS29" s="8">
         <v>0.75545536437519001</v>
       </c>
@@ -3189,12 +4942,93 @@
       <c r="BE29" s="8">
         <v>-3.26136668365932</v>
       </c>
+      <c r="BI29">
+        <v>32</v>
+      </c>
+      <c r="BJ29" s="12">
+        <v>1.0000001061018</v>
+      </c>
+      <c r="BK29" s="12">
+        <v>1.0000002126284799</v>
+      </c>
+      <c r="BL29" s="12">
+        <v>1.12756434857136E-14</v>
+      </c>
+      <c r="BM29" s="12">
+        <v>-4.2284172905442002E-8</v>
+      </c>
+      <c r="BN29" s="12">
+        <v>-8.4959744602883097E-8</v>
+      </c>
+      <c r="BO29" s="12">
+        <v>9.9840188130423196E-4</v>
+      </c>
+      <c r="BP29" s="12">
+        <v>2.6112989082171998E-7</v>
+      </c>
+      <c r="BQ29" s="12">
+        <v>1.30198252623614E-7</v>
+      </c>
+      <c r="BR29" s="12">
+        <v>4.26383246315813E-11</v>
+      </c>
+      <c r="BS29" s="12">
+        <v>161.45937521634599</v>
+      </c>
+      <c r="BT29" s="12">
+        <v>4.2256594843809102E-8</v>
+      </c>
+      <c r="BU29" s="12">
+        <v>8.4973494907103394E-8</v>
+      </c>
+      <c r="BW29">
+        <v>24</v>
+      </c>
+      <c r="BX29" s="12">
+        <v>1.0000007858962501</v>
+      </c>
+      <c r="BY29" s="12">
+        <v>1.0000013193588999</v>
+      </c>
+      <c r="BZ29" s="12">
+        <v>6.9899361429181104E-12</v>
+      </c>
+      <c r="CA29" s="12">
+        <v>-1.26799952458501E-2</v>
+      </c>
+      <c r="CB29" s="12">
+        <v>2.0318629794813199E-4</v>
+      </c>
+      <c r="CC29" s="12">
+        <v>4.1270292373907198E-4</v>
+      </c>
+      <c r="CD29" s="12">
+        <v>4.5241345272245001E-8</v>
+      </c>
+      <c r="CE29" s="12">
+        <v>0.50001552274897398</v>
+      </c>
+      <c r="CF29" s="12">
+        <v>1.00022185237523</v>
+      </c>
+      <c r="CG29" s="12">
+        <v>1.00022185237523</v>
+      </c>
+      <c r="CH29" s="12">
+        <v>2.00579682253146</v>
+      </c>
+      <c r="CI29" s="12">
+        <v>1.02545557356321E-4</v>
+      </c>
+      <c r="CJ29" s="12">
+        <v>-5.0486842750885303E-5</v>
+      </c>
     </row>
-    <row r="30" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="30" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ30" s="2">
         <v>5</v>
       </c>
-      <c r="AR30" s="15"/>
+      <c r="AR30" s="14"/>
       <c r="AS30" s="8">
         <v>0.915370720424591</v>
       </c>
@@ -3234,12 +5068,24 @@
       <c r="BE30" s="8">
         <v>-1.5777900868878501</v>
       </c>
+      <c r="BJ30" s="12"/>
+      <c r="BK30" s="12"/>
+      <c r="BL30" s="12"/>
+      <c r="BM30" s="12"/>
+      <c r="BN30" s="12"/>
+      <c r="BO30" s="12"/>
+      <c r="BP30" s="12"/>
+      <c r="BQ30" s="12"/>
+      <c r="BR30" s="12"/>
+      <c r="BS30" s="12"/>
+      <c r="BT30" s="12"/>
+      <c r="BU30" s="12"/>
     </row>
-    <row r="31" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="31" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ31" s="2">
         <v>6</v>
       </c>
-      <c r="AR31" s="15"/>
+      <c r="AR31" s="14"/>
       <c r="AS31" s="8">
         <v>0.90698818162734796</v>
       </c>
@@ -3279,12 +5125,29 @@
       <c r="BE31" s="8">
         <v>-0.23465014284222899</v>
       </c>
+      <c r="BJ31" s="12"/>
+      <c r="BK31" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="BL31" s="12"/>
+      <c r="BM31" s="12"/>
+      <c r="BN31" s="12"/>
+      <c r="BO31" s="12"/>
+      <c r="BP31" s="12"/>
+      <c r="BQ31" s="12"/>
+      <c r="BR31" s="12"/>
+      <c r="BS31" s="12"/>
+      <c r="BT31" s="12"/>
+      <c r="BU31" s="12"/>
+      <c r="BX31" s="12" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="32" spans="28:57" x14ac:dyDescent="0.25">
+    <row r="32" spans="28:88" x14ac:dyDescent="0.25">
       <c r="AQ32" s="2">
         <v>7</v>
       </c>
-      <c r="AR32" s="15"/>
+      <c r="AR32" s="14"/>
       <c r="AS32" s="8">
         <v>0.97030032391341603</v>
       </c>
@@ -3324,12 +5187,30 @@
       <c r="BE32" s="8">
         <v>-0.62890875681131897</v>
       </c>
+      <c r="BI32" t="s">
+        <v>38</v>
+      </c>
+      <c r="BJ32" s="12"/>
+      <c r="BK32" s="12"/>
+      <c r="BL32" s="12"/>
+      <c r="BM32" s="12"/>
+      <c r="BN32" s="12"/>
+      <c r="BO32" s="12"/>
+      <c r="BP32" s="12"/>
+      <c r="BQ32" s="12"/>
+      <c r="BR32" s="12"/>
+      <c r="BS32" s="12"/>
+      <c r="BT32" s="12"/>
+      <c r="BU32" s="12"/>
+      <c r="BW32" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="33" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="33" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ33" s="2">
         <v>8</v>
       </c>
-      <c r="AR33" s="15"/>
+      <c r="AR33" s="14"/>
       <c r="AS33" s="8">
         <v>0.97980724354348103</v>
       </c>
@@ -3369,12 +5250,93 @@
       <c r="BE33" s="8">
         <v>0.10697613269356999</v>
       </c>
+      <c r="BI33" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ33" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK33" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL33" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM33" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN33" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO33" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP33" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR33" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS33" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT33" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU33" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BW33" t="s">
+        <v>0</v>
+      </c>
+      <c r="BX33" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BY33" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BZ33" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="CA33" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB33" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="CC33" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="CD33" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="CE33" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF33" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG33" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="CH33" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="CI33" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="CJ33" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="34" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="34" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ34" s="2">
         <v>9</v>
       </c>
-      <c r="AR34" s="15"/>
+      <c r="AR34" s="14"/>
       <c r="AS34" s="8">
         <v>0.97980724294740595</v>
       </c>
@@ -3414,12 +5376,93 @@
       <c r="BE34" s="8">
         <v>0.10697613771109001</v>
       </c>
+      <c r="BI34">
+        <v>1</v>
+      </c>
+      <c r="BJ34" s="12">
+        <v>0.11724137931034399</v>
+      </c>
+      <c r="BK34" s="12">
+        <v>0</v>
+      </c>
+      <c r="BL34" s="12">
+        <v>0.79815677220227799</v>
+      </c>
+      <c r="BM34" s="12">
+        <v>5.5279037475398498</v>
+      </c>
+      <c r="BN34" s="12">
+        <v>2.7491082045184299</v>
+      </c>
+      <c r="BO34" s="12">
+        <v>5.8620689655172399E-2</v>
+      </c>
+      <c r="BP34" s="12">
+        <v>0.11724137931034399</v>
+      </c>
+      <c r="BQ34" s="12">
+        <v>0</v>
+      </c>
+      <c r="BR34" s="12">
+        <v>0.20184322779772099</v>
+      </c>
+      <c r="BS34" s="12">
+        <v>26.441837343965702</v>
+      </c>
+      <c r="BT34" s="12">
+        <v>-1.1208987658370499</v>
+      </c>
+      <c r="BU34" s="12">
+        <v>-2.7491082045184299</v>
+      </c>
+      <c r="BW34">
+        <v>1</v>
+      </c>
+      <c r="BX34" s="12">
+        <v>0.11724137931034399</v>
+      </c>
+      <c r="BY34" s="12">
+        <v>0</v>
+      </c>
+      <c r="BZ34" s="12">
+        <v>0.79815677220227799</v>
+      </c>
+      <c r="CA34" s="12">
+        <v>5.8620689655172399E-2</v>
+      </c>
+      <c r="CB34" s="12">
+        <v>0.11724137931034399</v>
+      </c>
+      <c r="CC34" s="12">
+        <v>0</v>
+      </c>
+      <c r="CD34" s="12">
+        <v>0.20184322779772099</v>
+      </c>
+      <c r="CE34" s="12">
+        <v>0.92945108820038003</v>
+      </c>
+      <c r="CF34" s="12">
+        <v>0.25456990680484698</v>
+      </c>
+      <c r="CG34" s="12">
+        <v>0.25456990680484698</v>
+      </c>
+      <c r="CH34" s="12">
+        <v>8.1405569589826102E-2</v>
+      </c>
+      <c r="CI34" s="12">
+        <v>-1.1208987658370499</v>
+      </c>
+      <c r="CJ34" s="12">
+        <v>-2.7491082045184299</v>
+      </c>
     </row>
-    <row r="35" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="35" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ35" s="2">
         <v>10</v>
       </c>
-      <c r="AR35" s="15"/>
+      <c r="AR35" s="14"/>
       <c r="AS35" s="8">
         <v>0.998321853102348</v>
       </c>
@@ -3459,12 +5502,93 @@
       <c r="BE35" s="8">
         <v>-5.4117184634483402E-2</v>
       </c>
+      <c r="BI35">
+        <v>2</v>
+      </c>
+      <c r="BJ35" s="12">
+        <v>0.13075937632335</v>
+      </c>
+      <c r="BK35" s="12">
+        <v>3.3154141685004399E-2</v>
+      </c>
+      <c r="BL35" s="12">
+        <v>0.781359183879206</v>
+      </c>
+      <c r="BM35" s="12">
+        <v>4.7350547119877797</v>
+      </c>
+      <c r="BN35" s="12">
+        <v>2.0784721770024701</v>
+      </c>
+      <c r="BO35" s="12">
+        <v>1.20599624381871E-2</v>
+      </c>
+      <c r="BP35" s="12">
+        <v>1.35179970130053E-2</v>
+      </c>
+      <c r="BQ35" s="12">
+        <v>3.3154141685004399E-2</v>
+      </c>
+      <c r="BR35" s="12">
+        <v>1.6797588323072699E-2</v>
+      </c>
+      <c r="BS35" s="12">
+        <v>9.4717141614335603</v>
+      </c>
+      <c r="BT35" s="12">
+        <v>-2.5782769182896801</v>
+      </c>
+      <c r="BU35" s="12">
+        <v>3.2112254377065899</v>
+      </c>
+      <c r="BW35">
+        <v>2</v>
+      </c>
+      <c r="BX35" s="12">
+        <v>0.26587746320829903</v>
+      </c>
+      <c r="BY35" s="12">
+        <v>4.3450796032099497E-2</v>
+      </c>
+      <c r="BZ35" s="12">
+        <v>0.61313781925114397</v>
+      </c>
+      <c r="CA35" s="12">
+        <v>8.5341579799156603E-2</v>
+      </c>
+      <c r="CB35" s="12">
+        <v>0.14863608389795399</v>
+      </c>
+      <c r="CC35" s="12">
+        <v>4.3450796032099497E-2</v>
+      </c>
+      <c r="CD35" s="12">
+        <v>0.18501895295113399</v>
+      </c>
+      <c r="CE35" s="12">
+        <v>0.109404238703595</v>
+      </c>
+      <c r="CF35" s="12">
+        <v>4.8281664156349602E-2</v>
+      </c>
+      <c r="CG35" s="12">
+        <v>4.8281664156349602E-2</v>
+      </c>
+      <c r="CH35" s="12">
+        <v>2.9512389241509299E-2</v>
+      </c>
+      <c r="CI35" s="12">
+        <v>1.42875889331468</v>
+      </c>
+      <c r="CJ35" s="12">
+        <v>-5.4480058819961901</v>
+      </c>
     </row>
-    <row r="36" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="36" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ36" s="2">
         <v>11</v>
       </c>
-      <c r="AR36" s="15"/>
+      <c r="AR36" s="14"/>
       <c r="AS36" s="8">
         <v>0.99971749419261002</v>
       </c>
@@ -3504,12 +5628,93 @@
       <c r="BE36" s="8">
         <v>2.7904849830617802E-3</v>
       </c>
+      <c r="BI36">
+        <v>3</v>
+      </c>
+      <c r="BJ36" s="12">
+        <v>0.32609338091408502</v>
+      </c>
+      <c r="BK36" s="12">
+        <v>0.11889682439075</v>
+      </c>
+      <c r="BL36" s="12">
+        <v>0.46992531871098597</v>
+      </c>
+      <c r="BM36" s="12">
+        <v>7.2374057364152096</v>
+      </c>
+      <c r="BN36" s="12">
+        <v>-0.645856602561246</v>
+      </c>
+      <c r="BO36" s="12">
+        <v>4.1252744999166598E-2</v>
+      </c>
+      <c r="BP36" s="12">
+        <v>0.19533400459073499</v>
+      </c>
+      <c r="BQ36" s="12">
+        <v>8.5742682705745907E-2</v>
+      </c>
+      <c r="BR36" s="12">
+        <v>0.31143386516821903</v>
+      </c>
+      <c r="BS36" s="12">
+        <v>25.1318406117887</v>
+      </c>
+      <c r="BT36" s="12">
+        <v>-2.9860974247648802</v>
+      </c>
+      <c r="BU36" s="12">
+        <v>2.5119862629543599</v>
+      </c>
+      <c r="BW36">
+        <v>3</v>
+      </c>
+      <c r="BX36" s="12">
+        <v>0.554471976591005</v>
+      </c>
+      <c r="BY36" s="12">
+        <v>0.29168537871190497</v>
+      </c>
+      <c r="BZ36" s="12">
+        <v>0.223313422537672</v>
+      </c>
+      <c r="CA36" s="12">
+        <v>2.7040564697682501</v>
+      </c>
+      <c r="CB36" s="12">
+        <v>0.28859451338270597</v>
+      </c>
+      <c r="CC36" s="12">
+        <v>0.248234582679806</v>
+      </c>
+      <c r="CD36" s="12">
+        <v>0.38982439671347202</v>
+      </c>
+      <c r="CE36" s="12">
+        <v>0.11648574995797301</v>
+      </c>
+      <c r="CF36" s="12">
+        <v>6.6086468446126201E-2</v>
+      </c>
+      <c r="CG36" s="12">
+        <v>6.6086468446126201E-2</v>
+      </c>
+      <c r="CH36" s="12">
+        <v>7.4278406608390302E-2</v>
+      </c>
+      <c r="CI36" s="12">
+        <v>2.6029588974016802</v>
+      </c>
+      <c r="CJ36" s="12">
+        <v>-3.15075882256621</v>
+      </c>
     </row>
-    <row r="37" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="37" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ37" s="2">
         <v>12</v>
       </c>
-      <c r="AR37" s="15"/>
+      <c r="AR37" s="14"/>
       <c r="AS37" s="8">
         <v>0.99999698593479003</v>
       </c>
@@ -3549,8 +5754,255 @@
       <c r="BE37" s="8">
         <v>-1.15322515870097E-4</v>
       </c>
+      <c r="BI37">
+        <v>31</v>
+      </c>
+      <c r="BJ37" s="12">
+        <v>0.999669744515995</v>
+      </c>
+      <c r="BK37" s="12">
+        <v>0.99933754214996795</v>
+      </c>
+      <c r="BL37" s="12">
+        <v>1.09491378046345E-7</v>
+      </c>
+      <c r="BM37" s="12">
+        <v>2.6647569669401499E-4</v>
+      </c>
+      <c r="BN37" s="12">
+        <v>5.7988269279411395E-4</v>
+      </c>
+      <c r="BO37" s="12">
+        <v>2.2989432927596502E-3</v>
+      </c>
+      <c r="BP37" s="12">
+        <v>8.5326969001542299E-7</v>
+      </c>
+      <c r="BQ37" s="12">
+        <v>3.3625129569614302E-7</v>
+      </c>
+      <c r="BR37" s="12">
+        <v>1.88719468843207E-10</v>
+      </c>
+      <c r="BS37" s="12">
+        <v>20.3291416484041</v>
+      </c>
+      <c r="BT37" s="12">
+        <v>1.6159771955349001E-4</v>
+      </c>
+      <c r="BU37" s="12">
+        <v>-4.1119014158041902E-4</v>
+      </c>
+      <c r="BW37">
+        <v>11</v>
+      </c>
+      <c r="BX37" s="12">
+        <v>1.00450974365629</v>
+      </c>
+      <c r="BY37" s="12">
+        <v>1.0092163068719799</v>
+      </c>
+      <c r="BZ37" s="12">
+        <v>2.34523694148251E-5</v>
+      </c>
+      <c r="CA37" s="12">
+        <v>0.31440891476751798</v>
+      </c>
+      <c r="CB37" s="12">
+        <v>6.8436856228722897E-3</v>
+      </c>
+      <c r="CC37" s="12">
+        <v>1.20641446614232E-2</v>
+      </c>
+      <c r="CD37" s="12">
+        <v>3.1127181746114902E-4</v>
+      </c>
+      <c r="CE37" s="12">
+        <v>0.23957297687304899</v>
+      </c>
+      <c r="CF37" s="12">
+        <v>0.46679432331947701</v>
+      </c>
+      <c r="CG37" s="12">
+        <v>0.46679432331947701</v>
+      </c>
+      <c r="CH37" s="12">
+        <v>0.91339978204743899</v>
+      </c>
+      <c r="CI37" s="12">
+        <v>-6.1891576332272401E-2</v>
+      </c>
+      <c r="CJ37" s="12">
+        <v>3.5296354312475103E-2</v>
+      </c>
     </row>
-    <row r="40" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="38" spans="43:88" x14ac:dyDescent="0.25">
+      <c r="BI38">
+        <v>32</v>
+      </c>
+      <c r="BJ38" s="12">
+        <v>0.99966945208845304</v>
+      </c>
+      <c r="BK38" s="12">
+        <v>0.99933828624043397</v>
+      </c>
+      <c r="BL38" s="12">
+        <v>1.0931480357834399E-7</v>
+      </c>
+      <c r="BM38" s="12">
+        <v>2.39270023102921E-4</v>
+      </c>
+      <c r="BN38" s="12">
+        <v>4.7888140112300602E-4</v>
+      </c>
+      <c r="BO38" s="12">
+        <v>1.8096019118113099E-3</v>
+      </c>
+      <c r="BP38" s="12">
+        <v>2.9242754229219498E-7</v>
+      </c>
+      <c r="BQ38" s="12">
+        <v>7.4409046635359701E-7</v>
+      </c>
+      <c r="BR38" s="12">
+        <v>1.7657446800102101E-10</v>
+      </c>
+      <c r="BS38" s="12">
+        <v>18.460779631351901</v>
+      </c>
+      <c r="BT38" s="12">
+        <v>-3.7031261503481499E-4</v>
+      </c>
+      <c r="BU38" s="12">
+        <v>-1.4543967881142E-4</v>
+      </c>
+      <c r="BW38">
+        <v>12</v>
+      </c>
+      <c r="BX38" s="12">
+        <v>0.99985422066542595</v>
+      </c>
+      <c r="BY38" s="12">
+        <v>0.99975878695154197</v>
+      </c>
+      <c r="BZ38" s="12">
+        <v>2.74505826674446E-7</v>
+      </c>
+      <c r="CA38" s="12">
+        <v>2.8239445991869601</v>
+      </c>
+      <c r="CB38" s="12">
+        <v>4.65552299086358E-3</v>
+      </c>
+      <c r="CC38" s="12">
+        <v>9.4575199204449591E-3</v>
+      </c>
+      <c r="CD38" s="12">
+        <v>2.3177863588150699E-5</v>
+      </c>
+      <c r="CE38" s="12">
+        <v>0.51331969287778501</v>
+      </c>
+      <c r="CF38" s="12">
+        <v>1.0282605338075399</v>
+      </c>
+      <c r="CG38" s="12">
+        <v>1.0282605338075399</v>
+      </c>
+      <c r="CH38" s="12">
+        <v>2.0649909686769701</v>
+      </c>
+      <c r="CI38" s="12">
+        <v>-2.04183717981705E-2</v>
+      </c>
+      <c r="CJ38" s="12">
+        <v>1.00648738151187E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="43:88" x14ac:dyDescent="0.25">
+      <c r="BI39">
+        <v>33</v>
+      </c>
+      <c r="BJ39" s="12">
+        <v>1.0000000233414501</v>
+      </c>
+      <c r="BK39" s="12">
+        <v>0.99999990035638797</v>
+      </c>
+      <c r="BL39" s="12">
+        <v>2.1416900644604099E-12</v>
+      </c>
+      <c r="BM39" s="12">
+        <v>-5.2095711258948103E-5</v>
+      </c>
+      <c r="BN39" s="12">
+        <v>4.2237719678000898E-5</v>
+      </c>
+      <c r="BO39" s="12">
+        <v>1.3815824009928701</v>
+      </c>
+      <c r="BP39" s="12">
+        <v>3.3057125300417402E-4</v>
+      </c>
+      <c r="BQ39" s="12">
+        <v>6.6161411595433396E-4</v>
+      </c>
+      <c r="BR39" s="12">
+        <v>1.09312661888279E-7</v>
+      </c>
+      <c r="BS39" s="12">
+        <v>95.965848461570204</v>
+      </c>
+      <c r="BT39" s="12">
+        <v>5.8577294950350803E-5</v>
+      </c>
+      <c r="BU39" s="12">
+        <v>-2.9265305334646999E-5</v>
+      </c>
+      <c r="BW39">
+        <v>13</v>
+      </c>
+      <c r="BX39" s="12">
+        <v>0.999982601204225</v>
+      </c>
+      <c r="BY39" s="12">
+        <v>0.99996476901415299</v>
+      </c>
+      <c r="BZ39" s="12">
+        <v>3.2152740462262898E-10</v>
+      </c>
+      <c r="CA39" s="12">
+        <v>0.97376149408341806</v>
+      </c>
+      <c r="CB39" s="12">
+        <v>1.2838053879970999E-4</v>
+      </c>
+      <c r="CC39" s="12">
+        <v>2.0598206261079801E-4</v>
+      </c>
+      <c r="CD39" s="12">
+        <v>2.74184299269823E-7</v>
+      </c>
+      <c r="CE39" s="12">
+        <v>0.49955872145041103</v>
+      </c>
+      <c r="CF39" s="12">
+        <v>0.99896172709230502</v>
+      </c>
+      <c r="CG39" s="12">
+        <v>0.99896172709230502</v>
+      </c>
+      <c r="CH39" s="12">
+        <v>2.0026101927653701</v>
+      </c>
+      <c r="CI39" s="12">
+        <v>1.3867819682704299E-4</v>
+      </c>
+      <c r="CJ39" s="12">
+        <v>-8.6739403348801107E-5</v>
+      </c>
+    </row>
+    <row r="40" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ40" s="2" t="s">
         <v>0</v>
       </c>
@@ -3596,12 +6048,24 @@
       <c r="BE40" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="BJ40" s="12"/>
+      <c r="BK40" s="12"/>
+      <c r="BL40" s="12"/>
+      <c r="BM40" s="12"/>
+      <c r="BN40" s="12"/>
+      <c r="BO40" s="12"/>
+      <c r="BP40" s="12"/>
+      <c r="BQ40" s="12"/>
+      <c r="BR40" s="12"/>
+      <c r="BS40" s="12"/>
+      <c r="BT40" s="12"/>
+      <c r="BU40" s="12"/>
     </row>
-    <row r="41" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="41" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ41" s="2">
         <v>1</v>
       </c>
-      <c r="AR41" s="14" t="s">
+      <c r="AR41" s="13" t="s">
         <v>14</v>
       </c>
       <c r="AS41" s="8">
@@ -3643,12 +6107,30 @@
       <c r="BE41" s="8">
         <v>-0.26702947795808502</v>
       </c>
+      <c r="BI41" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="BJ41" s="12"/>
+      <c r="BK41" s="12"/>
+      <c r="BL41" s="12"/>
+      <c r="BM41" s="12"/>
+      <c r="BN41" s="12"/>
+      <c r="BO41" s="12"/>
+      <c r="BP41" s="12"/>
+      <c r="BQ41" s="12"/>
+      <c r="BR41" s="12"/>
+      <c r="BS41" s="12"/>
+      <c r="BT41" s="12"/>
+      <c r="BU41" s="12"/>
+      <c r="BW41" s="25" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="42" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="42" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ42" s="2">
         <v>2</v>
       </c>
-      <c r="AR42" s="15"/>
+      <c r="AR42" s="14"/>
       <c r="AS42" s="8">
         <v>1.83618812624156</v>
       </c>
@@ -3688,12 +6170,93 @@
       <c r="BE42" s="8">
         <v>-0.26702984164065302</v>
       </c>
+      <c r="BI42" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ42" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK42" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL42" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM42" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN42" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO42" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP42" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ42" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR42" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS42" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT42" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU42" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BW42" t="s">
+        <v>0</v>
+      </c>
+      <c r="BX42" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="BY42" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="BZ42" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="CA42" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="CB42" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="CC42" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="CD42" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="CE42" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="CF42" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CG42" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="CH42" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="CI42" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="CJ42" s="12" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="43" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="43" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ43" s="2">
         <v>3</v>
       </c>
-      <c r="AR43" s="15"/>
+      <c r="AR43" s="14"/>
       <c r="AS43" s="8">
         <v>1.1049303542026701</v>
       </c>
@@ -3733,12 +6296,93 @@
       <c r="BE43" s="8">
         <v>0.41424196088489301</v>
       </c>
+      <c r="BI43">
+        <v>1</v>
+      </c>
+      <c r="BJ43" s="12">
+        <v>1.50092308640672</v>
+      </c>
+      <c r="BK43" s="12">
+        <v>7.2529674781596798</v>
+      </c>
+      <c r="BL43" s="24">
+        <v>2500.4482946848502</v>
+      </c>
+      <c r="BM43" s="24">
+        <v>-1006.18526316091</v>
+      </c>
+      <c r="BN43" s="24">
+        <v>-3007.6286932032599</v>
+      </c>
+      <c r="BO43" s="12">
+        <v>-1.25296747815968E-3</v>
+      </c>
+      <c r="BP43" s="12">
+        <v>2.5009230864067198</v>
+      </c>
+      <c r="BQ43" s="12">
+        <v>1.25296747815968</v>
+      </c>
+      <c r="BR43" s="12">
+        <v>3.5517053151443099</v>
+      </c>
+      <c r="BS43" s="12">
+        <v>173.19433592514901</v>
+      </c>
+      <c r="BT43" s="24">
+        <v>-3000.96281962589</v>
+      </c>
+      <c r="BU43" s="24">
+        <v>1000.03947337019</v>
+      </c>
+      <c r="BW43">
+        <v>1</v>
+      </c>
+      <c r="BX43" s="12">
+        <v>1.50092308640672</v>
+      </c>
+      <c r="BY43" s="12">
+        <v>7.2529674781596798</v>
+      </c>
+      <c r="BZ43" s="24">
+        <v>2500.4482946848502</v>
+      </c>
+      <c r="CA43" s="12">
+        <v>-1.25296747815968E-3</v>
+      </c>
+      <c r="CB43" s="12">
+        <v>2.5009230864067198</v>
+      </c>
+      <c r="CC43" s="12">
+        <v>1.25296747815968</v>
+      </c>
+      <c r="CD43" s="12">
+        <v>3.5517053151443099</v>
+      </c>
+      <c r="CE43" s="12">
+        <v>-5.0049055048950698E-4</v>
+      </c>
+      <c r="CF43" s="12">
+        <v>-2.42846335682496E-4</v>
+      </c>
+      <c r="CG43" s="12">
+        <v>-2.42846335682496E-4</v>
+      </c>
+      <c r="CH43" s="12">
+        <v>0.99999994105515799</v>
+      </c>
+      <c r="CI43" s="24">
+        <v>-3000.96281962589</v>
+      </c>
+      <c r="CJ43" s="24">
+        <v>1000.03947337019</v>
+      </c>
     </row>
-    <row r="44" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="44" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ44" s="2">
         <v>4</v>
       </c>
-      <c r="AR44" s="15"/>
+      <c r="AR44" s="14"/>
       <c r="AS44" s="8">
         <v>1.0954834129533899</v>
       </c>
@@ -3778,12 +6422,93 @@
       <c r="BE44" s="8">
         <v>8.4813839966966197E-3</v>
       </c>
+      <c r="BI44">
+        <v>2</v>
+      </c>
+      <c r="BJ44" s="12">
+        <v>1.5010816646095899</v>
+      </c>
+      <c r="BK44" s="12">
+        <v>7.2529146336321002</v>
+      </c>
+      <c r="BL44" s="24">
+        <v>2499.91956363082</v>
+      </c>
+      <c r="BM44" s="24">
+        <v>6001.8601863525801</v>
+      </c>
+      <c r="BN44" s="24">
+        <v>-1999.9515942015701</v>
+      </c>
+      <c r="BO44" s="12">
+        <v>5.2842441710406502E-8</v>
+      </c>
+      <c r="BP44" s="12">
+        <v>1.5857820287124E-4</v>
+      </c>
+      <c r="BQ44" s="12">
+        <v>5.2844527579587403E-5</v>
+      </c>
+      <c r="BR44" s="12">
+        <v>0.528731054033869</v>
+      </c>
+      <c r="BS44" s="12">
+        <v>96.736210351165695</v>
+      </c>
+      <c r="BT44" s="24">
+        <v>-3000.9621043311699</v>
+      </c>
+      <c r="BU44" s="12">
+        <v>999.93369396099695</v>
+      </c>
+      <c r="BW44">
+        <v>2</v>
+      </c>
+      <c r="BX44" s="12">
+        <v>1.49462824637831</v>
+      </c>
+      <c r="BY44" s="12">
+        <v>2.2496416164709299</v>
+      </c>
+      <c r="BZ44" s="12">
+        <v>0.26939416845723702</v>
+      </c>
+      <c r="CA44" s="12">
+        <v>4.99948532082224E-3</v>
+      </c>
+      <c r="CB44" s="12">
+        <v>6.2948400284128497E-3</v>
+      </c>
+      <c r="CC44" s="12">
+        <v>5.0033258616887402</v>
+      </c>
+      <c r="CD44" s="24">
+        <v>2500.1789005163901</v>
+      </c>
+      <c r="CE44" s="12">
+        <v>-5.0207393158193097E-4</v>
+      </c>
+      <c r="CF44" s="12">
+        <v>-1.5008478609559899E-3</v>
+      </c>
+      <c r="CG44" s="12">
+        <v>-1.5008478609559899E-3</v>
+      </c>
+      <c r="CH44" s="12">
+        <v>5.1356019442483304E-4</v>
+      </c>
+      <c r="CI44" s="12">
+        <v>-8.4137616438663905</v>
+      </c>
+      <c r="CJ44" s="12">
+        <v>3.1456043198058801</v>
+      </c>
     </row>
-    <row r="45" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="45" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ45" s="2">
         <v>5</v>
       </c>
-      <c r="AR45" s="15"/>
+      <c r="AR45" s="14"/>
       <c r="AS45" s="8">
         <v>1.20680936289287</v>
       </c>
@@ -3823,12 +6548,93 @@
       <c r="BE45" s="8">
         <v>1.11858498058418E-3</v>
       </c>
+      <c r="BI45">
+        <v>3</v>
+      </c>
+      <c r="BJ45" s="12">
+        <v>1.5011223088415</v>
+      </c>
+      <c r="BK45" s="12">
+        <v>7.25290109008162</v>
+      </c>
+      <c r="BL45" s="24">
+        <v>2499.7840493662502</v>
+      </c>
+      <c r="BM45" s="24">
+        <v>9002.78885228332</v>
+      </c>
+      <c r="BN45" s="24">
+        <v>-2999.8470987556502</v>
+      </c>
+      <c r="BO45" s="12">
+        <v>6.7719391402975898E-9</v>
+      </c>
+      <c r="BP45" s="12">
+        <v>4.0644231910524902E-5</v>
+      </c>
+      <c r="BQ45" s="12">
+        <v>1.35435504793335E-5</v>
+      </c>
+      <c r="BR45" s="12">
+        <v>0.13551426456615401</v>
+      </c>
+      <c r="BS45" s="12">
+        <v>96.735424021086502</v>
+      </c>
+      <c r="BT45" s="24">
+        <v>-3000.9619057629102</v>
+      </c>
+      <c r="BU45" s="12">
+        <v>999.90658079599302</v>
+      </c>
+      <c r="BW45">
+        <v>3</v>
+      </c>
+      <c r="BX45" s="12">
+        <v>1.4951200371342099</v>
+      </c>
+      <c r="BY45" s="12">
+        <v>2.23554038364479</v>
+      </c>
+      <c r="BZ45" s="12">
+        <v>0.24514629908876001</v>
+      </c>
+      <c r="CA45" s="12">
+        <v>0.99003031808828801</v>
+      </c>
+      <c r="CB45" s="12">
+        <v>4.9179075589877996E-4</v>
+      </c>
+      <c r="CC45" s="12">
+        <v>1.4101232826140699E-2</v>
+      </c>
+      <c r="CD45" s="12">
+        <v>2.42478693684769E-2</v>
+      </c>
+      <c r="CE45" s="12">
+        <v>-0.363523359298487</v>
+      </c>
+      <c r="CF45" s="12">
+        <v>-1.0869336927458499</v>
+      </c>
+      <c r="CG45" s="12">
+        <v>-1.0869336927458499</v>
+      </c>
+      <c r="CH45" s="12">
+        <v>-3.2449282589103299</v>
+      </c>
+      <c r="CI45" s="12">
+        <v>0.89667055560401798</v>
+      </c>
+      <c r="CJ45" s="12">
+        <v>3.1291640918595903E-2</v>
+      </c>
     </row>
-    <row r="46" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="46" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ46" s="2">
         <v>6</v>
       </c>
-      <c r="AR46" s="15"/>
+      <c r="AR46" s="14"/>
       <c r="AS46" s="8">
         <v>1.1898798465112601</v>
       </c>
@@ -3868,12 +6674,93 @@
       <c r="BE46" s="8">
         <v>-1.3076470745183801E-4</v>
       </c>
+      <c r="BI46">
+        <v>15433</v>
+      </c>
+      <c r="BJ46" s="12">
+        <v>1.0003931307013501</v>
+      </c>
+      <c r="BK46" s="12">
+        <v>1.0007881559791101</v>
+      </c>
+      <c r="BL46" s="12">
+        <v>1.54854516927051E-7</v>
+      </c>
+      <c r="BM46" s="12">
+        <v>-7.5192972917376797E-5</v>
+      </c>
+      <c r="BN46" s="12">
+        <v>-3.5664887432358802E-4</v>
+      </c>
+      <c r="BO46" s="12">
+        <v>1.16336745515067E-3</v>
+      </c>
+      <c r="BP46" s="12">
+        <v>5.4511286315950199E-6</v>
+      </c>
+      <c r="BQ46" s="12">
+        <v>3.1869748724489E-6</v>
+      </c>
+      <c r="BR46" s="12">
+        <v>2.05109478654547E-8</v>
+      </c>
+      <c r="BS46" s="12">
+        <v>146.91673459468501</v>
+      </c>
+      <c r="BT46" s="12">
+        <v>8.9977915536160999E-5</v>
+      </c>
+      <c r="BU46" s="12">
+        <v>3.4800493216024999E-4</v>
+      </c>
+      <c r="BW46">
+        <v>12</v>
+      </c>
+      <c r="BX46" s="12">
+        <v>1.00550575797104</v>
+      </c>
+      <c r="BY46" s="12">
+        <v>1.01090388576042</v>
+      </c>
+      <c r="BZ46" s="12">
+        <v>3.2216213203059202E-5</v>
+      </c>
+      <c r="CA46" s="12">
+        <v>0.38024384120973898</v>
+      </c>
+      <c r="CB46" s="12">
+        <v>3.2188149309768598E-3</v>
+      </c>
+      <c r="CC46" s="12">
+        <v>7.7272534940526702E-3</v>
+      </c>
+      <c r="CD46" s="12">
+        <v>1.6971001047467801E-4</v>
+      </c>
+      <c r="CE46" s="12">
+        <v>0.24537346910235999</v>
+      </c>
+      <c r="CF46" s="12">
+        <v>0.498178306002587</v>
+      </c>
+      <c r="CG46" s="12">
+        <v>0.498178306002587</v>
+      </c>
+      <c r="CH46" s="12">
+        <v>1.0161581372808</v>
+      </c>
+      <c r="CI46" s="12">
+        <v>6.6492730463809505E-2</v>
+      </c>
+      <c r="CJ46" s="12">
+        <v>-2.7588710498127601E-2</v>
+      </c>
     </row>
-    <row r="47" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="47" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ47" s="2">
         <v>1</v>
       </c>
-      <c r="AR47" s="14" t="s">
+      <c r="AR47" s="13" t="s">
         <v>24</v>
       </c>
       <c r="AS47" s="8">
@@ -3915,12 +6802,93 @@
       <c r="BE47" s="8">
         <v>-0.37877393402439202</v>
       </c>
+      <c r="BI47">
+        <v>15434</v>
+      </c>
+      <c r="BJ47" s="12">
+        <v>1.00039107660691</v>
+      </c>
+      <c r="BK47" s="12">
+        <v>1.0007802114186</v>
+      </c>
+      <c r="BL47" s="12">
+        <v>1.53379704427954E-7</v>
+      </c>
+      <c r="BM47" s="12">
+        <v>-3.57109801696899E-3</v>
+      </c>
+      <c r="BN47" s="12">
+        <v>-7.12580533194944E-3</v>
+      </c>
+      <c r="BO47" s="12">
+        <v>2.2828873319677999E-2</v>
+      </c>
+      <c r="BP47" s="12">
+        <v>2.05409443543302E-6</v>
+      </c>
+      <c r="BQ47" s="12">
+        <v>7.9445605110084404E-6</v>
+      </c>
+      <c r="BR47" s="12">
+        <v>1.47481249909744E-9</v>
+      </c>
+      <c r="BS47" s="12">
+        <v>161.62888474616</v>
+      </c>
+      <c r="BT47" s="12">
+        <v>1.62037535212605E-3</v>
+      </c>
+      <c r="BU47" s="12">
+        <v>-4.1894722868640599E-4</v>
+      </c>
+      <c r="BW47">
+        <v>13</v>
+      </c>
+      <c r="BX47" s="12">
+        <v>0.99998986685529001</v>
+      </c>
+      <c r="BY47" s="12">
+        <v>0.99998400335463999</v>
+      </c>
+      <c r="BZ47" s="12">
+        <v>1.9255789801158602E-9</v>
+      </c>
+      <c r="CA47" s="12">
+        <v>2.1450468183212101</v>
+      </c>
+      <c r="CB47" s="12">
+        <v>5.5158911157507902E-3</v>
+      </c>
+      <c r="CC47" s="12">
+        <v>1.09198824057873E-2</v>
+      </c>
+      <c r="CD47" s="12">
+        <v>3.2214287624079E-5</v>
+      </c>
+      <c r="CE47" s="12">
+        <v>0.49348306849781498</v>
+      </c>
+      <c r="CF47" s="12">
+        <v>0.989709029716342</v>
+      </c>
+      <c r="CG47" s="12">
+        <v>0.989709029716342</v>
+      </c>
+      <c r="CH47" s="12">
+        <v>1.98993123168446</v>
+      </c>
+      <c r="CI47" s="12">
+        <v>-1.72806553533273E-3</v>
+      </c>
+      <c r="CJ47" s="12">
+        <v>8.5390827573306096E-4</v>
+      </c>
     </row>
-    <row r="48" spans="43:57" x14ac:dyDescent="0.25">
+    <row r="48" spans="43:88" x14ac:dyDescent="0.25">
       <c r="AQ48" s="2">
         <v>2</v>
       </c>
-      <c r="AR48" s="15"/>
+      <c r="AR48" s="14"/>
       <c r="AS48" s="8">
         <v>3.4844176834867602</v>
       </c>
@@ -3960,8 +6928,89 @@
       <c r="BE48" s="8">
         <v>-5.8594907387670397E-2</v>
       </c>
+      <c r="BI48">
+        <v>15435</v>
+      </c>
+      <c r="BJ48" s="12">
+        <v>0.99999987552818803</v>
+      </c>
+      <c r="BK48" s="12">
+        <v>0.99999960480421601</v>
+      </c>
+      <c r="BL48" s="12">
+        <v>2.1544631313770099E-12</v>
+      </c>
+      <c r="BM48" s="12">
+        <v>-6.3668708176440098E-5</v>
+      </c>
+      <c r="BN48" s="12">
+        <v>1.8441719966895101E-5</v>
+      </c>
+      <c r="BO48" s="12">
+        <v>0.109546441141775</v>
+      </c>
+      <c r="BP48" s="12">
+        <v>3.91201078727365E-4</v>
+      </c>
+      <c r="BQ48" s="12">
+        <v>7.8060661438417102E-4</v>
+      </c>
+      <c r="BR48" s="12">
+        <v>1.53377549964822E-7</v>
+      </c>
+      <c r="BS48" s="12">
+        <v>118.846283030878</v>
+      </c>
+      <c r="BT48" s="12">
+        <v>5.8251919510054302E-5</v>
+      </c>
+      <c r="BU48" s="12">
+        <v>-2.9250435207295301E-5</v>
+      </c>
+      <c r="BW48">
+        <v>14</v>
+      </c>
+      <c r="BX48" s="12">
+        <v>0.99999765193710199</v>
+      </c>
+      <c r="BY48" s="12">
+        <v>0.99999526150747997</v>
+      </c>
+      <c r="BZ48" s="12">
+        <v>5.6929400256117503E-12</v>
+      </c>
+      <c r="CA48" s="12">
+        <v>1.0176109432688401</v>
+      </c>
+      <c r="CB48" s="12">
+        <v>7.7850818120950192E-6</v>
+      </c>
+      <c r="CC48" s="12">
+        <v>1.12581528401989E-5</v>
+      </c>
+      <c r="CD48" s="12">
+        <v>1.9198860400902502E-9</v>
+      </c>
+      <c r="CE48" s="12">
+        <v>0.60488791182652601</v>
+      </c>
+      <c r="CF48" s="12">
+        <v>1.2116573895903999</v>
+      </c>
+      <c r="CG48" s="12">
+        <v>1.2116573895903999</v>
+      </c>
+      <c r="CH48" s="12">
+        <v>2.4321119572157399</v>
+      </c>
+      <c r="CI48" s="12">
+        <v>1.22527296288857E-5</v>
+      </c>
+      <c r="CJ48" s="12">
+        <v>-8.4744476103182297E-6</v>
+      </c>
     </row>
-    <row r="49" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="49" spans="6:77" x14ac:dyDescent="0.25">
       <c r="G49" s="1"/>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -3969,7 +7018,7 @@
       <c r="AQ49" s="2">
         <v>3</v>
       </c>
-      <c r="AR49" s="15"/>
+      <c r="AR49" s="14"/>
       <c r="AS49" s="8">
         <v>0.93622320381316804</v>
       </c>
@@ -4010,11 +7059,11 @@
         <v>0.197338081306109</v>
       </c>
     </row>
-    <row r="50" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="50" spans="6:77" x14ac:dyDescent="0.25">
       <c r="AQ50" s="2">
         <v>4</v>
       </c>
-      <c r="AR50" s="15"/>
+      <c r="AR50" s="14"/>
       <c r="AS50" s="8">
         <v>1.1389615854687201</v>
       </c>
@@ -4054,13 +7103,31 @@
       <c r="BE50" s="8">
         <v>-0.124974898671857</v>
       </c>
+      <c r="BI50" t="s">
+        <v>44</v>
+      </c>
+      <c r="BJ50" t="s">
+        <v>39</v>
+      </c>
+      <c r="BK50" t="s">
+        <v>40</v>
+      </c>
+      <c r="BW50" t="s">
+        <v>44</v>
+      </c>
+      <c r="BX50" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="BY50" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="51" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="51" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J51" s="1"/>
       <c r="AQ51" s="2">
         <v>5</v>
       </c>
-      <c r="AR51" s="15"/>
+      <c r="AR51" s="14"/>
       <c r="AS51" s="8">
         <v>1.2004622213737499</v>
       </c>
@@ -4100,12 +7167,21 @@
       <c r="BE51" s="8">
         <v>2.70463209652336E-2</v>
       </c>
+      <c r="BI51" t="s">
+        <v>45</v>
+      </c>
+      <c r="BW51" t="s">
+        <v>45</v>
+      </c>
+      <c r="BX51" s="25" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="52" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="52" spans="6:77" x14ac:dyDescent="0.25">
       <c r="AQ52" s="2">
         <v>6</v>
       </c>
-      <c r="AR52" s="15"/>
+      <c r="AR52" s="14"/>
       <c r="AS52" s="8">
         <v>1.1899497347037</v>
       </c>
@@ -4145,70 +7221,1124 @@
       <c r="BE52" s="8">
         <v>-1.05951174109261E-4</v>
       </c>
+      <c r="BI52" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ52" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK52" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL52" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM52" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN52" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO52" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP52" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ52" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR52" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS52" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT52" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU52" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="53" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="53" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J53" s="1"/>
+      <c r="BI53">
+        <v>1</v>
+      </c>
+      <c r="BJ53" s="12">
+        <v>1.836188157427</v>
+      </c>
+      <c r="BK53" s="12">
+        <v>1.85990433858004</v>
+      </c>
+      <c r="BL53" s="12">
+        <v>-2.48569673407416</v>
+      </c>
+      <c r="BM53" s="12">
+        <v>0.17296067034283999</v>
+      </c>
+      <c r="BN53" s="12">
+        <v>1.1841999415142901</v>
+      </c>
+      <c r="BO53" s="12">
+        <v>15.164031239319099</v>
+      </c>
+      <c r="BP53" s="12">
+        <v>1.836188157427</v>
+      </c>
+      <c r="BQ53" s="12">
+        <v>2.8599043385800398</v>
+      </c>
+      <c r="BR53" s="12">
+        <v>1.8814838737637301</v>
+      </c>
+      <c r="BS53" s="12">
+        <v>36.322671635114098</v>
+      </c>
+      <c r="BT53" s="12">
+        <v>0.41590435634651202</v>
+      </c>
+      <c r="BU53" s="12">
+        <v>-0.26702942287485198</v>
+      </c>
     </row>
-    <row r="54" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="54" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J54" s="1"/>
+      <c r="BI54">
+        <v>2</v>
+      </c>
+      <c r="BJ54" s="12">
+        <v>1.49484128039553</v>
+      </c>
+      <c r="BK54" s="12">
+        <v>2.07906448485633</v>
+      </c>
+      <c r="BL54" s="12">
+        <v>-2.5976536979712401</v>
+      </c>
+      <c r="BM54" s="12">
+        <v>-0.64990726378602703</v>
+      </c>
+      <c r="BN54" s="12">
+        <v>-0.15222063829726101</v>
+      </c>
+      <c r="BO54" s="12">
+        <v>0.82073407460794601</v>
+      </c>
+      <c r="BP54" s="12">
+        <v>0.34134687703146799</v>
+      </c>
+      <c r="BQ54" s="12">
+        <v>0.219160146276285</v>
+      </c>
+      <c r="BR54" s="12">
+        <v>0.11195696389708799</v>
+      </c>
+      <c r="BS54" s="12">
+        <v>138.89816295461799</v>
+      </c>
+      <c r="BT54" s="12">
+        <v>0.25891018967580898</v>
+      </c>
+      <c r="BU54" s="12">
+        <v>0.40325845853691999</v>
+      </c>
     </row>
-    <row r="55" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="55" spans="6:77" x14ac:dyDescent="0.25">
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
       <c r="J55" s="1"/>
+      <c r="BI55">
+        <v>3</v>
+      </c>
+      <c r="BJ55" s="12">
+        <v>1.16224621159202</v>
+      </c>
+      <c r="BK55" s="12">
+        <v>2.0011643958915499</v>
+      </c>
+      <c r="BL55" s="12">
+        <v>-2.6595838325968599</v>
+      </c>
+      <c r="BM55" s="12">
+        <v>-8.4228238533432306E-3</v>
+      </c>
+      <c r="BN55" s="12">
+        <v>-0.113011283724293</v>
+      </c>
+      <c r="BO55" s="12">
+        <v>0.51175773427423699</v>
+      </c>
+      <c r="BP55" s="12">
+        <v>0.33259506880350598</v>
+      </c>
+      <c r="BQ55" s="12">
+        <v>7.7900088964784495E-2</v>
+      </c>
+      <c r="BR55" s="12">
+        <v>6.19301346256175E-2</v>
+      </c>
+      <c r="BS55" s="12">
+        <v>154.115044779518</v>
+      </c>
+      <c r="BT55" s="12">
+        <v>-2.4654802455678599E-2</v>
+      </c>
+      <c r="BU55" s="12">
+        <v>0.10526387471583599</v>
+      </c>
     </row>
-    <row r="56" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="56" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J56" s="1"/>
+      <c r="BI56">
+        <v>4</v>
+      </c>
+      <c r="BJ56" s="12">
+        <v>1.1686914060364999</v>
+      </c>
+      <c r="BK56" s="12">
+        <v>1.97364658706942</v>
+      </c>
+      <c r="BL56" s="12">
+        <v>-2.6611099288342599</v>
+      </c>
+      <c r="BM56" s="12">
+        <v>2.1125486776491901E-2</v>
+      </c>
+      <c r="BN56" s="12">
+        <v>8.52435039451967E-4</v>
+      </c>
+      <c r="BO56" s="12">
+        <v>0.26141740360980398</v>
+      </c>
+      <c r="BP56" s="12">
+        <v>6.44519444447611E-3</v>
+      </c>
+      <c r="BQ56" s="12">
+        <v>2.7517808822121501E-2</v>
+      </c>
+      <c r="BR56" s="12">
+        <v>1.5260962373959601E-3</v>
+      </c>
+      <c r="BS56" s="12">
+        <v>57.057487340928901</v>
+      </c>
+      <c r="BT56" s="12">
+        <v>-2.0216121679518199E-2</v>
+      </c>
+      <c r="BU56" s="12">
+        <v>-4.7349765366254803E-3</v>
+      </c>
     </row>
-    <row r="57" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="57" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J57" s="1"/>
+      <c r="BI57">
+        <v>5</v>
+      </c>
+      <c r="BJ57" s="12">
+        <v>1.1898638454750701</v>
+      </c>
+      <c r="BK57" s="12">
+        <v>1.9745009166969001</v>
+      </c>
+      <c r="BL57" s="12">
+        <v>-2.66132563078691</v>
+      </c>
+      <c r="BM57" s="12">
+        <v>1.1192007132176699E-5</v>
+      </c>
+      <c r="BN57" s="12">
+        <v>-2.1885334872378501E-4</v>
+      </c>
+      <c r="BO57" s="12">
+        <v>1.00222256000902</v>
+      </c>
+      <c r="BP57" s="12">
+        <v>2.11724394385726E-2</v>
+      </c>
+      <c r="BQ57" s="12">
+        <v>8.5432962748099796E-4</v>
+      </c>
+      <c r="BR57" s="12">
+        <v>2.15701952652747E-4</v>
+      </c>
+      <c r="BS57" s="12">
+        <v>145.99868727346899</v>
+      </c>
+      <c r="BT57" s="12">
+        <v>-8.8390858842546298E-6</v>
+      </c>
+      <c r="BU57" s="12">
+        <v>2.1894829150725901E-4</v>
+      </c>
     </row>
-    <row r="58" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="58" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J58" s="1"/>
     </row>
-    <row r="59" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="59" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J59" s="1"/>
+      <c r="BI59" s="25" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="60" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="60" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J60" s="1"/>
+      <c r="BI60" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ60" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK60" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL60" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM60" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN60" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO60" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP60" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ60" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR60" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS60" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT60" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU60" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="61" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="61" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J61" s="1"/>
+      <c r="BI61">
+        <v>1</v>
+      </c>
+      <c r="BJ61" s="12">
+        <v>3.4590889294209699</v>
+      </c>
+      <c r="BK61" s="12">
+        <v>1.5311301604498799</v>
+      </c>
+      <c r="BL61" s="12">
+        <v>-1.6802474475223801</v>
+      </c>
+      <c r="BM61" s="12">
+        <v>-1.04180103139989</v>
+      </c>
+      <c r="BN61" s="12">
+        <v>-1.6544030388881501</v>
+      </c>
+      <c r="BO61" s="12">
+        <v>45.319523988038199</v>
+      </c>
+      <c r="BP61" s="12">
+        <v>1.5409110705790201</v>
+      </c>
+      <c r="BQ61" s="12">
+        <v>4.4688698395501101</v>
+      </c>
+      <c r="BR61" s="12">
+        <v>1.3481672470211301</v>
+      </c>
+      <c r="BS61" s="12">
+        <v>146.07528670110901</v>
+      </c>
+      <c r="BT61" s="12">
+        <v>0.42126092618023597</v>
+      </c>
+      <c r="BU61" s="12">
+        <v>-0.14525497733037401</v>
+      </c>
     </row>
-    <row r="62" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="62" spans="6:77" x14ac:dyDescent="0.25">
       <c r="J62" s="1"/>
+      <c r="BI62">
+        <v>2</v>
+      </c>
+      <c r="BJ62" s="12">
+        <v>1.5324496818251401</v>
+      </c>
+      <c r="BK62" s="12">
+        <v>2.19545462740414</v>
+      </c>
+      <c r="BL62" s="12">
+        <v>-2.5185606007048298</v>
+      </c>
+      <c r="BM62" s="12">
+        <v>-1.6789760057968799</v>
+      </c>
+      <c r="BN62" s="12">
+        <v>-0.284305933904071</v>
+      </c>
+      <c r="BO62" s="12">
+        <v>4.5735057012420901</v>
+      </c>
+      <c r="BP62" s="12">
+        <v>1.9266392475958301</v>
+      </c>
+      <c r="BQ62" s="12">
+        <v>0.66432446695425795</v>
+      </c>
+      <c r="BR62" s="12">
+        <v>0.83831315318244903</v>
+      </c>
+      <c r="BS62" s="12">
+        <v>134.52632777696701</v>
+      </c>
+      <c r="BT62" s="12">
+        <v>0.26602306574665302</v>
+      </c>
+      <c r="BU62" s="12">
+        <v>0.771506228355476</v>
+      </c>
     </row>
-    <row r="63" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="63" spans="6:77" x14ac:dyDescent="0.25">
       <c r="I63" s="1"/>
       <c r="J63" s="1"/>
+      <c r="BI63">
+        <v>3</v>
+      </c>
+      <c r="BJ63" s="12">
+        <v>1.0844611199479199</v>
+      </c>
+      <c r="BK63" s="12">
+        <v>2.1195954096290799</v>
+      </c>
+      <c r="BL63" s="12">
+        <v>-2.61475887393178</v>
+      </c>
+      <c r="BM63" s="12">
+        <v>-0.73858993849795695</v>
+      </c>
+      <c r="BN63" s="12">
+        <v>-0.70865257140646598</v>
+      </c>
+      <c r="BO63" s="12">
+        <v>0.26682249200135999</v>
+      </c>
+      <c r="BP63" s="12">
+        <v>0.44798856187721597</v>
+      </c>
+      <c r="BQ63" s="12">
+        <v>7.5859217775058302E-2</v>
+      </c>
+      <c r="BR63" s="12">
+        <v>9.6198273226948794E-2</v>
+      </c>
+      <c r="BS63" s="12">
+        <v>160.91087582142501</v>
+      </c>
+      <c r="BT63" s="12">
+        <v>-9.6065599913542493E-2</v>
+      </c>
+      <c r="BU63" s="12">
+        <v>0.56731789984654701</v>
+      </c>
     </row>
-    <row r="64" spans="6:57" x14ac:dyDescent="0.25">
+    <row r="64" spans="6:77" x14ac:dyDescent="0.25">
       <c r="F64" s="1"/>
       <c r="J64" s="1"/>
+      <c r="BI64">
+        <v>4</v>
+      </c>
+      <c r="BJ64" s="12">
+        <v>1.10935765841948</v>
+      </c>
+      <c r="BK64" s="12">
+        <v>1.9725682538954401</v>
+      </c>
+      <c r="BL64" s="12">
+        <v>-2.6582032737435202</v>
+      </c>
+      <c r="BM64" s="12">
+        <v>7.9421257175280993E-2</v>
+      </c>
+      <c r="BN64" s="12">
+        <v>2.52340288791289E-3</v>
+      </c>
+      <c r="BO64" s="12">
+        <v>0.259161848715526</v>
+      </c>
+      <c r="BP64" s="12">
+        <v>2.4896538471559801E-2</v>
+      </c>
+      <c r="BQ64" s="12">
+        <v>0.147027155733641</v>
+      </c>
+      <c r="BR64" s="12">
+        <v>4.3444399811736201E-2</v>
+      </c>
+      <c r="BS64" s="12">
+        <v>58.827112607139703</v>
+      </c>
+      <c r="BT64" s="12">
+        <v>-7.7622826100684703E-2</v>
+      </c>
+      <c r="BU64" s="12">
+        <v>-1.31440843928116E-2</v>
+      </c>
     </row>
-    <row r="65" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="6:73" x14ac:dyDescent="0.25">
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
+      <c r="BI65">
+        <v>5</v>
+      </c>
+      <c r="BJ65" s="12">
+        <v>1.1897348558541401</v>
+      </c>
+      <c r="BK65" s="12">
+        <v>1.9751220292868501</v>
+      </c>
+      <c r="BL65" s="12">
+        <v>-2.6613247225583998</v>
+      </c>
+      <c r="BM65" s="12">
+        <v>1.77889678818255E-4</v>
+      </c>
+      <c r="BN65" s="12">
+        <v>-2.6831733199963099E-3</v>
+      </c>
+      <c r="BO65" s="12">
+        <v>1.0120363274691699</v>
+      </c>
+      <c r="BP65" s="12">
+        <v>8.03771974346561E-2</v>
+      </c>
+      <c r="BQ65" s="12">
+        <v>2.5537753914084398E-3</v>
+      </c>
+      <c r="BR65" s="12">
+        <v>3.1214488148845199E-3</v>
+      </c>
+      <c r="BS65" s="12">
+        <v>145.14385584673499</v>
+      </c>
+      <c r="BT65" s="12">
+        <v>-8.5341632828500602E-5</v>
+      </c>
+      <c r="BU65" s="12">
+        <v>2.6861137922933702E-3</v>
+      </c>
     </row>
-    <row r="66" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="6:73" x14ac:dyDescent="0.25">
       <c r="J66" s="1"/>
+      <c r="BI66">
+        <v>6</v>
+      </c>
+      <c r="BJ66" s="12">
+        <v>1.18975630022274</v>
+      </c>
+      <c r="BK66" s="12">
+        <v>1.97444707132825</v>
+      </c>
+      <c r="BL66" s="12">
+        <v>-2.6613256299431298</v>
+      </c>
+      <c r="BM66" s="12">
+        <v>1.14796834659972E-4</v>
+      </c>
+      <c r="BN66" s="12">
+        <v>-1.2285332566151701E-6</v>
+      </c>
+      <c r="BO66" s="12">
+        <v>0.25127675548790701</v>
+      </c>
+      <c r="BP66" s="12">
+        <v>2.1444368605294501E-5</v>
+      </c>
+      <c r="BQ66" s="12">
+        <v>6.7495795859873198E-4</v>
+      </c>
+      <c r="BR66" s="12">
+        <v>9.0738473446094695E-7</v>
+      </c>
+      <c r="BS66" s="12">
+        <v>59.540946596731601</v>
+      </c>
+      <c r="BT66" s="12">
+        <v>-1.14641381245672E-4</v>
+      </c>
+      <c r="BU66" s="12">
+        <v>-3.66433727294612E-6</v>
+      </c>
     </row>
-    <row r="67" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="6:73" x14ac:dyDescent="0.25">
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
       <c r="J67" s="1"/>
     </row>
-    <row r="68" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="6:73" x14ac:dyDescent="0.25">
       <c r="F68" s="1"/>
       <c r="J68" s="1"/>
+      <c r="BK68" t="s">
+        <v>41</v>
+      </c>
     </row>
-    <row r="69" spans="6:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="6:73" x14ac:dyDescent="0.25">
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
       <c r="J69" s="1"/>
+      <c r="BI69" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI70" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ70" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK70" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL70" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM70" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN70" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO70" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP70" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ70" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR70" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS70" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT70" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU70" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="71" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI71">
+        <v>1</v>
+      </c>
+      <c r="BJ71" s="12">
+        <v>1.93741427033298</v>
+      </c>
+      <c r="BK71" s="12">
+        <v>2.0175662853181602</v>
+      </c>
+      <c r="BL71" s="12">
+        <v>-2.4454754704077399</v>
+      </c>
+      <c r="BM71" s="12">
+        <v>0.161537077032783</v>
+      </c>
+      <c r="BN71" s="12">
+        <v>0.79940491418457205</v>
+      </c>
+      <c r="BO71" s="12">
+        <v>16</v>
+      </c>
+      <c r="BP71" s="12">
+        <v>1.93741427033298</v>
+      </c>
+      <c r="BQ71" s="12">
+        <v>3.0175662853181602</v>
+      </c>
+      <c r="BR71" s="12">
+        <v>1.84126261009732</v>
+      </c>
+      <c r="BS71" s="12">
+        <v>32.414978276288203</v>
+      </c>
+      <c r="BT71" s="12">
+        <v>0.47637259541295002</v>
+      </c>
+      <c r="BU71" s="12">
+        <v>0.19415374290106699</v>
+      </c>
+    </row>
+    <row r="72" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI72">
+        <v>2</v>
+      </c>
+      <c r="BJ72" s="12">
+        <v>1.46240033606557</v>
+      </c>
+      <c r="BK72" s="12">
+        <v>1.8239662878451</v>
+      </c>
+      <c r="BL72" s="12">
+        <v>-2.5915813293902898</v>
+      </c>
+      <c r="BM72" s="12">
+        <v>-0.71983170951195996</v>
+      </c>
+      <c r="BN72" s="12">
+        <v>0.28558678117200198</v>
+      </c>
+      <c r="BO72" s="12">
+        <v>0.99714790238016104</v>
+      </c>
+      <c r="BP72" s="12">
+        <v>0.475013934267416</v>
+      </c>
+      <c r="BQ72" s="12">
+        <v>0.19359999747305601</v>
+      </c>
+      <c r="BR72" s="12">
+        <v>0.14610585898254799</v>
+      </c>
+      <c r="BS72" s="12">
+        <v>107.081311799212</v>
+      </c>
+      <c r="BT72" s="12">
+        <v>0.202367505331077</v>
+      </c>
+      <c r="BU72" s="12">
+        <v>-0.49648810720640402</v>
+      </c>
+    </row>
+    <row r="73" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI73">
+        <v>3</v>
+      </c>
+      <c r="BJ73" s="12">
+        <v>1.1516077324712</v>
+      </c>
+      <c r="BK73" s="12">
+        <v>1.9472704686691999</v>
+      </c>
+      <c r="BL73" s="12">
+        <v>-2.6590774200627401</v>
+      </c>
+      <c r="BM73" s="12">
+        <v>3.9515567301374203E-3</v>
+      </c>
+      <c r="BN73" s="12">
+        <v>0.124938257993989</v>
+      </c>
+      <c r="BO73" s="12">
+        <v>0.43175731144864299</v>
+      </c>
+      <c r="BP73" s="12">
+        <v>0.310792603594364</v>
+      </c>
+      <c r="BQ73" s="12">
+        <v>0.123304180824095</v>
+      </c>
+      <c r="BR73" s="12">
+        <v>6.7496090672443998E-2</v>
+      </c>
+      <c r="BS73" s="12">
+        <v>28.788343710208999</v>
+      </c>
+      <c r="BT73" s="12">
+        <v>-3.8642127782103602E-2</v>
+      </c>
+      <c r="BU73" s="12">
+        <v>-0.11117508475108399</v>
+      </c>
+    </row>
+    <row r="74" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI74">
+        <v>4</v>
+      </c>
+      <c r="BJ74" s="12">
+        <v>1.16202067988182</v>
+      </c>
+      <c r="BK74" s="12">
+        <v>1.9772289719227401</v>
+      </c>
+      <c r="BL74" s="12">
+        <v>-2.6609467543124898</v>
+      </c>
+      <c r="BM74" s="12">
+        <v>2.85202795051239E-2</v>
+      </c>
+      <c r="BN74" s="12">
+        <v>-2.8968385192763499E-3</v>
+      </c>
+      <c r="BO74" s="12">
+        <v>0.26947137769774199</v>
+      </c>
+      <c r="BP74" s="12">
+        <v>1.0412947410615599E-2</v>
+      </c>
+      <c r="BQ74" s="12">
+        <v>2.9958503253537799E-2</v>
+      </c>
+      <c r="BR74" s="12">
+        <v>1.86933424975199E-3</v>
+      </c>
+      <c r="BS74" s="12">
+        <v>65.356886986258999</v>
+      </c>
+      <c r="BT74" s="12">
+        <v>-2.6350454443150199E-2</v>
+      </c>
+      <c r="BU74" s="12">
+        <v>9.1395197329043002E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI75">
+        <v>5</v>
+      </c>
+      <c r="BJ75" s="12">
+        <v>1.18988747243962</v>
+      </c>
+      <c r="BK75" s="12">
+        <v>1.97439850884556</v>
+      </c>
+      <c r="BL75" s="12">
+        <v>-2.6613256324253198</v>
+      </c>
+      <c r="BM75" s="12">
+        <v>-4.6882876898962796E-6</v>
+      </c>
+      <c r="BN75" s="12">
+        <v>1.8747612827723099E-4</v>
+      </c>
+      <c r="BO75" s="12">
+        <v>0.97708693748242603</v>
+      </c>
+      <c r="BP75" s="12">
+        <v>2.7866792557804401E-2</v>
+      </c>
+      <c r="BQ75" s="12">
+        <v>2.8304630771809301E-3</v>
+      </c>
+      <c r="BR75" s="12">
+        <v>3.7887811283265899E-4</v>
+      </c>
+      <c r="BS75" s="12">
+        <v>32.508132670838599</v>
+      </c>
+      <c r="BT75" s="12">
+        <v>5.9800522260178197E-6</v>
+      </c>
+      <c r="BU75" s="12">
+        <v>-1.8760733432888999E-4</v>
+      </c>
+    </row>
+    <row r="77" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI77" s="25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="78" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI78" t="s">
+        <v>0</v>
+      </c>
+      <c r="BJ78" t="s">
+        <v>19</v>
+      </c>
+      <c r="BK78" t="s">
+        <v>20</v>
+      </c>
+      <c r="BL78" t="s">
+        <v>21</v>
+      </c>
+      <c r="BM78" t="s">
+        <v>3</v>
+      </c>
+      <c r="BN78" t="s">
+        <v>4</v>
+      </c>
+      <c r="BO78" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP78" t="s">
+        <v>30</v>
+      </c>
+      <c r="BQ78" t="s">
+        <v>31</v>
+      </c>
+      <c r="BR78" t="s">
+        <v>32</v>
+      </c>
+      <c r="BS78" t="s">
+        <v>33</v>
+      </c>
+      <c r="BT78" t="s">
+        <v>22</v>
+      </c>
+      <c r="BU78" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="79" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI79">
+        <v>1</v>
+      </c>
+      <c r="BJ79" s="12">
+        <v>2.8239332667508301</v>
+      </c>
+      <c r="BK79" s="12">
+        <v>-0.31091513244263502</v>
+      </c>
+      <c r="BL79" s="12">
+        <v>-1.11611018126785</v>
+      </c>
+      <c r="BM79" s="12">
+        <v>-0.46885500672508101</v>
+      </c>
+      <c r="BN79" s="12">
+        <v>-0.95254102834105503</v>
+      </c>
+      <c r="BO79" s="12">
+        <v>64</v>
+      </c>
+      <c r="BP79" s="12">
+        <v>2.1760667332491601</v>
+      </c>
+      <c r="BQ79" s="12">
+        <v>6.3109151324426298</v>
+      </c>
+      <c r="BR79" s="12">
+        <v>0.78402998076660002</v>
+      </c>
+      <c r="BS79" s="12">
+        <v>109.924143132483</v>
+      </c>
+      <c r="BT79" s="12">
+        <v>8.0323443974578898E-3</v>
+      </c>
+      <c r="BU79" s="12">
+        <v>-0.38391279847405502</v>
+      </c>
+    </row>
+    <row r="80" spans="6:73" x14ac:dyDescent="0.25">
+      <c r="BI80">
+        <v>2</v>
+      </c>
+      <c r="BJ80" s="12">
+        <v>2.78228125225522</v>
+      </c>
+      <c r="BK80" s="12">
+        <v>1.67987867019269</v>
+      </c>
+      <c r="BL80" s="12">
+        <v>-2.00092187010772</v>
+      </c>
+      <c r="BM80" s="12">
+        <v>-0.465926552649852</v>
+      </c>
+      <c r="BN80" s="12">
+        <v>0.87966651733381396</v>
+      </c>
+      <c r="BO80" s="12">
+        <v>5.1855364305336202</v>
+      </c>
+      <c r="BP80" s="12">
+        <v>4.1652014495610498E-2</v>
+      </c>
+      <c r="BQ80" s="12">
+        <v>1.99079380263533</v>
+      </c>
+      <c r="BR80" s="12">
+        <v>0.88481168883987105</v>
+      </c>
+      <c r="BS80" s="12">
+        <v>86.785868047509098</v>
+      </c>
+      <c r="BT80" s="12">
+        <v>0.45213840339419398</v>
+      </c>
+      <c r="BU80" s="12">
+        <v>-0.22065008270571901</v>
+      </c>
+    </row>
+    <row r="81" spans="61:73" x14ac:dyDescent="0.25">
+      <c r="BI81">
+        <v>3</v>
+      </c>
+      <c r="BJ81" s="12">
+        <v>2.5819132041508799</v>
+      </c>
+      <c r="BK81" s="12">
+        <v>2.05817233484541</v>
+      </c>
+      <c r="BL81" s="12">
+        <v>-2.1020009192173599</v>
+      </c>
+      <c r="BM81" s="12">
+        <v>-1.1643506327551501</v>
+      </c>
+      <c r="BN81" s="12">
+        <v>0.93944651058198902</v>
+      </c>
+      <c r="BO81" s="12">
+        <v>0.43004213210171</v>
+      </c>
+      <c r="BP81" s="12">
+        <v>0.200368048104342</v>
+      </c>
+      <c r="BQ81" s="12">
+        <v>0.37829366465272002</v>
+      </c>
+      <c r="BR81" s="12">
+        <v>0.10107904910964</v>
+      </c>
+      <c r="BS81" s="12">
+        <v>102.54186355456601</v>
+      </c>
+      <c r="BT81" s="12">
+        <v>0.52512086741167496</v>
+      </c>
+      <c r="BU81" s="12">
+        <v>0.26741542561333098</v>
+      </c>
+    </row>
+    <row r="82" spans="61:73" x14ac:dyDescent="0.25">
+      <c r="BI82">
+        <v>6</v>
+      </c>
+      <c r="BJ82" s="12">
+        <v>1.13763859375024</v>
+      </c>
+      <c r="BK82" s="12">
+        <v>1.9770668432018901</v>
+      </c>
+      <c r="BL82" s="12">
+        <v>-2.66001950697934</v>
+      </c>
+      <c r="BM82" s="12">
+        <v>5.0570917816719699E-2</v>
+      </c>
+      <c r="BN82" s="12">
+        <v>-2.26010441625493E-3</v>
+      </c>
+      <c r="BO82" s="12">
+        <v>0.26531258375549899</v>
+      </c>
+      <c r="BP82" s="12">
+        <v>2.2560791799899699E-2</v>
+      </c>
+      <c r="BQ82" s="12">
+        <v>0.14326648161344299</v>
+      </c>
+      <c r="BR82" s="12">
+        <v>4.0689419439797897E-2</v>
+      </c>
+      <c r="BS82" s="12">
+        <v>62.642077613483501</v>
+      </c>
+      <c r="BT82" s="12">
+        <v>-4.98504542824421E-2</v>
+      </c>
+      <c r="BU82" s="12">
+        <v>6.8352220186072704E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="61:73" x14ac:dyDescent="0.25">
+      <c r="BI83">
+        <v>7</v>
+      </c>
+      <c r="BJ83" s="12">
+        <v>1.1899851167022</v>
+      </c>
+      <c r="BK83" s="12">
+        <v>1.9747273838286601</v>
+      </c>
+      <c r="BL83" s="12">
+        <v>-2.66132547104483</v>
+      </c>
+      <c r="BM83" s="12">
+        <v>-9.6818512579216194E-5</v>
+      </c>
+      <c r="BN83" s="12">
+        <v>-1.13198630858474E-3</v>
+      </c>
+      <c r="BO83" s="12">
+        <v>1.03511119061902</v>
+      </c>
+      <c r="BP83" s="12">
+        <v>5.2346522951961502E-2</v>
+      </c>
+      <c r="BQ83" s="12">
+        <v>2.3394593732328699E-3</v>
+      </c>
+      <c r="BR83" s="12">
+        <v>1.3059640654917699E-3</v>
+      </c>
+      <c r="BS83" s="12">
+        <v>153.81512326399201</v>
+      </c>
+      <c r="BT83" s="12">
+        <v>1.2266188394113799E-4</v>
+      </c>
+      <c r="BU83" s="12">
+        <v>1.13083132227506E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="61:73" x14ac:dyDescent="0.25">
+      <c r="BI84">
+        <v>8</v>
+      </c>
+      <c r="BJ84" s="12">
+        <v>1.18995419993454</v>
+      </c>
+      <c r="BK84" s="12">
+        <v>1.97444235927062</v>
+      </c>
+      <c r="BL84" s="12">
+        <v>-2.6613256340960301</v>
+      </c>
+      <c r="BM84" s="12">
+        <v>-7.2896996595023101E-5</v>
+      </c>
+      <c r="BN84" s="12">
+        <v>3.2222554804606401E-6</v>
+      </c>
+      <c r="BO84" s="12">
+        <v>0.25204869410797898</v>
+      </c>
+      <c r="BP84" s="12">
+        <v>3.09167676642019E-5</v>
+      </c>
+      <c r="BQ84" s="12">
+        <v>2.85024558035917E-4</v>
+      </c>
+      <c r="BR84" s="12">
+        <v>1.63051199209007E-7</v>
+      </c>
+      <c r="BS84" s="12">
+        <v>118.545481961948</v>
+      </c>
+      <c r="BT84" s="12">
+        <v>7.2394274605286303E-5</v>
+      </c>
+      <c r="BU84" s="12">
+        <v>-7.8568962843111793E-6</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
